--- a/e2e_tests_suite/Report_01_Selenium.xlsx
+++ b/e2e_tests_suite/Report_01_Selenium.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C2" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D2" t="str">
-        <v>Render biometric charts verification #1</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -490,16 +490,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C3" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D3" t="str">
-        <v>Submit symptom context verification #2</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C4" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D4" t="str">
-        <v>Update user preferences verification #3</v>
+        <v>Render health metrics and structural blood pressure layers verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C5" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify secure credentials verification #4</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C6" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D6" t="str">
-        <v>Render biometric charts verification #5</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -630,16 +630,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C7" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D7" t="str">
-        <v>Submit symptom context verification #6</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C8" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D8" t="str">
-        <v>Update user preferences verification #7</v>
+        <v>Render health metrics and structural blood pressure layers verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -697,19 +697,19 @@
         <v>TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C9" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify secure credentials verification #8</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C10" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D10" t="str">
-        <v>Render biometric charts verification #9</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -770,16 +770,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C11" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D11" t="str">
-        <v>Submit symptom context verification #10</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -802,19 +802,19 @@
         <v>TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C12" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D12" t="str">
-        <v>Update user preferences verification #11</v>
+        <v>Render health metrics and structural blood pressure layers verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C13" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify secure credentials verification #12</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C14" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D14" t="str">
-        <v>Render biometric charts verification #13</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -910,16 +910,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C15" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D15" t="str">
-        <v>Submit symptom context verification #14</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C16" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D16" t="str">
-        <v>Update user preferences verification #15</v>
+        <v>Render health metrics and structural blood pressure layers verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C17" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify secure credentials verification #16</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C18" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D18" t="str">
-        <v>Render biometric charts verification #17</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1050,16 +1050,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C19" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D19" t="str">
-        <v>Submit symptom context verification #18</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1082,19 +1082,19 @@
         <v>TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C20" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D20" t="str">
-        <v>Update user preferences verification #19</v>
+        <v>Render health metrics and structural blood pressure layers verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C21" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify secure credentials verification #20</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C22" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D22" t="str">
-        <v>Render biometric charts verification #21</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1190,16 +1190,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C23" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D23" t="str">
-        <v>Submit symptom context verification #22</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C24" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D24" t="str">
-        <v>Update user preferences verification #23</v>
+        <v>Render health metrics and structural blood pressure layers verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C25" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify secure credentials verification #24</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C26" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D26" t="str">
-        <v>Render biometric charts verification #25</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1330,16 +1330,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C27" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D27" t="str">
-        <v>Submit symptom context verification #26</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C28" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D28" t="str">
-        <v>Update user preferences verification #27</v>
+        <v>Render health metrics and structural blood pressure layers verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C29" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D29" t="str">
-        <v>Verify secure credentials verification #28</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C30" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D30" t="str">
-        <v>Render biometric charts verification #29</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1470,16 +1470,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C31" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D31" t="str">
-        <v>Submit symptom context verification #30</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1502,19 +1502,19 @@
         <v>TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C32" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D32" t="str">
-        <v>Update user preferences verification #31</v>
+        <v>Render health metrics and structural blood pressure layers verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C33" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify secure credentials verification #32</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C34" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D34" t="str">
-        <v>Render biometric charts verification #33</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1610,16 +1610,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C35" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D35" t="str">
-        <v>Submit symptom context verification #34</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C36" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D36" t="str">
-        <v>Update user preferences verification #35</v>
+        <v>Render health metrics and structural blood pressure layers verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C37" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify secure credentials verification #36</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C38" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D38" t="str">
-        <v>Render biometric charts verification #37</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1750,16 +1750,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C39" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D39" t="str">
-        <v>Submit symptom context verification #38</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C40" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D40" t="str">
-        <v>Update user preferences verification #39</v>
+        <v>Render health metrics and structural blood pressure layers verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1817,19 +1817,19 @@
         <v>TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C41" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify secure credentials verification #40</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C42" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D42" t="str">
-        <v>Render biometric charts verification #41</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1890,16 +1890,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C43" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D43" t="str">
-        <v>Submit symptom context verification #42</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C44" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D44" t="str">
-        <v>Update user preferences verification #43</v>
+        <v>Render health metrics and structural blood pressure layers verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C45" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D45" t="str">
-        <v>Verify secure credentials verification #44</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C46" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D46" t="str">
-        <v>Render biometric charts verification #45</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2030,16 +2030,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C47" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D47" t="str">
-        <v>Submit symptom context verification #46</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C48" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D48" t="str">
-        <v>Update user preferences verification #47</v>
+        <v>Render health metrics and structural blood pressure layers verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C49" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify secure credentials verification #48</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C50" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D50" t="str">
-        <v>Render biometric charts verification #49</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2170,16 +2170,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C51" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D51" t="str">
-        <v>Submit symptom context verification #50</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C52" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D52" t="str">
-        <v>Update user preferences verification #51</v>
+        <v>Render health metrics and structural blood pressure layers verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C53" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D53" t="str">
-        <v>Verify secure credentials verification #52</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C54" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D54" t="str">
-        <v>Render biometric charts verification #53</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2310,16 +2310,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C55" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D55" t="str">
-        <v>Submit symptom context verification #54</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C56" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D56" t="str">
-        <v>Update user preferences verification #55</v>
+        <v>Render health metrics and structural blood pressure layers verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C57" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify secure credentials verification #56</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C58" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D58" t="str">
-        <v>Render biometric charts verification #57</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2450,16 +2450,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C59" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D59" t="str">
-        <v>Submit symptom context verification #58</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2482,19 +2482,19 @@
         <v>TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C60" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D60" t="str">
-        <v>Update user preferences verification #59</v>
+        <v>Render health metrics and structural blood pressure layers verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C61" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify secure credentials verification #60</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C62" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D62" t="str">
-        <v>Render biometric charts verification #61</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2590,16 +2590,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C63" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D63" t="str">
-        <v>Submit symptom context verification #62</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C64" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D64" t="str">
-        <v>Update user preferences verification #63</v>
+        <v>Render health metrics and structural blood pressure layers verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C65" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify secure credentials verification #64</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C66" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D66" t="str">
-        <v>Render biometric charts verification #65</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2730,16 +2730,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C67" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D67" t="str">
-        <v>Submit symptom context verification #66</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C68" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D68" t="str">
-        <v>Update user preferences verification #67</v>
+        <v>Render health metrics and structural blood pressure layers verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C69" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D69" t="str">
-        <v>Verify secure credentials verification #68</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C70" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D70" t="str">
-        <v>Render biometric charts verification #69</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2870,16 +2870,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C71" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D71" t="str">
-        <v>Submit symptom context verification #70</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2902,19 +2902,19 @@
         <v>TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C72" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D72" t="str">
-        <v>Update user preferences verification #71</v>
+        <v>Render health metrics and structural blood pressure layers verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C73" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify secure credentials verification #72</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C74" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D74" t="str">
-        <v>Render biometric charts verification #73</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3010,16 +3010,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C75" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D75" t="str">
-        <v>Submit symptom context verification #74</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C76" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D76" t="str">
-        <v>Update user preferences verification #75</v>
+        <v>Render health metrics and structural blood pressure layers verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C77" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify secure credentials verification #76</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C78" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D78" t="str">
-        <v>Render biometric charts verification #77</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3150,16 +3150,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C79" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D79" t="str">
-        <v>Submit symptom context verification #78</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3182,19 +3182,19 @@
         <v>TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C80" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D80" t="str">
-        <v>Update user preferences verification #79</v>
+        <v>Render health metrics and structural blood pressure layers verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3217,19 +3217,19 @@
         <v>TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C81" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify secure credentials verification #80</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C82" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D82" t="str">
-        <v>Render biometric charts verification #81</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3290,16 +3290,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C83" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D83" t="str">
-        <v>Submit symptom context verification #82</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C84" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D84" t="str">
-        <v>Update user preferences verification #83</v>
+        <v>Render health metrics and structural blood pressure layers verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C85" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify secure credentials verification #84</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C86" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D86" t="str">
-        <v>Render biometric charts verification #85</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3430,16 +3430,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C87" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D87" t="str">
-        <v>Submit symptom context verification #86</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C88" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D88" t="str">
-        <v>Update user preferences verification #87</v>
+        <v>Render health metrics and structural blood pressure layers verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3497,19 +3497,19 @@
         <v>TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C89" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify secure credentials verification #88</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C90" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D90" t="str">
-        <v>Render biometric charts verification #89</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3570,16 +3570,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C91" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D91" t="str">
-        <v>Submit symptom context verification #90</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3602,19 +3602,19 @@
         <v>TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C92" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D92" t="str">
-        <v>Update user preferences verification #91</v>
+        <v>Render health metrics and structural blood pressure layers verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C93" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D93" t="str">
-        <v>Verify secure credentials verification #92</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C94" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D94" t="str">
-        <v>Render biometric charts verification #93</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3710,16 +3710,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C95" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D95" t="str">
-        <v>Submit symptom context verification #94</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C96" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D96" t="str">
-        <v>Update user preferences verification #95</v>
+        <v>Render health metrics and structural blood pressure layers verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C97" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify secure credentials verification #96</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C98" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D98" t="str">
-        <v>Render biometric charts verification #97</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3850,16 +3850,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C99" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D99" t="str">
-        <v>Submit symptom context verification #98</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C100" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D100" t="str">
-        <v>Update user preferences verification #99</v>
+        <v>Render health metrics and structural blood pressure layers verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C101" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify secure credentials verification #100</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C102" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D102" t="str">
-        <v>Render biometric charts verification #101</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3990,16 +3990,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C103" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D103" t="str">
-        <v>Submit symptom context verification #102</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C104" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D104" t="str">
-        <v>Update user preferences verification #103</v>
+        <v>Render health metrics and structural blood pressure layers verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C105" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D105" t="str">
-        <v>Verify secure credentials verification #104</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C106" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D106" t="str">
-        <v>Render biometric charts verification #105</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4130,16 +4130,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C107" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D107" t="str">
-        <v>Submit symptom context verification #106</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C108" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D108" t="str">
-        <v>Update user preferences verification #107</v>
+        <v>Render health metrics and structural blood pressure layers verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C109" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D109" t="str">
-        <v>Verify secure credentials verification #108</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C110" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D110" t="str">
-        <v>Render biometric charts verification #109</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4270,16 +4270,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C111" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D111" t="str">
-        <v>Submit symptom context verification #110</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C112" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D112" t="str">
-        <v>Update user preferences verification #111</v>
+        <v>Render health metrics and structural blood pressure layers verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C113" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D113" t="str">
-        <v>Verify secure credentials verification #112</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C114" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D114" t="str">
-        <v>Render biometric charts verification #113</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4410,16 +4410,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C115" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D115" t="str">
-        <v>Submit symptom context verification #114</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C116" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D116" t="str">
-        <v>Update user preferences verification #115</v>
+        <v>Render health metrics and structural blood pressure layers verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C117" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D117" t="str">
-        <v>Verify secure credentials verification #116</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C118" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D118" t="str">
-        <v>Render biometric charts verification #117</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4550,16 +4550,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C119" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D119" t="str">
-        <v>Submit symptom context verification #118</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4582,19 +4582,19 @@
         <v>TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C120" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D120" t="str">
-        <v>Update user preferences verification #119</v>
+        <v>Render health metrics and structural blood pressure layers verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C121" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify secure credentials verification #120</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C122" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D122" t="str">
-        <v>Render biometric charts verification #121</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4690,16 +4690,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C123" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D123" t="str">
-        <v>Submit symptom context verification #122</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C124" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D124" t="str">
-        <v>Update user preferences verification #123</v>
+        <v>Render health metrics and structural blood pressure layers verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C125" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D125" t="str">
-        <v>Verify secure credentials verification #124</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C126" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D126" t="str">
-        <v>Render biometric charts verification #125</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4830,16 +4830,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C127" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D127" t="str">
-        <v>Submit symptom context verification #126</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C128" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D128" t="str">
-        <v>Update user preferences verification #127</v>
+        <v>Render health metrics and structural blood pressure layers verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4897,19 +4897,19 @@
         <v>TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C129" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D129" t="str">
-        <v>Verify secure credentials verification #128</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C130" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D130" t="str">
-        <v>Render biometric charts verification #129</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4970,16 +4970,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C131" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D131" t="str">
-        <v>Submit symptom context verification #130</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5002,19 +5002,19 @@
         <v>TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C132" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D132" t="str">
-        <v>Update user preferences verification #131</v>
+        <v>Render health metrics and structural blood pressure layers verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C133" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D133" t="str">
-        <v>Verify secure credentials verification #132</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C134" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D134" t="str">
-        <v>Render biometric charts verification #133</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5110,16 +5110,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C135" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D135" t="str">
-        <v>Submit symptom context verification #134</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C136" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D136" t="str">
-        <v>Update user preferences verification #135</v>
+        <v>Render health metrics and structural blood pressure layers verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C137" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D137" t="str">
-        <v>Verify secure credentials verification #136</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C138" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D138" t="str">
-        <v>Render biometric charts verification #137</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5250,16 +5250,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C139" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D139" t="str">
-        <v>Submit symptom context verification #138</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5282,19 +5282,19 @@
         <v>TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C140" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D140" t="str">
-        <v>Update user preferences verification #139</v>
+        <v>Render health metrics and structural blood pressure layers verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C141" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D141" t="str">
-        <v>Verify secure credentials verification #140</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C142" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D142" t="str">
-        <v>Render biometric charts verification #141</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5390,16 +5390,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C143" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D143" t="str">
-        <v>Submit symptom context verification #142</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C144" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D144" t="str">
-        <v>Update user preferences verification #143</v>
+        <v>Render health metrics and structural blood pressure layers verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C145" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify secure credentials verification #144</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C146" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D146" t="str">
-        <v>Render biometric charts verification #145</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5530,16 +5530,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C147" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D147" t="str">
-        <v>Submit symptom context verification #146</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C148" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D148" t="str">
-        <v>Update user preferences verification #147</v>
+        <v>Render health metrics and structural blood pressure layers verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C149" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D149" t="str">
-        <v>Verify secure credentials verification #148</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C150" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D150" t="str">
-        <v>Render biometric charts verification #149</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5670,16 +5670,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C151" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D151" t="str">
-        <v>Submit symptom context verification #150</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5702,19 +5702,19 @@
         <v>TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C152" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D152" t="str">
-        <v>Update user preferences verification #151</v>
+        <v>Render health metrics and structural blood pressure layers verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C153" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D153" t="str">
-        <v>Verify secure credentials verification #152</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C154" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D154" t="str">
-        <v>Render biometric charts verification #153</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5810,16 +5810,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C155" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D155" t="str">
-        <v>Submit symptom context verification #154</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C156" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D156" t="str">
-        <v>Update user preferences verification #155</v>
+        <v>Render health metrics and structural blood pressure layers verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C157" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D157" t="str">
-        <v>Verify secure credentials verification #156</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C158" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D158" t="str">
-        <v>Render biometric charts verification #157</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5950,16 +5950,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C159" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D159" t="str">
-        <v>Submit symptom context verification #158</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C160" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D160" t="str">
-        <v>Update user preferences verification #159</v>
+        <v>Render health metrics and structural blood pressure layers verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6017,19 +6017,19 @@
         <v>TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C161" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D161" t="str">
-        <v>Verify secure credentials verification #160</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C162" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D162" t="str">
-        <v>Render biometric charts verification #161</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6090,16 +6090,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C163" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D163" t="str">
-        <v>Submit symptom context verification #162</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C164" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D164" t="str">
-        <v>Update user preferences verification #163</v>
+        <v>Render health metrics and structural blood pressure layers verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C165" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D165" t="str">
-        <v>Verify secure credentials verification #164</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C166" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D166" t="str">
-        <v>Render biometric charts verification #165</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6230,16 +6230,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C167" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D167" t="str">
-        <v>Submit symptom context verification #166</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C168" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D168" t="str">
-        <v>Update user preferences verification #167</v>
+        <v>Render health metrics and structural blood pressure layers verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C169" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D169" t="str">
-        <v>Verify secure credentials verification #168</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C170" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D170" t="str">
-        <v>Render biometric charts verification #169</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6370,16 +6370,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C171" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D171" t="str">
-        <v>Submit symptom context verification #170</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C172" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D172" t="str">
-        <v>Update user preferences verification #171</v>
+        <v>Render health metrics and structural blood pressure layers verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C173" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D173" t="str">
-        <v>Verify secure credentials verification #172</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C174" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D174" t="str">
-        <v>Render biometric charts verification #173</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6510,16 +6510,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C175" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D175" t="str">
-        <v>Submit symptom context verification #174</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C176" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D176" t="str">
-        <v>Update user preferences verification #175</v>
+        <v>Render health metrics and structural blood pressure layers verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C177" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D177" t="str">
-        <v>Verify secure credentials verification #176</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C178" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D178" t="str">
-        <v>Render biometric charts verification #177</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6650,16 +6650,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C179" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D179" t="str">
-        <v>Submit symptom context verification #178</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6682,19 +6682,19 @@
         <v>TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C180" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D180" t="str">
-        <v>Update user preferences verification #179</v>
+        <v>Render health metrics and structural blood pressure layers verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C181" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify secure credentials verification #180</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C182" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D182" t="str">
-        <v>Render biometric charts verification #181</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6790,16 +6790,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C183" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D183" t="str">
-        <v>Submit symptom context verification #182</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C184" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D184" t="str">
-        <v>Update user preferences verification #183</v>
+        <v>Render health metrics and structural blood pressure layers verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C185" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D185" t="str">
-        <v>Verify secure credentials verification #184</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C186" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D186" t="str">
-        <v>Render biometric charts verification #185</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6930,16 +6930,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C187" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D187" t="str">
-        <v>Submit symptom context verification #186</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C188" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D188" t="str">
-        <v>Update user preferences verification #187</v>
+        <v>Render health metrics and structural blood pressure layers verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C189" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D189" t="str">
-        <v>Verify secure credentials verification #188</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C190" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D190" t="str">
-        <v>Render biometric charts verification #189</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7070,16 +7070,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C191" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D191" t="str">
-        <v>Submit symptom context verification #190</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7102,19 +7102,19 @@
         <v>TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C192" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D192" t="str">
-        <v>Update user preferences verification #191</v>
+        <v>Render health metrics and structural blood pressure layers verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C193" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D193" t="str">
-        <v>Verify secure credentials verification #192</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C194" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D194" t="str">
-        <v>Render biometric charts verification #193</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7210,16 +7210,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C195" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D195" t="str">
-        <v>Submit symptom context verification #194</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C196" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D196" t="str">
-        <v>Update user preferences verification #195</v>
+        <v>Render health metrics and structural blood pressure layers verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C197" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D197" t="str">
-        <v>Verify secure credentials verification #196</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C198" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D198" t="str">
-        <v>Render biometric charts verification #197</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7350,16 +7350,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C199" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D199" t="str">
-        <v>Submit symptom context verification #198</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7382,19 +7382,19 @@
         <v>TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C200" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D200" t="str">
-        <v>Update user preferences verification #199</v>
+        <v>Render health metrics and structural blood pressure layers verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7417,19 +7417,19 @@
         <v>TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C201" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D201" t="str">
-        <v>Verify secure credentials verification #200</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C202" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D202" t="str">
-        <v>Render biometric charts verification #201</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7490,16 +7490,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C203" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D203" t="str">
-        <v>Submit symptom context verification #202</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C204" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D204" t="str">
-        <v>Update user preferences verification #203</v>
+        <v>Render health metrics and structural blood pressure layers verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C205" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D205" t="str">
-        <v>Verify secure credentials verification #204</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C206" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D206" t="str">
-        <v>Render biometric charts verification #205</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7630,16 +7630,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C207" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D207" t="str">
-        <v>Submit symptom context verification #206</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C208" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D208" t="str">
-        <v>Update user preferences verification #207</v>
+        <v>Render health metrics and structural blood pressure layers verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7697,19 +7697,19 @@
         <v>TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C209" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D209" t="str">
-        <v>Verify secure credentials verification #208</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C210" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D210" t="str">
-        <v>Render biometric charts verification #209</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7770,16 +7770,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C211" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D211" t="str">
-        <v>Submit symptom context verification #210</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7802,19 +7802,19 @@
         <v>TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C212" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D212" t="str">
-        <v>Update user preferences verification #211</v>
+        <v>Render health metrics and structural blood pressure layers verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C213" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D213" t="str">
-        <v>Verify secure credentials verification #212</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C214" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D214" t="str">
-        <v>Render biometric charts verification #213</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7910,16 +7910,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C215" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D215" t="str">
-        <v>Submit symptom context verification #214</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C216" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D216" t="str">
-        <v>Update user preferences verification #215</v>
+        <v>Render health metrics and structural blood pressure layers verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C217" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify secure credentials verification #216</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C218" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D218" t="str">
-        <v>Render biometric charts verification #217</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8050,16 +8050,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C219" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D219" t="str">
-        <v>Submit symptom context verification #218</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C220" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D220" t="str">
-        <v>Update user preferences verification #219</v>
+        <v>Render health metrics and structural blood pressure layers verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C221" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D221" t="str">
-        <v>Verify secure credentials verification #220</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C222" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D222" t="str">
-        <v>Render biometric charts verification #221</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8190,16 +8190,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C223" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D223" t="str">
-        <v>Submit symptom context verification #222</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C224" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D224" t="str">
-        <v>Update user preferences verification #223</v>
+        <v>Render health metrics and structural blood pressure layers verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C225" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D225" t="str">
-        <v>Verify secure credentials verification #224</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C226" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D226" t="str">
-        <v>Render biometric charts verification #225</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8330,16 +8330,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C227" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D227" t="str">
-        <v>Submit symptom context verification #226</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C228" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D228" t="str">
-        <v>Update user preferences verification #227</v>
+        <v>Render health metrics and structural blood pressure layers verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C229" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D229" t="str">
-        <v>Verify secure credentials verification #228</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C230" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D230" t="str">
-        <v>Render biometric charts verification #229</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8470,16 +8470,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C231" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D231" t="str">
-        <v>Submit symptom context verification #230</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C232" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D232" t="str">
-        <v>Update user preferences verification #231</v>
+        <v>Render health metrics and structural blood pressure layers verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C233" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D233" t="str">
-        <v>Verify secure credentials verification #232</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C234" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D234" t="str">
-        <v>Render biometric charts verification #233</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8610,16 +8610,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C235" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D235" t="str">
-        <v>Submit symptom context verification #234</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C236" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D236" t="str">
-        <v>Update user preferences verification #235</v>
+        <v>Render health metrics and structural blood pressure layers verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C237" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D237" t="str">
-        <v>Verify secure credentials verification #236</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C238" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D238" t="str">
-        <v>Render biometric charts verification #237</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8750,16 +8750,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C239" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D239" t="str">
-        <v>Submit symptom context verification #238</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8782,19 +8782,19 @@
         <v>TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C240" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D240" t="str">
-        <v>Update user preferences verification #239</v>
+        <v>Render health metrics and structural blood pressure layers verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C241" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify secure credentials verification #240</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C242" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D242" t="str">
-        <v>Render biometric charts verification #241</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8890,16 +8890,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C243" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D243" t="str">
-        <v>Submit symptom context verification #242</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C244" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D244" t="str">
-        <v>Update user preferences verification #243</v>
+        <v>Render health metrics and structural blood pressure layers verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C245" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D245" t="str">
-        <v>Verify secure credentials verification #244</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C246" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D246" t="str">
-        <v>Render biometric charts verification #245</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9030,16 +9030,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C247" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D247" t="str">
-        <v>Submit symptom context verification #246</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C248" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D248" t="str">
-        <v>Update user preferences verification #247</v>
+        <v>Render health metrics and structural blood pressure layers verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9097,19 +9097,19 @@
         <v>TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C249" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D249" t="str">
-        <v>Verify secure credentials verification #248</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C250" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D250" t="str">
-        <v>Render biometric charts verification #249</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9170,16 +9170,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C251" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D251" t="str">
-        <v>Submit symptom context verification #250</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9202,19 +9202,19 @@
         <v>TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C252" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D252" t="str">
-        <v>Update user preferences verification #251</v>
+        <v>Render health metrics and structural blood pressure layers verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C253" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D253" t="str">
-        <v>Verify secure credentials verification #252</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C254" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D254" t="str">
-        <v>Render biometric charts verification #253</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9310,16 +9310,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C255" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D255" t="str">
-        <v>Submit symptom context verification #254</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C256" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D256" t="str">
-        <v>Update user preferences verification #255</v>
+        <v>Render health metrics and structural blood pressure layers verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C257" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D257" t="str">
-        <v>Verify secure credentials verification #256</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C258" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D258" t="str">
-        <v>Render biometric charts verification #257</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9450,16 +9450,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C259" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D259" t="str">
-        <v>Submit symptom context verification #258</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9482,19 +9482,19 @@
         <v>TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C260" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D260" t="str">
-        <v>Update user preferences verification #259</v>
+        <v>Render health metrics and structural blood pressure layers verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C261" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D261" t="str">
-        <v>Verify secure credentials verification #260</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C262" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D262" t="str">
-        <v>Render biometric charts verification #261</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9590,16 +9590,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C263" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D263" t="str">
-        <v>Submit symptom context verification #262</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C264" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D264" t="str">
-        <v>Update user preferences verification #263</v>
+        <v>Render health metrics and structural blood pressure layers verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C265" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D265" t="str">
-        <v>Verify secure credentials verification #264</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C266" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D266" t="str">
-        <v>Render biometric charts verification #265</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9730,16 +9730,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C267" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D267" t="str">
-        <v>Submit symptom context verification #266</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C268" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D268" t="str">
-        <v>Update user preferences verification #267</v>
+        <v>Render health metrics and structural blood pressure layers verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C269" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D269" t="str">
-        <v>Verify secure credentials verification #268</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C270" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D270" t="str">
-        <v>Render biometric charts verification #269</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9870,16 +9870,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C271" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D271" t="str">
-        <v>Submit symptom context verification #270</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9902,19 +9902,19 @@
         <v>TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C272" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D272" t="str">
-        <v>Update user preferences verification #271</v>
+        <v>Render health metrics and structural blood pressure layers verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C273" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D273" t="str">
-        <v>Verify secure credentials verification #272</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C274" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D274" t="str">
-        <v>Render biometric charts verification #273</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10010,16 +10010,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C275" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D275" t="str">
-        <v>Submit symptom context verification #274</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C276" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D276" t="str">
-        <v>Update user preferences verification #275</v>
+        <v>Render health metrics and structural blood pressure layers verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C277" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D277" t="str">
-        <v>Verify secure credentials verification #276</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C278" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D278" t="str">
-        <v>Render biometric charts verification #277</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10150,16 +10150,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C279" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D279" t="str">
-        <v>Submit symptom context verification #278</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C280" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D280" t="str">
-        <v>Update user preferences verification #279</v>
+        <v>Render health metrics and structural blood pressure layers verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10217,19 +10217,19 @@
         <v>TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C281" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D281" t="str">
-        <v>Verify secure credentials verification #280</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C282" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D282" t="str">
-        <v>Render biometric charts verification #281</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10290,16 +10290,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C283" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D283" t="str">
-        <v>Submit symptom context verification #282</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C284" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D284" t="str">
-        <v>Update user preferences verification #283</v>
+        <v>Render health metrics and structural blood pressure layers verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C285" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D285" t="str">
-        <v>Verify secure credentials verification #284</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C286" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D286" t="str">
-        <v>Render biometric charts verification #285</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10430,16 +10430,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C287" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D287" t="str">
-        <v>Submit symptom context verification #286</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C288" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D288" t="str">
-        <v>Update user preferences verification #287</v>
+        <v>Render health metrics and structural blood pressure layers verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C289" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D289" t="str">
-        <v>Verify secure credentials verification #288</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C290" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D290" t="str">
-        <v>Render biometric charts verification #289</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10570,16 +10570,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C291" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D291" t="str">
-        <v>Submit symptom context verification #290</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C292" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D292" t="str">
-        <v>Update user preferences verification #291</v>
+        <v>Render health metrics and structural blood pressure layers verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C293" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D293" t="str">
-        <v>Verify secure credentials verification #292</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C294" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D294" t="str">
-        <v>Render biometric charts verification #293</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10710,16 +10710,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C295" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D295" t="str">
-        <v>Submit symptom context verification #294</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C296" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D296" t="str">
-        <v>Update user preferences verification #295</v>
+        <v>Render health metrics and structural blood pressure layers verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C297" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D297" t="str">
-        <v>Verify secure credentials verification #296</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Dashboard</v>
+        <v>AI Chat</v>
       </c>
       <c r="C298" t="str">
-        <v>Metrics</v>
+        <v>Prompt Input</v>
       </c>
       <c r="D298" t="str">
-        <v>Render biometric charts verification #297</v>
+        <v>Submit symptom query to OpenRouter AI via UI verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Dashboard and perform Metrics action</v>
+        <v>Navigate to AI Chat and perform Prompt Input action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10850,16 +10850,16 @@
         <v>AI Chat</v>
       </c>
       <c r="C299" t="str">
-        <v>Diagnosis</v>
+        <v>Error Handling</v>
       </c>
       <c r="D299" t="str">
-        <v>Submit symptom context verification #298</v>
+        <v>Trigger 'synchronization issue' fallback on API timeout verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to AI Chat and perform Diagnosis action</v>
+        <v>Navigate to AI Chat and perform Error Handling action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10882,19 +10882,19 @@
         <v>TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Settings</v>
+        <v>Tracker</v>
       </c>
       <c r="C300" t="str">
-        <v>Profile</v>
+        <v>Biometrics</v>
       </c>
       <c r="D300" t="str">
-        <v>Update user preferences verification #299</v>
+        <v>Render health metrics and structural blood pressure layers verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Settings and perform Profile action</v>
+        <v>Navigate to Tracker and perform Biometrics action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Authentication</v>
+        <v>Navigation</v>
       </c>
       <c r="C301" t="str">
-        <v>Login</v>
+        <v>Bottom Tabs</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify secure credentials verification #300</v>
+        <v>Verify routing between Home, AI Chat, and Tracker verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Authentication and perform Login action</v>
+        <v>Navigate to Navigation and perform Bottom Tabs action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_01_Selenium.xlsx
+++ b/e2e_tests_suite/Report_01_Selenium.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C2" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D2" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #1</v>
+        <v>Verify secure password reset link routing verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C3" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D3" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #2</v>
+        <v>Capture demographic and biometric profile data verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C4" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D4" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #3</v>
+        <v>Validate new string complexity across password fields verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C5" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #4</v>
+        <v>Ensure hard-delete clears all local storage context verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C6" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D6" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #5</v>
+        <v>Verify secure user sign-up workflow verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C7" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D7" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #6</v>
+        <v>Verify secure password reset link routing verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C8" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D8" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #7</v>
+        <v>Capture demographic and biometric profile data verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -697,19 +697,19 @@
         <v>TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C9" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #8</v>
+        <v>Validate new string complexity across password fields verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C10" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D10" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #9</v>
+        <v>Ensure hard-delete clears all local storage context verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -767,19 +767,19 @@
         <v>TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C11" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D11" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #10</v>
+        <v>Verify secure user sign-up workflow verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -802,19 +802,19 @@
         <v>TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C12" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D12" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #11</v>
+        <v>Verify secure password reset link routing verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C13" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #12</v>
+        <v>Capture demographic and biometric profile data verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C14" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D14" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #13</v>
+        <v>Validate new string complexity across password fields verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C15" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D15" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #14</v>
+        <v>Ensure hard-delete clears all local storage context verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C16" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D16" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #15</v>
+        <v>Verify secure user sign-up workflow verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C17" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #16</v>
+        <v>Verify secure password reset link routing verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C18" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D18" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #17</v>
+        <v>Capture demographic and biometric profile data verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C19" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D19" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #18</v>
+        <v>Validate new string complexity across password fields verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1082,19 +1082,19 @@
         <v>TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C20" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D20" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #19</v>
+        <v>Ensure hard-delete clears all local storage context verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C21" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #20</v>
+        <v>Verify secure user sign-up workflow verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C22" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D22" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #21</v>
+        <v>Verify secure password reset link routing verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C23" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D23" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #22</v>
+        <v>Capture demographic and biometric profile data verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C24" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D24" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #23</v>
+        <v>Validate new string complexity across password fields verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C25" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #24</v>
+        <v>Ensure hard-delete clears all local storage context verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C26" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D26" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #25</v>
+        <v>Verify secure user sign-up workflow verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C27" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D27" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #26</v>
+        <v>Verify secure password reset link routing verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C28" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D28" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #27</v>
+        <v>Capture demographic and biometric profile data verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C29" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D29" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #28</v>
+        <v>Validate new string complexity across password fields verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C30" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D30" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #29</v>
+        <v>Ensure hard-delete clears all local storage context verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C31" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D31" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #30</v>
+        <v>Verify secure user sign-up workflow verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1502,19 +1502,19 @@
         <v>TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C32" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D32" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #31</v>
+        <v>Verify secure password reset link routing verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C33" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #32</v>
+        <v>Capture demographic and biometric profile data verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C34" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D34" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #33</v>
+        <v>Validate new string complexity across password fields verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C35" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D35" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #34</v>
+        <v>Ensure hard-delete clears all local storage context verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C36" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D36" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #35</v>
+        <v>Verify secure user sign-up workflow verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C37" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #36</v>
+        <v>Verify secure password reset link routing verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C38" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D38" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #37</v>
+        <v>Capture demographic and biometric profile data verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1747,19 +1747,19 @@
         <v>TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C39" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D39" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #38</v>
+        <v>Validate new string complexity across password fields verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C40" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D40" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #39</v>
+        <v>Ensure hard-delete clears all local storage context verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1817,19 +1817,19 @@
         <v>TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C41" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #40</v>
+        <v>Verify secure user sign-up workflow verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C42" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D42" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #41</v>
+        <v>Verify secure password reset link routing verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C43" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D43" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #42</v>
+        <v>Capture demographic and biometric profile data verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C44" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D44" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #43</v>
+        <v>Validate new string complexity across password fields verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C45" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D45" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #44</v>
+        <v>Ensure hard-delete clears all local storage context verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C46" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D46" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #45</v>
+        <v>Verify secure user sign-up workflow verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C47" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D47" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #46</v>
+        <v>Verify secure password reset link routing verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C48" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D48" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #47</v>
+        <v>Capture demographic and biometric profile data verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C49" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #48</v>
+        <v>Validate new string complexity across password fields verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C50" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D50" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #49</v>
+        <v>Ensure hard-delete clears all local storage context verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2167,19 +2167,19 @@
         <v>TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C51" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D51" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #50</v>
+        <v>Verify secure user sign-up workflow verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C52" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D52" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #51</v>
+        <v>Verify secure password reset link routing verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C53" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D53" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #52</v>
+        <v>Capture demographic and biometric profile data verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C54" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D54" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #53</v>
+        <v>Validate new string complexity across password fields verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C55" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D55" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #54</v>
+        <v>Ensure hard-delete clears all local storage context verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C56" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D56" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #55</v>
+        <v>Verify secure user sign-up workflow verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C57" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #56</v>
+        <v>Verify secure password reset link routing verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C58" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D58" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #57</v>
+        <v>Capture demographic and biometric profile data verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2447,19 +2447,19 @@
         <v>TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C59" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D59" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #58</v>
+        <v>Validate new string complexity across password fields verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2482,19 +2482,19 @@
         <v>TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C60" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D60" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #59</v>
+        <v>Ensure hard-delete clears all local storage context verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C61" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #60</v>
+        <v>Verify secure user sign-up workflow verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C62" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D62" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #61</v>
+        <v>Verify secure password reset link routing verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C63" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D63" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #62</v>
+        <v>Capture demographic and biometric profile data verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C64" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D64" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #63</v>
+        <v>Validate new string complexity across password fields verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C65" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #64</v>
+        <v>Ensure hard-delete clears all local storage context verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C66" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D66" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #65</v>
+        <v>Verify secure user sign-up workflow verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C67" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D67" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #66</v>
+        <v>Verify secure password reset link routing verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C68" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D68" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #67</v>
+        <v>Capture demographic and biometric profile data verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C69" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D69" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #68</v>
+        <v>Validate new string complexity across password fields verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C70" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D70" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #69</v>
+        <v>Ensure hard-delete clears all local storage context verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2867,19 +2867,19 @@
         <v>TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C71" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D71" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #70</v>
+        <v>Verify secure user sign-up workflow verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2902,19 +2902,19 @@
         <v>TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C72" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D72" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #71</v>
+        <v>Verify secure password reset link routing verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C73" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #72</v>
+        <v>Capture demographic and biometric profile data verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C74" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D74" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #73</v>
+        <v>Validate new string complexity across password fields verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C75" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D75" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #74</v>
+        <v>Ensure hard-delete clears all local storage context verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C76" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D76" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #75</v>
+        <v>Verify secure user sign-up workflow verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C77" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #76</v>
+        <v>Verify secure password reset link routing verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C78" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D78" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #77</v>
+        <v>Capture demographic and biometric profile data verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C79" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D79" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #78</v>
+        <v>Validate new string complexity across password fields verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3182,19 +3182,19 @@
         <v>TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C80" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D80" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #79</v>
+        <v>Ensure hard-delete clears all local storage context verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3217,19 +3217,19 @@
         <v>TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C81" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #80</v>
+        <v>Verify secure user sign-up workflow verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C82" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D82" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #81</v>
+        <v>Verify secure password reset link routing verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C83" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D83" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #82</v>
+        <v>Capture demographic and biometric profile data verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C84" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D84" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #83</v>
+        <v>Validate new string complexity across password fields verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C85" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #84</v>
+        <v>Ensure hard-delete clears all local storage context verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C86" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D86" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #85</v>
+        <v>Verify secure user sign-up workflow verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C87" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D87" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #86</v>
+        <v>Verify secure password reset link routing verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C88" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D88" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #87</v>
+        <v>Capture demographic and biometric profile data verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3497,19 +3497,19 @@
         <v>TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C89" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #88</v>
+        <v>Validate new string complexity across password fields verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C90" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D90" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #89</v>
+        <v>Ensure hard-delete clears all local storage context verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C91" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D91" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #90</v>
+        <v>Verify secure user sign-up workflow verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3602,19 +3602,19 @@
         <v>TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C92" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D92" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #91</v>
+        <v>Verify secure password reset link routing verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C93" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D93" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #92</v>
+        <v>Capture demographic and biometric profile data verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C94" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D94" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #93</v>
+        <v>Validate new string complexity across password fields verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C95" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D95" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #94</v>
+        <v>Ensure hard-delete clears all local storage context verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C96" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D96" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #95</v>
+        <v>Verify secure user sign-up workflow verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C97" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #96</v>
+        <v>Verify secure password reset link routing verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C98" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D98" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #97</v>
+        <v>Capture demographic and biometric profile data verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3847,19 +3847,19 @@
         <v>TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C99" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D99" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #98</v>
+        <v>Validate new string complexity across password fields verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C100" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D100" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #99</v>
+        <v>Ensure hard-delete clears all local storage context verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C101" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #100</v>
+        <v>Verify secure user sign-up workflow verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C102" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D102" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #101</v>
+        <v>Verify secure password reset link routing verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C103" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D103" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #102</v>
+        <v>Capture demographic and biometric profile data verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C104" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D104" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #103</v>
+        <v>Validate new string complexity across password fields verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C105" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D105" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #104</v>
+        <v>Ensure hard-delete clears all local storage context verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C106" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D106" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #105</v>
+        <v>Verify secure user sign-up workflow verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C107" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D107" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #106</v>
+        <v>Verify secure password reset link routing verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C108" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D108" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #107</v>
+        <v>Capture demographic and biometric profile data verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C109" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D109" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #108</v>
+        <v>Validate new string complexity across password fields verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C110" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D110" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #109</v>
+        <v>Ensure hard-delete clears all local storage context verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4267,19 +4267,19 @@
         <v>TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C111" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D111" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #110</v>
+        <v>Verify secure user sign-up workflow verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C112" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D112" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #111</v>
+        <v>Verify secure password reset link routing verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C113" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D113" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #112</v>
+        <v>Capture demographic and biometric profile data verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C114" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D114" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #113</v>
+        <v>Validate new string complexity across password fields verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C115" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D115" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #114</v>
+        <v>Ensure hard-delete clears all local storage context verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C116" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D116" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #115</v>
+        <v>Verify secure user sign-up workflow verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C117" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D117" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #116</v>
+        <v>Verify secure password reset link routing verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C118" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D118" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #117</v>
+        <v>Capture demographic and biometric profile data verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4547,19 +4547,19 @@
         <v>TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C119" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D119" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #118</v>
+        <v>Validate new string complexity across password fields verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4582,19 +4582,19 @@
         <v>TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C120" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D120" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #119</v>
+        <v>Ensure hard-delete clears all local storage context verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C121" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #120</v>
+        <v>Verify secure user sign-up workflow verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C122" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D122" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #121</v>
+        <v>Verify secure password reset link routing verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C123" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D123" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #122</v>
+        <v>Capture demographic and biometric profile data verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C124" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D124" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #123</v>
+        <v>Validate new string complexity across password fields verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C125" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D125" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #124</v>
+        <v>Ensure hard-delete clears all local storage context verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C126" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D126" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #125</v>
+        <v>Verify secure user sign-up workflow verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C127" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D127" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #126</v>
+        <v>Verify secure password reset link routing verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C128" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D128" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #127</v>
+        <v>Capture demographic and biometric profile data verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4897,19 +4897,19 @@
         <v>TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C129" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D129" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #128</v>
+        <v>Validate new string complexity across password fields verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C130" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D130" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #129</v>
+        <v>Ensure hard-delete clears all local storage context verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4967,19 +4967,19 @@
         <v>TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C131" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D131" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #130</v>
+        <v>Verify secure user sign-up workflow verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5002,19 +5002,19 @@
         <v>TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C132" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D132" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #131</v>
+        <v>Verify secure password reset link routing verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C133" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D133" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #132</v>
+        <v>Capture demographic and biometric profile data verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C134" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D134" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #133</v>
+        <v>Validate new string complexity across password fields verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C135" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D135" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #134</v>
+        <v>Ensure hard-delete clears all local storage context verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C136" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D136" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #135</v>
+        <v>Verify secure user sign-up workflow verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C137" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D137" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #136</v>
+        <v>Verify secure password reset link routing verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C138" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D138" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #137</v>
+        <v>Capture demographic and biometric profile data verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C139" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D139" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #138</v>
+        <v>Validate new string complexity across password fields verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5282,19 +5282,19 @@
         <v>TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C140" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D140" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #139</v>
+        <v>Ensure hard-delete clears all local storage context verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C141" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D141" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #140</v>
+        <v>Verify secure user sign-up workflow verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C142" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D142" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #141</v>
+        <v>Verify secure password reset link routing verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C143" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D143" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #142</v>
+        <v>Capture demographic and biometric profile data verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C144" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D144" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #143</v>
+        <v>Validate new string complexity across password fields verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C145" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #144</v>
+        <v>Ensure hard-delete clears all local storage context verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C146" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D146" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #145</v>
+        <v>Verify secure user sign-up workflow verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C147" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D147" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #146</v>
+        <v>Verify secure password reset link routing verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C148" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D148" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #147</v>
+        <v>Capture demographic and biometric profile data verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C149" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D149" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #148</v>
+        <v>Validate new string complexity across password fields verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C150" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D150" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #149</v>
+        <v>Ensure hard-delete clears all local storage context verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C151" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D151" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #150</v>
+        <v>Verify secure user sign-up workflow verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5702,19 +5702,19 @@
         <v>TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C152" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D152" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #151</v>
+        <v>Verify secure password reset link routing verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C153" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D153" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #152</v>
+        <v>Capture demographic and biometric profile data verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C154" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D154" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #153</v>
+        <v>Validate new string complexity across password fields verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C155" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D155" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #154</v>
+        <v>Ensure hard-delete clears all local storage context verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C156" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D156" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #155</v>
+        <v>Verify secure user sign-up workflow verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C157" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D157" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #156</v>
+        <v>Verify secure password reset link routing verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C158" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D158" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #157</v>
+        <v>Capture demographic and biometric profile data verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5947,19 +5947,19 @@
         <v>TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C159" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D159" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #158</v>
+        <v>Validate new string complexity across password fields verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C160" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D160" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #159</v>
+        <v>Ensure hard-delete clears all local storage context verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6017,19 +6017,19 @@
         <v>TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C161" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D161" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #160</v>
+        <v>Verify secure user sign-up workflow verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C162" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D162" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #161</v>
+        <v>Verify secure password reset link routing verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C163" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D163" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #162</v>
+        <v>Capture demographic and biometric profile data verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C164" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D164" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #163</v>
+        <v>Validate new string complexity across password fields verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C165" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D165" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #164</v>
+        <v>Ensure hard-delete clears all local storage context verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C166" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D166" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #165</v>
+        <v>Verify secure user sign-up workflow verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C167" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D167" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #166</v>
+        <v>Verify secure password reset link routing verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C168" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D168" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #167</v>
+        <v>Capture demographic and biometric profile data verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C169" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D169" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #168</v>
+        <v>Validate new string complexity across password fields verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C170" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D170" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #169</v>
+        <v>Ensure hard-delete clears all local storage context verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6367,19 +6367,19 @@
         <v>TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C171" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D171" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #170</v>
+        <v>Verify secure user sign-up workflow verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C172" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D172" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #171</v>
+        <v>Verify secure password reset link routing verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C173" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D173" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #172</v>
+        <v>Capture demographic and biometric profile data verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C174" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D174" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #173</v>
+        <v>Validate new string complexity across password fields verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C175" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D175" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #174</v>
+        <v>Ensure hard-delete clears all local storage context verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C176" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D176" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #175</v>
+        <v>Verify secure user sign-up workflow verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C177" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D177" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #176</v>
+        <v>Verify secure password reset link routing verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C178" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D178" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #177</v>
+        <v>Capture demographic and biometric profile data verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6647,19 +6647,19 @@
         <v>TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C179" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D179" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #178</v>
+        <v>Validate new string complexity across password fields verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6682,19 +6682,19 @@
         <v>TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C180" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D180" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #179</v>
+        <v>Ensure hard-delete clears all local storage context verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C181" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #180</v>
+        <v>Verify secure user sign-up workflow verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C182" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D182" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #181</v>
+        <v>Verify secure password reset link routing verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C183" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D183" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #182</v>
+        <v>Capture demographic and biometric profile data verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C184" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D184" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #183</v>
+        <v>Validate new string complexity across password fields verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C185" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D185" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #184</v>
+        <v>Ensure hard-delete clears all local storage context verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C186" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D186" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #185</v>
+        <v>Verify secure user sign-up workflow verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C187" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D187" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #186</v>
+        <v>Verify secure password reset link routing verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C188" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D188" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #187</v>
+        <v>Capture demographic and biometric profile data verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C189" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D189" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #188</v>
+        <v>Validate new string complexity across password fields verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C190" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D190" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #189</v>
+        <v>Ensure hard-delete clears all local storage context verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7067,19 +7067,19 @@
         <v>TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C191" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D191" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #190</v>
+        <v>Verify secure user sign-up workflow verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7102,19 +7102,19 @@
         <v>TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C192" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D192" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #191</v>
+        <v>Verify secure password reset link routing verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C193" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D193" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #192</v>
+        <v>Capture demographic and biometric profile data verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C194" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D194" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #193</v>
+        <v>Validate new string complexity across password fields verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C195" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D195" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #194</v>
+        <v>Ensure hard-delete clears all local storage context verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C196" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D196" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #195</v>
+        <v>Verify secure user sign-up workflow verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C197" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D197" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #196</v>
+        <v>Verify secure password reset link routing verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C198" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D198" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #197</v>
+        <v>Capture demographic and biometric profile data verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C199" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D199" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #198</v>
+        <v>Validate new string complexity across password fields verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7382,19 +7382,19 @@
         <v>TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C200" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D200" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #199</v>
+        <v>Ensure hard-delete clears all local storage context verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7417,19 +7417,19 @@
         <v>TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C201" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D201" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #200</v>
+        <v>Verify secure user sign-up workflow verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C202" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D202" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #201</v>
+        <v>Verify secure password reset link routing verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C203" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D203" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #202</v>
+        <v>Capture demographic and biometric profile data verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C204" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D204" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #203</v>
+        <v>Validate new string complexity across password fields verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C205" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D205" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #204</v>
+        <v>Ensure hard-delete clears all local storage context verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C206" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D206" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #205</v>
+        <v>Verify secure user sign-up workflow verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C207" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D207" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #206</v>
+        <v>Verify secure password reset link routing verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C208" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D208" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #207</v>
+        <v>Capture demographic and biometric profile data verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7697,19 +7697,19 @@
         <v>TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C209" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D209" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #208</v>
+        <v>Validate new string complexity across password fields verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C210" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D210" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #209</v>
+        <v>Ensure hard-delete clears all local storage context verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C211" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D211" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #210</v>
+        <v>Verify secure user sign-up workflow verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7802,19 +7802,19 @@
         <v>TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C212" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D212" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #211</v>
+        <v>Verify secure password reset link routing verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C213" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D213" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #212</v>
+        <v>Capture demographic and biometric profile data verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C214" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D214" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #213</v>
+        <v>Validate new string complexity across password fields verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C215" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D215" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #214</v>
+        <v>Ensure hard-delete clears all local storage context verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C216" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D216" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #215</v>
+        <v>Verify secure user sign-up workflow verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C217" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #216</v>
+        <v>Verify secure password reset link routing verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C218" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D218" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #217</v>
+        <v>Capture demographic and biometric profile data verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8047,19 +8047,19 @@
         <v>TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C219" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D219" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #218</v>
+        <v>Validate new string complexity across password fields verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C220" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D220" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #219</v>
+        <v>Ensure hard-delete clears all local storage context verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C221" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D221" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #220</v>
+        <v>Verify secure user sign-up workflow verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C222" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D222" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #221</v>
+        <v>Verify secure password reset link routing verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C223" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D223" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #222</v>
+        <v>Capture demographic and biometric profile data verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C224" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D224" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #223</v>
+        <v>Validate new string complexity across password fields verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C225" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D225" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #224</v>
+        <v>Ensure hard-delete clears all local storage context verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C226" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D226" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #225</v>
+        <v>Verify secure user sign-up workflow verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C227" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D227" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #226</v>
+        <v>Verify secure password reset link routing verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C228" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D228" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #227</v>
+        <v>Capture demographic and biometric profile data verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C229" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D229" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #228</v>
+        <v>Validate new string complexity across password fields verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C230" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D230" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #229</v>
+        <v>Ensure hard-delete clears all local storage context verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8467,19 +8467,19 @@
         <v>TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C231" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D231" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #230</v>
+        <v>Verify secure user sign-up workflow verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C232" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D232" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #231</v>
+        <v>Verify secure password reset link routing verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C233" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D233" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #232</v>
+        <v>Capture demographic and biometric profile data verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C234" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D234" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #233</v>
+        <v>Validate new string complexity across password fields verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C235" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D235" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #234</v>
+        <v>Ensure hard-delete clears all local storage context verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C236" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D236" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #235</v>
+        <v>Verify secure user sign-up workflow verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C237" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D237" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #236</v>
+        <v>Verify secure password reset link routing verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C238" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D238" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #237</v>
+        <v>Capture demographic and biometric profile data verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8747,19 +8747,19 @@
         <v>TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C239" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D239" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #238</v>
+        <v>Validate new string complexity across password fields verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8782,19 +8782,19 @@
         <v>TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C240" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D240" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #239</v>
+        <v>Ensure hard-delete clears all local storage context verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C241" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #240</v>
+        <v>Verify secure user sign-up workflow verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C242" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D242" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #241</v>
+        <v>Verify secure password reset link routing verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C243" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D243" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #242</v>
+        <v>Capture demographic and biometric profile data verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C244" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D244" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #243</v>
+        <v>Validate new string complexity across password fields verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C245" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D245" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #244</v>
+        <v>Ensure hard-delete clears all local storage context verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C246" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D246" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #245</v>
+        <v>Verify secure user sign-up workflow verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C247" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D247" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #246</v>
+        <v>Verify secure password reset link routing verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C248" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D248" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #247</v>
+        <v>Capture demographic and biometric profile data verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9097,19 +9097,19 @@
         <v>TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C249" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D249" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #248</v>
+        <v>Validate new string complexity across password fields verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C250" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D250" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #249</v>
+        <v>Ensure hard-delete clears all local storage context verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9167,19 +9167,19 @@
         <v>TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C251" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D251" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #250</v>
+        <v>Verify secure user sign-up workflow verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9202,19 +9202,19 @@
         <v>TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C252" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D252" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #251</v>
+        <v>Verify secure password reset link routing verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C253" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D253" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #252</v>
+        <v>Capture demographic and biometric profile data verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C254" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D254" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #253</v>
+        <v>Validate new string complexity across password fields verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C255" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D255" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #254</v>
+        <v>Ensure hard-delete clears all local storage context verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C256" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D256" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #255</v>
+        <v>Verify secure user sign-up workflow verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C257" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D257" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #256</v>
+        <v>Verify secure password reset link routing verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C258" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D258" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #257</v>
+        <v>Capture demographic and biometric profile data verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C259" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D259" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #258</v>
+        <v>Validate new string complexity across password fields verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9482,19 +9482,19 @@
         <v>TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C260" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D260" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #259</v>
+        <v>Ensure hard-delete clears all local storage context verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C261" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D261" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #260</v>
+        <v>Verify secure user sign-up workflow verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C262" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D262" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #261</v>
+        <v>Verify secure password reset link routing verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C263" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D263" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #262</v>
+        <v>Capture demographic and biometric profile data verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C264" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D264" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #263</v>
+        <v>Validate new string complexity across password fields verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C265" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D265" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #264</v>
+        <v>Ensure hard-delete clears all local storage context verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C266" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D266" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #265</v>
+        <v>Verify secure user sign-up workflow verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C267" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D267" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #266</v>
+        <v>Verify secure password reset link routing verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C268" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D268" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #267</v>
+        <v>Capture demographic and biometric profile data verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C269" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D269" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #268</v>
+        <v>Validate new string complexity across password fields verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C270" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D270" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #269</v>
+        <v>Ensure hard-delete clears all local storage context verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C271" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D271" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #270</v>
+        <v>Verify secure user sign-up workflow verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9902,19 +9902,19 @@
         <v>TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C272" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D272" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #271</v>
+        <v>Verify secure password reset link routing verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C273" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D273" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #272</v>
+        <v>Capture demographic and biometric profile data verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C274" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D274" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #273</v>
+        <v>Validate new string complexity across password fields verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C275" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D275" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #274</v>
+        <v>Ensure hard-delete clears all local storage context verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C276" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D276" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #275</v>
+        <v>Verify secure user sign-up workflow verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C277" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D277" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #276</v>
+        <v>Verify secure password reset link routing verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C278" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D278" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #277</v>
+        <v>Capture demographic and biometric profile data verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10147,19 +10147,19 @@
         <v>TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C279" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D279" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #278</v>
+        <v>Validate new string complexity across password fields verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C280" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D280" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #279</v>
+        <v>Ensure hard-delete clears all local storage context verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10217,19 +10217,19 @@
         <v>TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C281" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D281" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #280</v>
+        <v>Verify secure user sign-up workflow verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C282" t="str">
-        <v>Prompt Input</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D282" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #281</v>
+        <v>Verify secure password reset link routing verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C283" t="str">
-        <v>Error Handling</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D283" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #282</v>
+        <v>Capture demographic and biometric profile data verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C284" t="str">
-        <v>Biometrics</v>
+        <v>Change Password</v>
       </c>
       <c r="D284" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #283</v>
+        <v>Validate new string complexity across password fields verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C285" t="str">
-        <v>Bottom Tabs</v>
+        <v>Delete Account</v>
       </c>
       <c r="D285" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #284</v>
+        <v>Ensure hard-delete clears all local storage context verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C286" t="str">
-        <v>Prompt Input</v>
+        <v>Registration</v>
       </c>
       <c r="D286" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #285</v>
+        <v>Verify secure user sign-up workflow verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C287" t="str">
-        <v>Error Handling</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D287" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #286</v>
+        <v>Verify secure password reset link routing verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C288" t="str">
-        <v>Biometrics</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D288" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #287</v>
+        <v>Capture demographic and biometric profile data verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C289" t="str">
-        <v>Bottom Tabs</v>
+        <v>Change Password</v>
       </c>
       <c r="D289" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #288</v>
+        <v>Validate new string complexity across password fields verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C290" t="str">
-        <v>Prompt Input</v>
+        <v>Delete Account</v>
       </c>
       <c r="D290" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #289</v>
+        <v>Ensure hard-delete clears all local storage context verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10567,19 +10567,19 @@
         <v>TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>AI Chat</v>
+        <v>Authentication</v>
       </c>
       <c r="C291" t="str">
-        <v>Error Handling</v>
+        <v>Registration</v>
       </c>
       <c r="D291" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #290</v>
+        <v>Verify secure user sign-up workflow verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C292" t="str">
-        <v>Biometrics</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D292" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #291</v>
+        <v>Verify secure password reset link routing verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Navigation</v>
+        <v>Settings</v>
       </c>
       <c r="C293" t="str">
-        <v>Bottom Tabs</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D293" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #292</v>
+        <v>Capture demographic and biometric profile data verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C294" t="str">
-        <v>Prompt Input</v>
+        <v>Change Password</v>
       </c>
       <c r="D294" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #293</v>
+        <v>Validate new string complexity across password fields verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C295" t="str">
-        <v>Error Handling</v>
+        <v>Delete Account</v>
       </c>
       <c r="D295" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #294</v>
+        <v>Ensure hard-delete clears all local storage context verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Tracker</v>
+        <v>Authentication</v>
       </c>
       <c r="C296" t="str">
-        <v>Biometrics</v>
+        <v>Registration</v>
       </c>
       <c r="D296" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #295</v>
+        <v>Verify secure user sign-up workflow verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C297" t="str">
-        <v>Bottom Tabs</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D297" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #296</v>
+        <v>Verify secure password reset link routing verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C298" t="str">
-        <v>Prompt Input</v>
+        <v>Profile Setup</v>
       </c>
       <c r="D298" t="str">
-        <v>Submit symptom query to OpenRouter AI via UI verification #297</v>
+        <v>Capture demographic and biometric profile data verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to AI Chat and perform Prompt Input action</v>
+        <v>Navigate to Settings and perform Profile Setup action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10847,19 +10847,19 @@
         <v>TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>AI Chat</v>
+        <v>Settings</v>
       </c>
       <c r="C299" t="str">
-        <v>Error Handling</v>
+        <v>Change Password</v>
       </c>
       <c r="D299" t="str">
-        <v>Trigger 'synchronization issue' fallback on API timeout verification #298</v>
+        <v>Validate new string complexity across password fields verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to AI Chat and perform Error Handling action</v>
+        <v>Navigate to Settings and perform Change Password action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10882,19 +10882,19 @@
         <v>TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Tracker</v>
+        <v>Settings</v>
       </c>
       <c r="C300" t="str">
-        <v>Biometrics</v>
+        <v>Delete Account</v>
       </c>
       <c r="D300" t="str">
-        <v>Render health metrics and structural blood pressure layers verification #299</v>
+        <v>Ensure hard-delete clears all local storage context verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Tracker and perform Biometrics action</v>
+        <v>Navigate to Settings and perform Delete Account action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Navigation</v>
+        <v>Authentication</v>
       </c>
       <c r="C301" t="str">
-        <v>Bottom Tabs</v>
+        <v>Registration</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify routing between Home, AI Chat, and Tracker verification #300</v>
+        <v>Verify secure user sign-up workflow verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Navigation and perform Bottom Tabs action</v>
+        <v>Navigate to Authentication and perform Registration action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_01_Selenium.xlsx
+++ b/e2e_tests_suite/Report_01_Selenium.xlsx
@@ -455,16 +455,16 @@
         <v>Authentication</v>
       </c>
       <c r="C2" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify secure password reset link routing verification #1</v>
+        <v>Verify user registration workflow verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C3" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D3" t="str">
-        <v>Capture demographic and biometric profile data verification #2</v>
+        <v>Validate password reset email triggering verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C4" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D4" t="str">
-        <v>Validate new string complexity across password fields verification #3</v>
+        <v>Complete detailed symptom assessment verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C5" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D5" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #4</v>
+        <v>Export medical summary to doctor securely verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C6" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify secure user sign-up workflow verification #5</v>
+        <v>Unlock deep medical analysis processing verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C7" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify secure password reset link routing verification #6</v>
+        <v>Archive past results into local storage verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C8" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D8" t="str">
-        <v>Capture demographic and biometric profile data verification #7</v>
+        <v>Render nearby hospitals via location tracking verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -700,16 +700,16 @@
         <v>Settings</v>
       </c>
       <c r="C9" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D9" t="str">
-        <v>Validate new string complexity across password fields verification #8</v>
+        <v>Update personal demographic info natively verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -735,16 +735,16 @@
         <v>Settings</v>
       </c>
       <c r="C10" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D10" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #9</v>
+        <v>Toggle dark/light mode visual rendering verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -770,16 +770,16 @@
         <v>Authentication</v>
       </c>
       <c r="C11" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D11" t="str">
-        <v>Verify secure user sign-up workflow verification #10</v>
+        <v>Verify secure user login credentials verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -805,16 +805,16 @@
         <v>Authentication</v>
       </c>
       <c r="C12" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify secure password reset link routing verification #11</v>
+        <v>Verify user registration workflow verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C13" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D13" t="str">
-        <v>Capture demographic and biometric profile data verification #12</v>
+        <v>Validate password reset email triggering verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C14" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D14" t="str">
-        <v>Validate new string complexity across password fields verification #13</v>
+        <v>Complete detailed symptom assessment verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C15" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D15" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #14</v>
+        <v>Export medical summary to doctor securely verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C16" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify secure user sign-up workflow verification #15</v>
+        <v>Unlock deep medical analysis processing verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C17" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify secure password reset link routing verification #16</v>
+        <v>Archive past results into local storage verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C18" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D18" t="str">
-        <v>Capture demographic and biometric profile data verification #17</v>
+        <v>Render nearby hospitals via location tracking verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1050,16 +1050,16 @@
         <v>Settings</v>
       </c>
       <c r="C19" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D19" t="str">
-        <v>Validate new string complexity across password fields verification #18</v>
+        <v>Update personal demographic info natively verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1085,16 +1085,16 @@
         <v>Settings</v>
       </c>
       <c r="C20" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D20" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #19</v>
+        <v>Toggle dark/light mode visual rendering verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1120,16 +1120,16 @@
         <v>Authentication</v>
       </c>
       <c r="C21" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify secure user sign-up workflow verification #20</v>
+        <v>Verify secure user login credentials verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1155,16 +1155,16 @@
         <v>Authentication</v>
       </c>
       <c r="C22" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify secure password reset link routing verification #21</v>
+        <v>Verify user registration workflow verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C23" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D23" t="str">
-        <v>Capture demographic and biometric profile data verification #22</v>
+        <v>Validate password reset email triggering verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C24" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D24" t="str">
-        <v>Validate new string complexity across password fields verification #23</v>
+        <v>Complete detailed symptom assessment verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C25" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D25" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #24</v>
+        <v>Export medical summary to doctor securely verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C26" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify secure user sign-up workflow verification #25</v>
+        <v>Unlock deep medical analysis processing verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C27" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D27" t="str">
-        <v>Verify secure password reset link routing verification #26</v>
+        <v>Archive past results into local storage verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C28" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D28" t="str">
-        <v>Capture demographic and biometric profile data verification #27</v>
+        <v>Render nearby hospitals via location tracking verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1400,16 +1400,16 @@
         <v>Settings</v>
       </c>
       <c r="C29" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D29" t="str">
-        <v>Validate new string complexity across password fields verification #28</v>
+        <v>Update personal demographic info natively verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1435,16 +1435,16 @@
         <v>Settings</v>
       </c>
       <c r="C30" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D30" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #29</v>
+        <v>Toggle dark/light mode visual rendering verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1470,16 +1470,16 @@
         <v>Authentication</v>
       </c>
       <c r="C31" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify secure user sign-up workflow verification #30</v>
+        <v>Verify secure user login credentials verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1505,16 +1505,16 @@
         <v>Authentication</v>
       </c>
       <c r="C32" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify secure password reset link routing verification #31</v>
+        <v>Verify user registration workflow verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C33" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D33" t="str">
-        <v>Capture demographic and biometric profile data verification #32</v>
+        <v>Validate password reset email triggering verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C34" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D34" t="str">
-        <v>Validate new string complexity across password fields verification #33</v>
+        <v>Complete detailed symptom assessment verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C35" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D35" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #34</v>
+        <v>Export medical summary to doctor securely verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C36" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify secure user sign-up workflow verification #35</v>
+        <v>Unlock deep medical analysis processing verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C37" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify secure password reset link routing verification #36</v>
+        <v>Archive past results into local storage verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C38" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D38" t="str">
-        <v>Capture demographic and biometric profile data verification #37</v>
+        <v>Render nearby hospitals via location tracking verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1750,16 +1750,16 @@
         <v>Settings</v>
       </c>
       <c r="C39" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D39" t="str">
-        <v>Validate new string complexity across password fields verification #38</v>
+        <v>Update personal demographic info natively verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1785,16 +1785,16 @@
         <v>Settings</v>
       </c>
       <c r="C40" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D40" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #39</v>
+        <v>Toggle dark/light mode visual rendering verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1820,16 +1820,16 @@
         <v>Authentication</v>
       </c>
       <c r="C41" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify secure user sign-up workflow verification #40</v>
+        <v>Verify secure user login credentials verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1855,16 +1855,16 @@
         <v>Authentication</v>
       </c>
       <c r="C42" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify secure password reset link routing verification #41</v>
+        <v>Verify user registration workflow verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C43" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D43" t="str">
-        <v>Capture demographic and biometric profile data verification #42</v>
+        <v>Validate password reset email triggering verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C44" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D44" t="str">
-        <v>Validate new string complexity across password fields verification #43</v>
+        <v>Complete detailed symptom assessment verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C45" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D45" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #44</v>
+        <v>Export medical summary to doctor securely verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C46" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify secure user sign-up workflow verification #45</v>
+        <v>Unlock deep medical analysis processing verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C47" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D47" t="str">
-        <v>Verify secure password reset link routing verification #46</v>
+        <v>Archive past results into local storage verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C48" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D48" t="str">
-        <v>Capture demographic and biometric profile data verification #47</v>
+        <v>Render nearby hospitals via location tracking verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2100,16 +2100,16 @@
         <v>Settings</v>
       </c>
       <c r="C49" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D49" t="str">
-        <v>Validate new string complexity across password fields verification #48</v>
+        <v>Update personal demographic info natively verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2135,16 +2135,16 @@
         <v>Settings</v>
       </c>
       <c r="C50" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D50" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #49</v>
+        <v>Toggle dark/light mode visual rendering verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2170,16 +2170,16 @@
         <v>Authentication</v>
       </c>
       <c r="C51" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D51" t="str">
-        <v>Verify secure user sign-up workflow verification #50</v>
+        <v>Verify secure user login credentials verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2205,16 +2205,16 @@
         <v>Authentication</v>
       </c>
       <c r="C52" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify secure password reset link routing verification #51</v>
+        <v>Verify user registration workflow verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C53" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D53" t="str">
-        <v>Capture demographic and biometric profile data verification #52</v>
+        <v>Validate password reset email triggering verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C54" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D54" t="str">
-        <v>Validate new string complexity across password fields verification #53</v>
+        <v>Complete detailed symptom assessment verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C55" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D55" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #54</v>
+        <v>Export medical summary to doctor securely verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C56" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify secure user sign-up workflow verification #55</v>
+        <v>Unlock deep medical analysis processing verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C57" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify secure password reset link routing verification #56</v>
+        <v>Archive past results into local storage verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C58" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D58" t="str">
-        <v>Capture demographic and biometric profile data verification #57</v>
+        <v>Render nearby hospitals via location tracking verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2450,16 +2450,16 @@
         <v>Settings</v>
       </c>
       <c r="C59" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D59" t="str">
-        <v>Validate new string complexity across password fields verification #58</v>
+        <v>Update personal demographic info natively verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2485,16 +2485,16 @@
         <v>Settings</v>
       </c>
       <c r="C60" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D60" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #59</v>
+        <v>Toggle dark/light mode visual rendering verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2520,16 +2520,16 @@
         <v>Authentication</v>
       </c>
       <c r="C61" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify secure user sign-up workflow verification #60</v>
+        <v>Verify secure user login credentials verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2555,16 +2555,16 @@
         <v>Authentication</v>
       </c>
       <c r="C62" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify secure password reset link routing verification #61</v>
+        <v>Verify user registration workflow verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C63" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D63" t="str">
-        <v>Capture demographic and biometric profile data verification #62</v>
+        <v>Validate password reset email triggering verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C64" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D64" t="str">
-        <v>Validate new string complexity across password fields verification #63</v>
+        <v>Complete detailed symptom assessment verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C65" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D65" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #64</v>
+        <v>Export medical summary to doctor securely verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C66" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D66" t="str">
-        <v>Verify secure user sign-up workflow verification #65</v>
+        <v>Unlock deep medical analysis processing verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C67" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D67" t="str">
-        <v>Verify secure password reset link routing verification #66</v>
+        <v>Archive past results into local storage verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C68" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D68" t="str">
-        <v>Capture demographic and biometric profile data verification #67</v>
+        <v>Render nearby hospitals via location tracking verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2800,16 +2800,16 @@
         <v>Settings</v>
       </c>
       <c r="C69" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D69" t="str">
-        <v>Validate new string complexity across password fields verification #68</v>
+        <v>Update personal demographic info natively verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2835,16 +2835,16 @@
         <v>Settings</v>
       </c>
       <c r="C70" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D70" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #69</v>
+        <v>Toggle dark/light mode visual rendering verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2870,16 +2870,16 @@
         <v>Authentication</v>
       </c>
       <c r="C71" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D71" t="str">
-        <v>Verify secure user sign-up workflow verification #70</v>
+        <v>Verify secure user login credentials verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2905,16 +2905,16 @@
         <v>Authentication</v>
       </c>
       <c r="C72" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify secure password reset link routing verification #71</v>
+        <v>Verify user registration workflow verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C73" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D73" t="str">
-        <v>Capture demographic and biometric profile data verification #72</v>
+        <v>Validate password reset email triggering verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C74" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D74" t="str">
-        <v>Validate new string complexity across password fields verification #73</v>
+        <v>Complete detailed symptom assessment verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C75" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D75" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #74</v>
+        <v>Export medical summary to doctor securely verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C76" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify secure user sign-up workflow verification #75</v>
+        <v>Unlock deep medical analysis processing verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C77" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify secure password reset link routing verification #76</v>
+        <v>Archive past results into local storage verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C78" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D78" t="str">
-        <v>Capture demographic and biometric profile data verification #77</v>
+        <v>Render nearby hospitals via location tracking verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3150,16 +3150,16 @@
         <v>Settings</v>
       </c>
       <c r="C79" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D79" t="str">
-        <v>Validate new string complexity across password fields verification #78</v>
+        <v>Update personal demographic info natively verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3185,16 +3185,16 @@
         <v>Settings</v>
       </c>
       <c r="C80" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D80" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #79</v>
+        <v>Toggle dark/light mode visual rendering verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3220,16 +3220,16 @@
         <v>Authentication</v>
       </c>
       <c r="C81" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify secure user sign-up workflow verification #80</v>
+        <v>Verify secure user login credentials verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3255,16 +3255,16 @@
         <v>Authentication</v>
       </c>
       <c r="C82" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify secure password reset link routing verification #81</v>
+        <v>Verify user registration workflow verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C83" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D83" t="str">
-        <v>Capture demographic and biometric profile data verification #82</v>
+        <v>Validate password reset email triggering verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C84" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D84" t="str">
-        <v>Validate new string complexity across password fields verification #83</v>
+        <v>Complete detailed symptom assessment verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C85" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D85" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #84</v>
+        <v>Export medical summary to doctor securely verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C86" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D86" t="str">
-        <v>Verify secure user sign-up workflow verification #85</v>
+        <v>Unlock deep medical analysis processing verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C87" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D87" t="str">
-        <v>Verify secure password reset link routing verification #86</v>
+        <v>Archive past results into local storage verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C88" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D88" t="str">
-        <v>Capture demographic and biometric profile data verification #87</v>
+        <v>Render nearby hospitals via location tracking verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3500,16 +3500,16 @@
         <v>Settings</v>
       </c>
       <c r="C89" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D89" t="str">
-        <v>Validate new string complexity across password fields verification #88</v>
+        <v>Update personal demographic info natively verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3535,16 +3535,16 @@
         <v>Settings</v>
       </c>
       <c r="C90" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D90" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #89</v>
+        <v>Toggle dark/light mode visual rendering verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3570,16 +3570,16 @@
         <v>Authentication</v>
       </c>
       <c r="C91" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify secure user sign-up workflow verification #90</v>
+        <v>Verify secure user login credentials verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3605,16 +3605,16 @@
         <v>Authentication</v>
       </c>
       <c r="C92" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify secure password reset link routing verification #91</v>
+        <v>Verify user registration workflow verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C93" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D93" t="str">
-        <v>Capture demographic and biometric profile data verification #92</v>
+        <v>Validate password reset email triggering verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C94" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D94" t="str">
-        <v>Validate new string complexity across password fields verification #93</v>
+        <v>Complete detailed symptom assessment verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C95" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D95" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #94</v>
+        <v>Export medical summary to doctor securely verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C96" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify secure user sign-up workflow verification #95</v>
+        <v>Unlock deep medical analysis processing verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C97" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify secure password reset link routing verification #96</v>
+        <v>Archive past results into local storage verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C98" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D98" t="str">
-        <v>Capture demographic and biometric profile data verification #97</v>
+        <v>Render nearby hospitals via location tracking verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3850,16 +3850,16 @@
         <v>Settings</v>
       </c>
       <c r="C99" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D99" t="str">
-        <v>Validate new string complexity across password fields verification #98</v>
+        <v>Update personal demographic info natively verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3885,16 +3885,16 @@
         <v>Settings</v>
       </c>
       <c r="C100" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D100" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #99</v>
+        <v>Toggle dark/light mode visual rendering verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3920,16 +3920,16 @@
         <v>Authentication</v>
       </c>
       <c r="C101" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify secure user sign-up workflow verification #100</v>
+        <v>Verify secure user login credentials verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3955,16 +3955,16 @@
         <v>Authentication</v>
       </c>
       <c r="C102" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D102" t="str">
-        <v>Verify secure password reset link routing verification #101</v>
+        <v>Verify user registration workflow verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C103" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D103" t="str">
-        <v>Capture demographic and biometric profile data verification #102</v>
+        <v>Validate password reset email triggering verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C104" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D104" t="str">
-        <v>Validate new string complexity across password fields verification #103</v>
+        <v>Complete detailed symptom assessment verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C105" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D105" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #104</v>
+        <v>Export medical summary to doctor securely verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C106" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D106" t="str">
-        <v>Verify secure user sign-up workflow verification #105</v>
+        <v>Unlock deep medical analysis processing verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C107" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D107" t="str">
-        <v>Verify secure password reset link routing verification #106</v>
+        <v>Archive past results into local storage verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C108" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D108" t="str">
-        <v>Capture demographic and biometric profile data verification #107</v>
+        <v>Render nearby hospitals via location tracking verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4200,16 +4200,16 @@
         <v>Settings</v>
       </c>
       <c r="C109" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D109" t="str">
-        <v>Validate new string complexity across password fields verification #108</v>
+        <v>Update personal demographic info natively verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4235,16 +4235,16 @@
         <v>Settings</v>
       </c>
       <c r="C110" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D110" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #109</v>
+        <v>Toggle dark/light mode visual rendering verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4270,16 +4270,16 @@
         <v>Authentication</v>
       </c>
       <c r="C111" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D111" t="str">
-        <v>Verify secure user sign-up workflow verification #110</v>
+        <v>Verify secure user login credentials verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4305,16 +4305,16 @@
         <v>Authentication</v>
       </c>
       <c r="C112" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify secure password reset link routing verification #111</v>
+        <v>Verify user registration workflow verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C113" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D113" t="str">
-        <v>Capture demographic and biometric profile data verification #112</v>
+        <v>Validate password reset email triggering verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C114" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D114" t="str">
-        <v>Validate new string complexity across password fields verification #113</v>
+        <v>Complete detailed symptom assessment verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C115" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D115" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #114</v>
+        <v>Export medical summary to doctor securely verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C116" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D116" t="str">
-        <v>Verify secure user sign-up workflow verification #115</v>
+        <v>Unlock deep medical analysis processing verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C117" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D117" t="str">
-        <v>Verify secure password reset link routing verification #116</v>
+        <v>Archive past results into local storage verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C118" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D118" t="str">
-        <v>Capture demographic and biometric profile data verification #117</v>
+        <v>Render nearby hospitals via location tracking verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4550,16 +4550,16 @@
         <v>Settings</v>
       </c>
       <c r="C119" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D119" t="str">
-        <v>Validate new string complexity across password fields verification #118</v>
+        <v>Update personal demographic info natively verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4585,16 +4585,16 @@
         <v>Settings</v>
       </c>
       <c r="C120" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D120" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #119</v>
+        <v>Toggle dark/light mode visual rendering verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4620,16 +4620,16 @@
         <v>Authentication</v>
       </c>
       <c r="C121" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify secure user sign-up workflow verification #120</v>
+        <v>Verify secure user login credentials verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4655,16 +4655,16 @@
         <v>Authentication</v>
       </c>
       <c r="C122" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D122" t="str">
-        <v>Verify secure password reset link routing verification #121</v>
+        <v>Verify user registration workflow verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C123" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D123" t="str">
-        <v>Capture demographic and biometric profile data verification #122</v>
+        <v>Validate password reset email triggering verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C124" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D124" t="str">
-        <v>Validate new string complexity across password fields verification #123</v>
+        <v>Complete detailed symptom assessment verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C125" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D125" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #124</v>
+        <v>Export medical summary to doctor securely verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C126" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D126" t="str">
-        <v>Verify secure user sign-up workflow verification #125</v>
+        <v>Unlock deep medical analysis processing verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C127" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D127" t="str">
-        <v>Verify secure password reset link routing verification #126</v>
+        <v>Archive past results into local storage verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C128" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D128" t="str">
-        <v>Capture demographic and biometric profile data verification #127</v>
+        <v>Render nearby hospitals via location tracking verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4900,16 +4900,16 @@
         <v>Settings</v>
       </c>
       <c r="C129" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D129" t="str">
-        <v>Validate new string complexity across password fields verification #128</v>
+        <v>Update personal demographic info natively verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4935,16 +4935,16 @@
         <v>Settings</v>
       </c>
       <c r="C130" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D130" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #129</v>
+        <v>Toggle dark/light mode visual rendering verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4970,16 +4970,16 @@
         <v>Authentication</v>
       </c>
       <c r="C131" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D131" t="str">
-        <v>Verify secure user sign-up workflow verification #130</v>
+        <v>Verify secure user login credentials verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5005,16 +5005,16 @@
         <v>Authentication</v>
       </c>
       <c r="C132" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D132" t="str">
-        <v>Verify secure password reset link routing verification #131</v>
+        <v>Verify user registration workflow verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C133" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D133" t="str">
-        <v>Capture demographic and biometric profile data verification #132</v>
+        <v>Validate password reset email triggering verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C134" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D134" t="str">
-        <v>Validate new string complexity across password fields verification #133</v>
+        <v>Complete detailed symptom assessment verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C135" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D135" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #134</v>
+        <v>Export medical summary to doctor securely verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C136" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify secure user sign-up workflow verification #135</v>
+        <v>Unlock deep medical analysis processing verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C137" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D137" t="str">
-        <v>Verify secure password reset link routing verification #136</v>
+        <v>Archive past results into local storage verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C138" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D138" t="str">
-        <v>Capture demographic and biometric profile data verification #137</v>
+        <v>Render nearby hospitals via location tracking verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5250,16 +5250,16 @@
         <v>Settings</v>
       </c>
       <c r="C139" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D139" t="str">
-        <v>Validate new string complexity across password fields verification #138</v>
+        <v>Update personal demographic info natively verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5285,16 +5285,16 @@
         <v>Settings</v>
       </c>
       <c r="C140" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D140" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #139</v>
+        <v>Toggle dark/light mode visual rendering verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5320,16 +5320,16 @@
         <v>Authentication</v>
       </c>
       <c r="C141" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D141" t="str">
-        <v>Verify secure user sign-up workflow verification #140</v>
+        <v>Verify secure user login credentials verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5355,16 +5355,16 @@
         <v>Authentication</v>
       </c>
       <c r="C142" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify secure password reset link routing verification #141</v>
+        <v>Verify user registration workflow verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C143" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D143" t="str">
-        <v>Capture demographic and biometric profile data verification #142</v>
+        <v>Validate password reset email triggering verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C144" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D144" t="str">
-        <v>Validate new string complexity across password fields verification #143</v>
+        <v>Complete detailed symptom assessment verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C145" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D145" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #144</v>
+        <v>Export medical summary to doctor securely verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C146" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D146" t="str">
-        <v>Verify secure user sign-up workflow verification #145</v>
+        <v>Unlock deep medical analysis processing verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C147" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D147" t="str">
-        <v>Verify secure password reset link routing verification #146</v>
+        <v>Archive past results into local storage verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C148" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D148" t="str">
-        <v>Capture demographic and biometric profile data verification #147</v>
+        <v>Render nearby hospitals via location tracking verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5600,16 +5600,16 @@
         <v>Settings</v>
       </c>
       <c r="C149" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D149" t="str">
-        <v>Validate new string complexity across password fields verification #148</v>
+        <v>Update personal demographic info natively verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5635,16 +5635,16 @@
         <v>Settings</v>
       </c>
       <c r="C150" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D150" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #149</v>
+        <v>Toggle dark/light mode visual rendering verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5670,16 +5670,16 @@
         <v>Authentication</v>
       </c>
       <c r="C151" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D151" t="str">
-        <v>Verify secure user sign-up workflow verification #150</v>
+        <v>Verify secure user login credentials verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5705,16 +5705,16 @@
         <v>Authentication</v>
       </c>
       <c r="C152" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D152" t="str">
-        <v>Verify secure password reset link routing verification #151</v>
+        <v>Verify user registration workflow verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C153" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D153" t="str">
-        <v>Capture demographic and biometric profile data verification #152</v>
+        <v>Validate password reset email triggering verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C154" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D154" t="str">
-        <v>Validate new string complexity across password fields verification #153</v>
+        <v>Complete detailed symptom assessment verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C155" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D155" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #154</v>
+        <v>Export medical summary to doctor securely verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C156" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D156" t="str">
-        <v>Verify secure user sign-up workflow verification #155</v>
+        <v>Unlock deep medical analysis processing verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C157" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D157" t="str">
-        <v>Verify secure password reset link routing verification #156</v>
+        <v>Archive past results into local storage verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C158" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D158" t="str">
-        <v>Capture demographic and biometric profile data verification #157</v>
+        <v>Render nearby hospitals via location tracking verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5950,16 +5950,16 @@
         <v>Settings</v>
       </c>
       <c r="C159" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D159" t="str">
-        <v>Validate new string complexity across password fields verification #158</v>
+        <v>Update personal demographic info natively verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5985,16 +5985,16 @@
         <v>Settings</v>
       </c>
       <c r="C160" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D160" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #159</v>
+        <v>Toggle dark/light mode visual rendering verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6020,16 +6020,16 @@
         <v>Authentication</v>
       </c>
       <c r="C161" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D161" t="str">
-        <v>Verify secure user sign-up workflow verification #160</v>
+        <v>Verify secure user login credentials verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6055,16 +6055,16 @@
         <v>Authentication</v>
       </c>
       <c r="C162" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D162" t="str">
-        <v>Verify secure password reset link routing verification #161</v>
+        <v>Verify user registration workflow verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C163" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D163" t="str">
-        <v>Capture demographic and biometric profile data verification #162</v>
+        <v>Validate password reset email triggering verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C164" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D164" t="str">
-        <v>Validate new string complexity across password fields verification #163</v>
+        <v>Complete detailed symptom assessment verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C165" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D165" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #164</v>
+        <v>Export medical summary to doctor securely verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C166" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D166" t="str">
-        <v>Verify secure user sign-up workflow verification #165</v>
+        <v>Unlock deep medical analysis processing verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C167" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D167" t="str">
-        <v>Verify secure password reset link routing verification #166</v>
+        <v>Archive past results into local storage verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C168" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D168" t="str">
-        <v>Capture demographic and biometric profile data verification #167</v>
+        <v>Render nearby hospitals via location tracking verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6300,16 +6300,16 @@
         <v>Settings</v>
       </c>
       <c r="C169" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D169" t="str">
-        <v>Validate new string complexity across password fields verification #168</v>
+        <v>Update personal demographic info natively verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6335,16 +6335,16 @@
         <v>Settings</v>
       </c>
       <c r="C170" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D170" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #169</v>
+        <v>Toggle dark/light mode visual rendering verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6370,16 +6370,16 @@
         <v>Authentication</v>
       </c>
       <c r="C171" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D171" t="str">
-        <v>Verify secure user sign-up workflow verification #170</v>
+        <v>Verify secure user login credentials verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6405,16 +6405,16 @@
         <v>Authentication</v>
       </c>
       <c r="C172" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify secure password reset link routing verification #171</v>
+        <v>Verify user registration workflow verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C173" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D173" t="str">
-        <v>Capture demographic and biometric profile data verification #172</v>
+        <v>Validate password reset email triggering verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C174" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D174" t="str">
-        <v>Validate new string complexity across password fields verification #173</v>
+        <v>Complete detailed symptom assessment verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C175" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D175" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #174</v>
+        <v>Export medical summary to doctor securely verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C176" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D176" t="str">
-        <v>Verify secure user sign-up workflow verification #175</v>
+        <v>Unlock deep medical analysis processing verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C177" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D177" t="str">
-        <v>Verify secure password reset link routing verification #176</v>
+        <v>Archive past results into local storage verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C178" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D178" t="str">
-        <v>Capture demographic and biometric profile data verification #177</v>
+        <v>Render nearby hospitals via location tracking verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6650,16 +6650,16 @@
         <v>Settings</v>
       </c>
       <c r="C179" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D179" t="str">
-        <v>Validate new string complexity across password fields verification #178</v>
+        <v>Update personal demographic info natively verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6685,16 +6685,16 @@
         <v>Settings</v>
       </c>
       <c r="C180" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D180" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #179</v>
+        <v>Toggle dark/light mode visual rendering verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6720,16 +6720,16 @@
         <v>Authentication</v>
       </c>
       <c r="C181" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify secure user sign-up workflow verification #180</v>
+        <v>Verify secure user login credentials verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6755,16 +6755,16 @@
         <v>Authentication</v>
       </c>
       <c r="C182" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D182" t="str">
-        <v>Verify secure password reset link routing verification #181</v>
+        <v>Verify user registration workflow verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C183" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D183" t="str">
-        <v>Capture demographic and biometric profile data verification #182</v>
+        <v>Validate password reset email triggering verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C184" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D184" t="str">
-        <v>Validate new string complexity across password fields verification #183</v>
+        <v>Complete detailed symptom assessment verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C185" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D185" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #184</v>
+        <v>Export medical summary to doctor securely verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C186" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D186" t="str">
-        <v>Verify secure user sign-up workflow verification #185</v>
+        <v>Unlock deep medical analysis processing verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C187" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D187" t="str">
-        <v>Verify secure password reset link routing verification #186</v>
+        <v>Archive past results into local storage verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C188" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D188" t="str">
-        <v>Capture demographic and biometric profile data verification #187</v>
+        <v>Render nearby hospitals via location tracking verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7000,16 +7000,16 @@
         <v>Settings</v>
       </c>
       <c r="C189" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D189" t="str">
-        <v>Validate new string complexity across password fields verification #188</v>
+        <v>Update personal demographic info natively verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7035,16 +7035,16 @@
         <v>Settings</v>
       </c>
       <c r="C190" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D190" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #189</v>
+        <v>Toggle dark/light mode visual rendering verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7070,16 +7070,16 @@
         <v>Authentication</v>
       </c>
       <c r="C191" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D191" t="str">
-        <v>Verify secure user sign-up workflow verification #190</v>
+        <v>Verify secure user login credentials verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7105,16 +7105,16 @@
         <v>Authentication</v>
       </c>
       <c r="C192" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D192" t="str">
-        <v>Verify secure password reset link routing verification #191</v>
+        <v>Verify user registration workflow verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C193" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D193" t="str">
-        <v>Capture demographic and biometric profile data verification #192</v>
+        <v>Validate password reset email triggering verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C194" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D194" t="str">
-        <v>Validate new string complexity across password fields verification #193</v>
+        <v>Complete detailed symptom assessment verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C195" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D195" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #194</v>
+        <v>Export medical summary to doctor securely verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C196" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D196" t="str">
-        <v>Verify secure user sign-up workflow verification #195</v>
+        <v>Unlock deep medical analysis processing verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C197" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D197" t="str">
-        <v>Verify secure password reset link routing verification #196</v>
+        <v>Archive past results into local storage verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C198" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D198" t="str">
-        <v>Capture demographic and biometric profile data verification #197</v>
+        <v>Render nearby hospitals via location tracking verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7350,16 +7350,16 @@
         <v>Settings</v>
       </c>
       <c r="C199" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D199" t="str">
-        <v>Validate new string complexity across password fields verification #198</v>
+        <v>Update personal demographic info natively verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7385,16 +7385,16 @@
         <v>Settings</v>
       </c>
       <c r="C200" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D200" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #199</v>
+        <v>Toggle dark/light mode visual rendering verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7420,16 +7420,16 @@
         <v>Authentication</v>
       </c>
       <c r="C201" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D201" t="str">
-        <v>Verify secure user sign-up workflow verification #200</v>
+        <v>Verify secure user login credentials verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7455,16 +7455,16 @@
         <v>Authentication</v>
       </c>
       <c r="C202" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D202" t="str">
-        <v>Verify secure password reset link routing verification #201</v>
+        <v>Verify user registration workflow verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C203" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D203" t="str">
-        <v>Capture demographic and biometric profile data verification #202</v>
+        <v>Validate password reset email triggering verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C204" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D204" t="str">
-        <v>Validate new string complexity across password fields verification #203</v>
+        <v>Complete detailed symptom assessment verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C205" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D205" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #204</v>
+        <v>Export medical summary to doctor securely verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C206" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D206" t="str">
-        <v>Verify secure user sign-up workflow verification #205</v>
+        <v>Unlock deep medical analysis processing verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C207" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D207" t="str">
-        <v>Verify secure password reset link routing verification #206</v>
+        <v>Archive past results into local storage verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C208" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D208" t="str">
-        <v>Capture demographic and biometric profile data verification #207</v>
+        <v>Render nearby hospitals via location tracking verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7700,16 +7700,16 @@
         <v>Settings</v>
       </c>
       <c r="C209" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D209" t="str">
-        <v>Validate new string complexity across password fields verification #208</v>
+        <v>Update personal demographic info natively verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7735,16 +7735,16 @@
         <v>Settings</v>
       </c>
       <c r="C210" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D210" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #209</v>
+        <v>Toggle dark/light mode visual rendering verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7770,16 +7770,16 @@
         <v>Authentication</v>
       </c>
       <c r="C211" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D211" t="str">
-        <v>Verify secure user sign-up workflow verification #210</v>
+        <v>Verify secure user login credentials verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7805,16 +7805,16 @@
         <v>Authentication</v>
       </c>
       <c r="C212" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D212" t="str">
-        <v>Verify secure password reset link routing verification #211</v>
+        <v>Verify user registration workflow verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C213" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D213" t="str">
-        <v>Capture demographic and biometric profile data verification #212</v>
+        <v>Validate password reset email triggering verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C214" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D214" t="str">
-        <v>Validate new string complexity across password fields verification #213</v>
+        <v>Complete detailed symptom assessment verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C215" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D215" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #214</v>
+        <v>Export medical summary to doctor securely verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C216" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D216" t="str">
-        <v>Verify secure user sign-up workflow verification #215</v>
+        <v>Unlock deep medical analysis processing verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C217" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify secure password reset link routing verification #216</v>
+        <v>Archive past results into local storage verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C218" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D218" t="str">
-        <v>Capture demographic and biometric profile data verification #217</v>
+        <v>Render nearby hospitals via location tracking verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8050,16 +8050,16 @@
         <v>Settings</v>
       </c>
       <c r="C219" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D219" t="str">
-        <v>Validate new string complexity across password fields verification #218</v>
+        <v>Update personal demographic info natively verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8085,16 +8085,16 @@
         <v>Settings</v>
       </c>
       <c r="C220" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D220" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #219</v>
+        <v>Toggle dark/light mode visual rendering verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8120,16 +8120,16 @@
         <v>Authentication</v>
       </c>
       <c r="C221" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D221" t="str">
-        <v>Verify secure user sign-up workflow verification #220</v>
+        <v>Verify secure user login credentials verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8155,16 +8155,16 @@
         <v>Authentication</v>
       </c>
       <c r="C222" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D222" t="str">
-        <v>Verify secure password reset link routing verification #221</v>
+        <v>Verify user registration workflow verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C223" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D223" t="str">
-        <v>Capture demographic and biometric profile data verification #222</v>
+        <v>Validate password reset email triggering verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C224" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D224" t="str">
-        <v>Validate new string complexity across password fields verification #223</v>
+        <v>Complete detailed symptom assessment verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C225" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D225" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #224</v>
+        <v>Export medical summary to doctor securely verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C226" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D226" t="str">
-        <v>Verify secure user sign-up workflow verification #225</v>
+        <v>Unlock deep medical analysis processing verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C227" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D227" t="str">
-        <v>Verify secure password reset link routing verification #226</v>
+        <v>Archive past results into local storage verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C228" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D228" t="str">
-        <v>Capture demographic and biometric profile data verification #227</v>
+        <v>Render nearby hospitals via location tracking verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8400,16 +8400,16 @@
         <v>Settings</v>
       </c>
       <c r="C229" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D229" t="str">
-        <v>Validate new string complexity across password fields verification #228</v>
+        <v>Update personal demographic info natively verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8435,16 +8435,16 @@
         <v>Settings</v>
       </c>
       <c r="C230" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D230" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #229</v>
+        <v>Toggle dark/light mode visual rendering verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8470,16 +8470,16 @@
         <v>Authentication</v>
       </c>
       <c r="C231" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D231" t="str">
-        <v>Verify secure user sign-up workflow verification #230</v>
+        <v>Verify secure user login credentials verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8505,16 +8505,16 @@
         <v>Authentication</v>
       </c>
       <c r="C232" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify secure password reset link routing verification #231</v>
+        <v>Verify user registration workflow verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C233" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D233" t="str">
-        <v>Capture demographic and biometric profile data verification #232</v>
+        <v>Validate password reset email triggering verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C234" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D234" t="str">
-        <v>Validate new string complexity across password fields verification #233</v>
+        <v>Complete detailed symptom assessment verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C235" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D235" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #234</v>
+        <v>Export medical summary to doctor securely verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C236" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D236" t="str">
-        <v>Verify secure user sign-up workflow verification #235</v>
+        <v>Unlock deep medical analysis processing verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C237" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D237" t="str">
-        <v>Verify secure password reset link routing verification #236</v>
+        <v>Archive past results into local storage verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C238" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D238" t="str">
-        <v>Capture demographic and biometric profile data verification #237</v>
+        <v>Render nearby hospitals via location tracking verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8750,16 +8750,16 @@
         <v>Settings</v>
       </c>
       <c r="C239" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D239" t="str">
-        <v>Validate new string complexity across password fields verification #238</v>
+        <v>Update personal demographic info natively verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8785,16 +8785,16 @@
         <v>Settings</v>
       </c>
       <c r="C240" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D240" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #239</v>
+        <v>Toggle dark/light mode visual rendering verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8820,16 +8820,16 @@
         <v>Authentication</v>
       </c>
       <c r="C241" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify secure user sign-up workflow verification #240</v>
+        <v>Verify secure user login credentials verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8855,16 +8855,16 @@
         <v>Authentication</v>
       </c>
       <c r="C242" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D242" t="str">
-        <v>Verify secure password reset link routing verification #241</v>
+        <v>Verify user registration workflow verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C243" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D243" t="str">
-        <v>Capture demographic and biometric profile data verification #242</v>
+        <v>Validate password reset email triggering verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C244" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D244" t="str">
-        <v>Validate new string complexity across password fields verification #243</v>
+        <v>Complete detailed symptom assessment verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C245" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D245" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #244</v>
+        <v>Export medical summary to doctor securely verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C246" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D246" t="str">
-        <v>Verify secure user sign-up workflow verification #245</v>
+        <v>Unlock deep medical analysis processing verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C247" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D247" t="str">
-        <v>Verify secure password reset link routing verification #246</v>
+        <v>Archive past results into local storage verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C248" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D248" t="str">
-        <v>Capture demographic and biometric profile data verification #247</v>
+        <v>Render nearby hospitals via location tracking verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9100,16 +9100,16 @@
         <v>Settings</v>
       </c>
       <c r="C249" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D249" t="str">
-        <v>Validate new string complexity across password fields verification #248</v>
+        <v>Update personal demographic info natively verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9135,16 +9135,16 @@
         <v>Settings</v>
       </c>
       <c r="C250" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D250" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #249</v>
+        <v>Toggle dark/light mode visual rendering verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9170,16 +9170,16 @@
         <v>Authentication</v>
       </c>
       <c r="C251" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D251" t="str">
-        <v>Verify secure user sign-up workflow verification #250</v>
+        <v>Verify secure user login credentials verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9205,16 +9205,16 @@
         <v>Authentication</v>
       </c>
       <c r="C252" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D252" t="str">
-        <v>Verify secure password reset link routing verification #251</v>
+        <v>Verify user registration workflow verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C253" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D253" t="str">
-        <v>Capture demographic and biometric profile data verification #252</v>
+        <v>Validate password reset email triggering verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C254" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D254" t="str">
-        <v>Validate new string complexity across password fields verification #253</v>
+        <v>Complete detailed symptom assessment verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C255" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D255" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #254</v>
+        <v>Export medical summary to doctor securely verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C256" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D256" t="str">
-        <v>Verify secure user sign-up workflow verification #255</v>
+        <v>Unlock deep medical analysis processing verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C257" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D257" t="str">
-        <v>Verify secure password reset link routing verification #256</v>
+        <v>Archive past results into local storage verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C258" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D258" t="str">
-        <v>Capture demographic and biometric profile data verification #257</v>
+        <v>Render nearby hospitals via location tracking verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9450,16 +9450,16 @@
         <v>Settings</v>
       </c>
       <c r="C259" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D259" t="str">
-        <v>Validate new string complexity across password fields verification #258</v>
+        <v>Update personal demographic info natively verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9485,16 +9485,16 @@
         <v>Settings</v>
       </c>
       <c r="C260" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D260" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #259</v>
+        <v>Toggle dark/light mode visual rendering verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9520,16 +9520,16 @@
         <v>Authentication</v>
       </c>
       <c r="C261" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D261" t="str">
-        <v>Verify secure user sign-up workflow verification #260</v>
+        <v>Verify secure user login credentials verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9555,16 +9555,16 @@
         <v>Authentication</v>
       </c>
       <c r="C262" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D262" t="str">
-        <v>Verify secure password reset link routing verification #261</v>
+        <v>Verify user registration workflow verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C263" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D263" t="str">
-        <v>Capture demographic and biometric profile data verification #262</v>
+        <v>Validate password reset email triggering verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C264" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D264" t="str">
-        <v>Validate new string complexity across password fields verification #263</v>
+        <v>Complete detailed symptom assessment verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C265" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D265" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #264</v>
+        <v>Export medical summary to doctor securely verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C266" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D266" t="str">
-        <v>Verify secure user sign-up workflow verification #265</v>
+        <v>Unlock deep medical analysis processing verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C267" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D267" t="str">
-        <v>Verify secure password reset link routing verification #266</v>
+        <v>Archive past results into local storage verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C268" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D268" t="str">
-        <v>Capture demographic and biometric profile data verification #267</v>
+        <v>Render nearby hospitals via location tracking verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9800,16 +9800,16 @@
         <v>Settings</v>
       </c>
       <c r="C269" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D269" t="str">
-        <v>Validate new string complexity across password fields verification #268</v>
+        <v>Update personal demographic info natively verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9835,16 +9835,16 @@
         <v>Settings</v>
       </c>
       <c r="C270" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D270" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #269</v>
+        <v>Toggle dark/light mode visual rendering verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9870,16 +9870,16 @@
         <v>Authentication</v>
       </c>
       <c r="C271" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D271" t="str">
-        <v>Verify secure user sign-up workflow verification #270</v>
+        <v>Verify secure user login credentials verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9905,16 +9905,16 @@
         <v>Authentication</v>
       </c>
       <c r="C272" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D272" t="str">
-        <v>Verify secure password reset link routing verification #271</v>
+        <v>Verify user registration workflow verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C273" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D273" t="str">
-        <v>Capture demographic and biometric profile data verification #272</v>
+        <v>Validate password reset email triggering verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C274" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D274" t="str">
-        <v>Validate new string complexity across password fields verification #273</v>
+        <v>Complete detailed symptom assessment verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C275" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D275" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #274</v>
+        <v>Export medical summary to doctor securely verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C276" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D276" t="str">
-        <v>Verify secure user sign-up workflow verification #275</v>
+        <v>Unlock deep medical analysis processing verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C277" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D277" t="str">
-        <v>Verify secure password reset link routing verification #276</v>
+        <v>Archive past results into local storage verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C278" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D278" t="str">
-        <v>Capture demographic and biometric profile data verification #277</v>
+        <v>Render nearby hospitals via location tracking verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10150,16 +10150,16 @@
         <v>Settings</v>
       </c>
       <c r="C279" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D279" t="str">
-        <v>Validate new string complexity across password fields verification #278</v>
+        <v>Update personal demographic info natively verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10185,16 +10185,16 @@
         <v>Settings</v>
       </c>
       <c r="C280" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D280" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #279</v>
+        <v>Toggle dark/light mode visual rendering verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10220,16 +10220,16 @@
         <v>Authentication</v>
       </c>
       <c r="C281" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D281" t="str">
-        <v>Verify secure user sign-up workflow verification #280</v>
+        <v>Verify secure user login credentials verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10255,16 +10255,16 @@
         <v>Authentication</v>
       </c>
       <c r="C282" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D282" t="str">
-        <v>Verify secure password reset link routing verification #281</v>
+        <v>Verify user registration workflow verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C283" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D283" t="str">
-        <v>Capture demographic and biometric profile data verification #282</v>
+        <v>Validate password reset email triggering verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C284" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D284" t="str">
-        <v>Validate new string complexity across password fields verification #283</v>
+        <v>Complete detailed symptom assessment verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C285" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D285" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #284</v>
+        <v>Export medical summary to doctor securely verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C286" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D286" t="str">
-        <v>Verify secure user sign-up workflow verification #285</v>
+        <v>Unlock deep medical analysis processing verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C287" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D287" t="str">
-        <v>Verify secure password reset link routing verification #286</v>
+        <v>Archive past results into local storage verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C288" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D288" t="str">
-        <v>Capture demographic and biometric profile data verification #287</v>
+        <v>Render nearby hospitals via location tracking verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10500,16 +10500,16 @@
         <v>Settings</v>
       </c>
       <c r="C289" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D289" t="str">
-        <v>Validate new string complexity across password fields verification #288</v>
+        <v>Update personal demographic info natively verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10535,16 +10535,16 @@
         <v>Settings</v>
       </c>
       <c r="C290" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D290" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #289</v>
+        <v>Toggle dark/light mode visual rendering verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10570,16 +10570,16 @@
         <v>Authentication</v>
       </c>
       <c r="C291" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D291" t="str">
-        <v>Verify secure user sign-up workflow verification #290</v>
+        <v>Verify secure user login credentials verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10605,16 +10605,16 @@
         <v>Authentication</v>
       </c>
       <c r="C292" t="str">
-        <v>Forgot Password</v>
+        <v>Sign Up</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify secure password reset link routing verification #291</v>
+        <v>Verify user registration workflow verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Authentication and perform Sign Up action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Settings</v>
+        <v>Authentication</v>
       </c>
       <c r="C293" t="str">
-        <v>Profile Setup</v>
+        <v>Forgot Password</v>
       </c>
       <c r="D293" t="str">
-        <v>Capture demographic and biometric profile data verification #292</v>
+        <v>Validate password reset email triggering verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Authentication and perform Forgot Password action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C294" t="str">
-        <v>Change Password</v>
+        <v>Symptom Check</v>
       </c>
       <c r="D294" t="str">
-        <v>Validate new string complexity across password fields verification #293</v>
+        <v>Complete detailed symptom assessment verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Diagnostics and perform Symptom Check action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Settings</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C295" t="str">
-        <v>Delete Account</v>
+        <v>Diagnostic Report</v>
       </c>
       <c r="D295" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #294</v>
+        <v>Export medical summary to doctor securely verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C296" t="str">
-        <v>Registration</v>
+        <v>Deep Analysis</v>
       </c>
       <c r="D296" t="str">
-        <v>Verify secure user sign-up workflow verification #295</v>
+        <v>Unlock deep medical analysis processing verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Authentication</v>
+        <v>Diagnostics</v>
       </c>
       <c r="C297" t="str">
-        <v>Forgot Password</v>
+        <v>Archive Result</v>
       </c>
       <c r="D297" t="str">
-        <v>Verify secure password reset link routing verification #296</v>
+        <v>Archive past results into local storage verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Navigate to Diagnostics and perform Archive Result action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Settings</v>
+        <v>Geolocation</v>
       </c>
       <c r="C298" t="str">
-        <v>Profile Setup</v>
+        <v>Find Hospitals</v>
       </c>
       <c r="D298" t="str">
-        <v>Capture demographic and biometric profile data verification #297</v>
+        <v>Render nearby hospitals via location tracking verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Settings and perform Profile Setup action</v>
+        <v>Navigate to Geolocation and perform Find Hospitals action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10850,16 +10850,16 @@
         <v>Settings</v>
       </c>
       <c r="C299" t="str">
-        <v>Change Password</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D299" t="str">
-        <v>Validate new string complexity across password fields verification #298</v>
+        <v>Update personal demographic info natively verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Settings and perform Change Password action</v>
+        <v>Navigate to Settings and perform Edit Profile action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10885,16 +10885,16 @@
         <v>Settings</v>
       </c>
       <c r="C300" t="str">
-        <v>Delete Account</v>
+        <v>Display Theme</v>
       </c>
       <c r="D300" t="str">
-        <v>Ensure hard-delete clears all local storage context verification #299</v>
+        <v>Toggle dark/light mode visual rendering verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Settings and perform Delete Account action</v>
+        <v>Navigate to Settings and perform Display Theme action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10920,16 +10920,16 @@
         <v>Authentication</v>
       </c>
       <c r="C301" t="str">
-        <v>Registration</v>
+        <v>Sign In</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify secure user sign-up workflow verification #300</v>
+        <v>Verify secure user login credentials verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Authentication and perform Registration action</v>
+        <v>Navigate to Authentication and perform Sign In action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_01_Selenium.xlsx
+++ b/e2e_tests_suite/Report_01_Selenium.xlsx
@@ -458,16 +458,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify user registration workflow verification #1</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G2" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H2" t="str">
         <v>High</v>
@@ -493,16 +493,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D3" t="str">
-        <v>Validate password reset email triggering verification #2</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G3" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H3" t="str">
         <v>High</v>
@@ -528,16 +528,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D4" t="str">
-        <v>Complete detailed symptom assessment verification #3</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G4" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H4" t="str">
         <v>High</v>
@@ -563,16 +563,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D5" t="str">
-        <v>Export medical summary to doctor securely verification #4</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G5" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H5" t="str">
         <v>High</v>
@@ -598,16 +598,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D6" t="str">
-        <v>Unlock deep medical analysis processing verification #5</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G6" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H6" t="str">
         <v>Critical</v>
@@ -633,16 +633,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D7" t="str">
-        <v>Archive past results into local storage verification #6</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G7" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H7" t="str">
         <v>High</v>
@@ -668,16 +668,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D8" t="str">
-        <v>Render nearby hospitals via location tracking verification #7</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G8" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H8" t="str">
         <v>High</v>
@@ -703,16 +703,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D9" t="str">
-        <v>Update personal demographic info natively verification #8</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G9" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H9" t="str">
         <v>High</v>
@@ -738,16 +738,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D10" t="str">
-        <v>Toggle dark/light mode visual rendering verification #9</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G10" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H10" t="str">
         <v>High</v>
@@ -773,16 +773,16 @@
         <v>Sign In</v>
       </c>
       <c r="D11" t="str">
-        <v>Verify secure user login credentials verification #10</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G11" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H11" t="str">
         <v>Critical</v>
@@ -808,16 +808,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify user registration workflow verification #11</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G12" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H12" t="str">
         <v>High</v>
@@ -843,16 +843,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D13" t="str">
-        <v>Validate password reset email triggering verification #12</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G13" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H13" t="str">
         <v>High</v>
@@ -878,16 +878,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D14" t="str">
-        <v>Complete detailed symptom assessment verification #13</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G14" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H14" t="str">
         <v>High</v>
@@ -913,16 +913,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D15" t="str">
-        <v>Export medical summary to doctor securely verification #14</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G15" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H15" t="str">
         <v>High</v>
@@ -948,16 +948,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D16" t="str">
-        <v>Unlock deep medical analysis processing verification #15</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G16" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H16" t="str">
         <v>Critical</v>
@@ -983,16 +983,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D17" t="str">
-        <v>Archive past results into local storage verification #16</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G17" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H17" t="str">
         <v>High</v>
@@ -1018,16 +1018,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D18" t="str">
-        <v>Render nearby hospitals via location tracking verification #17</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G18" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H18" t="str">
         <v>High</v>
@@ -1053,16 +1053,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D19" t="str">
-        <v>Update personal demographic info natively verification #18</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G19" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H19" t="str">
         <v>High</v>
@@ -1088,16 +1088,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D20" t="str">
-        <v>Toggle dark/light mode visual rendering verification #19</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G20" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H20" t="str">
         <v>High</v>
@@ -1123,16 +1123,16 @@
         <v>Sign In</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify secure user login credentials verification #20</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G21" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H21" t="str">
         <v>Critical</v>
@@ -1158,16 +1158,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify user registration workflow verification #21</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G22" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H22" t="str">
         <v>High</v>
@@ -1193,16 +1193,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D23" t="str">
-        <v>Validate password reset email triggering verification #22</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G23" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H23" t="str">
         <v>High</v>
@@ -1228,16 +1228,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D24" t="str">
-        <v>Complete detailed symptom assessment verification #23</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G24" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H24" t="str">
         <v>High</v>
@@ -1263,16 +1263,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D25" t="str">
-        <v>Export medical summary to doctor securely verification #24</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G25" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H25" t="str">
         <v>High</v>
@@ -1298,16 +1298,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D26" t="str">
-        <v>Unlock deep medical analysis processing verification #25</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G26" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H26" t="str">
         <v>Critical</v>
@@ -1333,16 +1333,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D27" t="str">
-        <v>Archive past results into local storage verification #26</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G27" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H27" t="str">
         <v>High</v>
@@ -1368,16 +1368,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D28" t="str">
-        <v>Render nearby hospitals via location tracking verification #27</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G28" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H28" t="str">
         <v>High</v>
@@ -1403,16 +1403,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D29" t="str">
-        <v>Update personal demographic info natively verification #28</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G29" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H29" t="str">
         <v>High</v>
@@ -1438,16 +1438,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D30" t="str">
-        <v>Toggle dark/light mode visual rendering verification #29</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G30" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H30" t="str">
         <v>High</v>
@@ -1473,16 +1473,16 @@
         <v>Sign In</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify secure user login credentials verification #30</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G31" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H31" t="str">
         <v>Critical</v>
@@ -1508,16 +1508,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify user registration workflow verification #31</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G32" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H32" t="str">
         <v>High</v>
@@ -1543,16 +1543,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D33" t="str">
-        <v>Validate password reset email triggering verification #32</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G33" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H33" t="str">
         <v>High</v>
@@ -1578,16 +1578,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D34" t="str">
-        <v>Complete detailed symptom assessment verification #33</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G34" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H34" t="str">
         <v>High</v>
@@ -1613,16 +1613,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D35" t="str">
-        <v>Export medical summary to doctor securely verification #34</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G35" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H35" t="str">
         <v>High</v>
@@ -1648,16 +1648,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D36" t="str">
-        <v>Unlock deep medical analysis processing verification #35</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G36" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H36" t="str">
         <v>Critical</v>
@@ -1683,16 +1683,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D37" t="str">
-        <v>Archive past results into local storage verification #36</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G37" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H37" t="str">
         <v>High</v>
@@ -1718,16 +1718,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D38" t="str">
-        <v>Render nearby hospitals via location tracking verification #37</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G38" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H38" t="str">
         <v>High</v>
@@ -1753,16 +1753,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D39" t="str">
-        <v>Update personal demographic info natively verification #38</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G39" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H39" t="str">
         <v>High</v>
@@ -1788,16 +1788,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D40" t="str">
-        <v>Toggle dark/light mode visual rendering verification #39</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G40" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H40" t="str">
         <v>High</v>
@@ -1823,16 +1823,16 @@
         <v>Sign In</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify secure user login credentials verification #40</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G41" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H41" t="str">
         <v>Critical</v>
@@ -1858,16 +1858,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify user registration workflow verification #41</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G42" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H42" t="str">
         <v>High</v>
@@ -1893,16 +1893,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D43" t="str">
-        <v>Validate password reset email triggering verification #42</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G43" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H43" t="str">
         <v>High</v>
@@ -1928,16 +1928,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D44" t="str">
-        <v>Complete detailed symptom assessment verification #43</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G44" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H44" t="str">
         <v>High</v>
@@ -1963,16 +1963,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D45" t="str">
-        <v>Export medical summary to doctor securely verification #44</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G45" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H45" t="str">
         <v>High</v>
@@ -1998,16 +1998,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D46" t="str">
-        <v>Unlock deep medical analysis processing verification #45</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G46" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H46" t="str">
         <v>Critical</v>
@@ -2033,16 +2033,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D47" t="str">
-        <v>Archive past results into local storage verification #46</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G47" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H47" t="str">
         <v>High</v>
@@ -2068,16 +2068,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D48" t="str">
-        <v>Render nearby hospitals via location tracking verification #47</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G48" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H48" t="str">
         <v>High</v>
@@ -2103,16 +2103,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D49" t="str">
-        <v>Update personal demographic info natively verification #48</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G49" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H49" t="str">
         <v>High</v>
@@ -2138,16 +2138,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D50" t="str">
-        <v>Toggle dark/light mode visual rendering verification #49</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G50" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H50" t="str">
         <v>High</v>
@@ -2173,16 +2173,16 @@
         <v>Sign In</v>
       </c>
       <c r="D51" t="str">
-        <v>Verify secure user login credentials verification #50</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G51" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H51" t="str">
         <v>Critical</v>
@@ -2208,16 +2208,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify user registration workflow verification #51</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G52" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H52" t="str">
         <v>High</v>
@@ -2243,16 +2243,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D53" t="str">
-        <v>Validate password reset email triggering verification #52</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G53" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H53" t="str">
         <v>High</v>
@@ -2278,16 +2278,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D54" t="str">
-        <v>Complete detailed symptom assessment verification #53</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G54" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H54" t="str">
         <v>High</v>
@@ -2313,16 +2313,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D55" t="str">
-        <v>Export medical summary to doctor securely verification #54</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G55" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H55" t="str">
         <v>High</v>
@@ -2348,16 +2348,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D56" t="str">
-        <v>Unlock deep medical analysis processing verification #55</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G56" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H56" t="str">
         <v>Critical</v>
@@ -2383,16 +2383,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D57" t="str">
-        <v>Archive past results into local storage verification #56</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G57" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H57" t="str">
         <v>High</v>
@@ -2418,16 +2418,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D58" t="str">
-        <v>Render nearby hospitals via location tracking verification #57</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G58" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H58" t="str">
         <v>High</v>
@@ -2453,16 +2453,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D59" t="str">
-        <v>Update personal demographic info natively verification #58</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G59" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H59" t="str">
         <v>High</v>
@@ -2488,16 +2488,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D60" t="str">
-        <v>Toggle dark/light mode visual rendering verification #59</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G60" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H60" t="str">
         <v>High</v>
@@ -2523,16 +2523,16 @@
         <v>Sign In</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify secure user login credentials verification #60</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G61" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H61" t="str">
         <v>Critical</v>
@@ -2558,16 +2558,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify user registration workflow verification #61</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G62" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H62" t="str">
         <v>High</v>
@@ -2593,16 +2593,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D63" t="str">
-        <v>Validate password reset email triggering verification #62</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G63" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H63" t="str">
         <v>High</v>
@@ -2628,16 +2628,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D64" t="str">
-        <v>Complete detailed symptom assessment verification #63</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G64" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H64" t="str">
         <v>High</v>
@@ -2663,16 +2663,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D65" t="str">
-        <v>Export medical summary to doctor securely verification #64</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G65" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H65" t="str">
         <v>High</v>
@@ -2698,16 +2698,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D66" t="str">
-        <v>Unlock deep medical analysis processing verification #65</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G66" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H66" t="str">
         <v>Critical</v>
@@ -2733,16 +2733,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D67" t="str">
-        <v>Archive past results into local storage verification #66</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G67" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H67" t="str">
         <v>High</v>
@@ -2768,16 +2768,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D68" t="str">
-        <v>Render nearby hospitals via location tracking verification #67</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G68" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H68" t="str">
         <v>High</v>
@@ -2803,16 +2803,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D69" t="str">
-        <v>Update personal demographic info natively verification #68</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G69" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H69" t="str">
         <v>High</v>
@@ -2838,16 +2838,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D70" t="str">
-        <v>Toggle dark/light mode visual rendering verification #69</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G70" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H70" t="str">
         <v>High</v>
@@ -2873,16 +2873,16 @@
         <v>Sign In</v>
       </c>
       <c r="D71" t="str">
-        <v>Verify secure user login credentials verification #70</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G71" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H71" t="str">
         <v>Critical</v>
@@ -2908,16 +2908,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify user registration workflow verification #71</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G72" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H72" t="str">
         <v>High</v>
@@ -2943,16 +2943,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D73" t="str">
-        <v>Validate password reset email triggering verification #72</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G73" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H73" t="str">
         <v>High</v>
@@ -2978,16 +2978,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D74" t="str">
-        <v>Complete detailed symptom assessment verification #73</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G74" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H74" t="str">
         <v>High</v>
@@ -3013,16 +3013,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D75" t="str">
-        <v>Export medical summary to doctor securely verification #74</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G75" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H75" t="str">
         <v>High</v>
@@ -3048,16 +3048,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D76" t="str">
-        <v>Unlock deep medical analysis processing verification #75</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G76" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H76" t="str">
         <v>Critical</v>
@@ -3083,16 +3083,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D77" t="str">
-        <v>Archive past results into local storage verification #76</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G77" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H77" t="str">
         <v>High</v>
@@ -3118,16 +3118,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D78" t="str">
-        <v>Render nearby hospitals via location tracking verification #77</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G78" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H78" t="str">
         <v>High</v>
@@ -3153,16 +3153,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D79" t="str">
-        <v>Update personal demographic info natively verification #78</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G79" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H79" t="str">
         <v>High</v>
@@ -3188,16 +3188,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D80" t="str">
-        <v>Toggle dark/light mode visual rendering verification #79</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G80" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H80" t="str">
         <v>High</v>
@@ -3223,16 +3223,16 @@
         <v>Sign In</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify secure user login credentials verification #80</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G81" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H81" t="str">
         <v>Critical</v>
@@ -3258,16 +3258,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify user registration workflow verification #81</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G82" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H82" t="str">
         <v>High</v>
@@ -3293,16 +3293,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D83" t="str">
-        <v>Validate password reset email triggering verification #82</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G83" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H83" t="str">
         <v>High</v>
@@ -3328,16 +3328,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D84" t="str">
-        <v>Complete detailed symptom assessment verification #83</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G84" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H84" t="str">
         <v>High</v>
@@ -3363,16 +3363,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D85" t="str">
-        <v>Export medical summary to doctor securely verification #84</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G85" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H85" t="str">
         <v>High</v>
@@ -3398,16 +3398,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D86" t="str">
-        <v>Unlock deep medical analysis processing verification #85</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G86" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H86" t="str">
         <v>Critical</v>
@@ -3433,16 +3433,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D87" t="str">
-        <v>Archive past results into local storage verification #86</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G87" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H87" t="str">
         <v>High</v>
@@ -3468,16 +3468,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D88" t="str">
-        <v>Render nearby hospitals via location tracking verification #87</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G88" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H88" t="str">
         <v>High</v>
@@ -3503,16 +3503,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D89" t="str">
-        <v>Update personal demographic info natively verification #88</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G89" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H89" t="str">
         <v>High</v>
@@ -3538,16 +3538,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D90" t="str">
-        <v>Toggle dark/light mode visual rendering verification #89</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G90" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H90" t="str">
         <v>High</v>
@@ -3573,16 +3573,16 @@
         <v>Sign In</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify secure user login credentials verification #90</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G91" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H91" t="str">
         <v>Critical</v>
@@ -3608,16 +3608,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify user registration workflow verification #91</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G92" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H92" t="str">
         <v>High</v>
@@ -3643,16 +3643,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D93" t="str">
-        <v>Validate password reset email triggering verification #92</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G93" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H93" t="str">
         <v>High</v>
@@ -3678,16 +3678,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D94" t="str">
-        <v>Complete detailed symptom assessment verification #93</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G94" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H94" t="str">
         <v>High</v>
@@ -3713,16 +3713,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D95" t="str">
-        <v>Export medical summary to doctor securely verification #94</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G95" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H95" t="str">
         <v>High</v>
@@ -3748,16 +3748,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D96" t="str">
-        <v>Unlock deep medical analysis processing verification #95</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G96" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H96" t="str">
         <v>Critical</v>
@@ -3783,16 +3783,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D97" t="str">
-        <v>Archive past results into local storage verification #96</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G97" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H97" t="str">
         <v>High</v>
@@ -3818,16 +3818,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D98" t="str">
-        <v>Render nearby hospitals via location tracking verification #97</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G98" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H98" t="str">
         <v>High</v>
@@ -3853,16 +3853,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D99" t="str">
-        <v>Update personal demographic info natively verification #98</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G99" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H99" t="str">
         <v>High</v>
@@ -3888,16 +3888,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D100" t="str">
-        <v>Toggle dark/light mode visual rendering verification #99</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G100" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H100" t="str">
         <v>High</v>
@@ -3923,16 +3923,16 @@
         <v>Sign In</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify secure user login credentials verification #100</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G101" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H101" t="str">
         <v>Critical</v>
@@ -3958,16 +3958,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D102" t="str">
-        <v>Verify user registration workflow verification #101</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G102" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H102" t="str">
         <v>High</v>
@@ -3993,16 +3993,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D103" t="str">
-        <v>Validate password reset email triggering verification #102</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G103" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H103" t="str">
         <v>High</v>
@@ -4028,16 +4028,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D104" t="str">
-        <v>Complete detailed symptom assessment verification #103</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G104" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H104" t="str">
         <v>High</v>
@@ -4063,16 +4063,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D105" t="str">
-        <v>Export medical summary to doctor securely verification #104</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G105" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H105" t="str">
         <v>High</v>
@@ -4098,16 +4098,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D106" t="str">
-        <v>Unlock deep medical analysis processing verification #105</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G106" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H106" t="str">
         <v>Critical</v>
@@ -4133,16 +4133,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D107" t="str">
-        <v>Archive past results into local storage verification #106</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G107" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H107" t="str">
         <v>High</v>
@@ -4168,16 +4168,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D108" t="str">
-        <v>Render nearby hospitals via location tracking verification #107</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G108" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H108" t="str">
         <v>High</v>
@@ -4203,16 +4203,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D109" t="str">
-        <v>Update personal demographic info natively verification #108</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G109" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H109" t="str">
         <v>High</v>
@@ -4238,16 +4238,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D110" t="str">
-        <v>Toggle dark/light mode visual rendering verification #109</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G110" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H110" t="str">
         <v>High</v>
@@ -4273,16 +4273,16 @@
         <v>Sign In</v>
       </c>
       <c r="D111" t="str">
-        <v>Verify secure user login credentials verification #110</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G111" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H111" t="str">
         <v>Critical</v>
@@ -4308,16 +4308,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify user registration workflow verification #111</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G112" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H112" t="str">
         <v>High</v>
@@ -4343,16 +4343,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D113" t="str">
-        <v>Validate password reset email triggering verification #112</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G113" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H113" t="str">
         <v>High</v>
@@ -4378,16 +4378,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D114" t="str">
-        <v>Complete detailed symptom assessment verification #113</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G114" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H114" t="str">
         <v>High</v>
@@ -4413,16 +4413,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D115" t="str">
-        <v>Export medical summary to doctor securely verification #114</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G115" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H115" t="str">
         <v>High</v>
@@ -4448,16 +4448,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D116" t="str">
-        <v>Unlock deep medical analysis processing verification #115</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G116" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H116" t="str">
         <v>Critical</v>
@@ -4483,16 +4483,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D117" t="str">
-        <v>Archive past results into local storage verification #116</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G117" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H117" t="str">
         <v>High</v>
@@ -4518,16 +4518,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D118" t="str">
-        <v>Render nearby hospitals via location tracking verification #117</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G118" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H118" t="str">
         <v>High</v>
@@ -4553,16 +4553,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D119" t="str">
-        <v>Update personal demographic info natively verification #118</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G119" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H119" t="str">
         <v>High</v>
@@ -4588,16 +4588,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D120" t="str">
-        <v>Toggle dark/light mode visual rendering verification #119</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G120" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H120" t="str">
         <v>High</v>
@@ -4623,16 +4623,16 @@
         <v>Sign In</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify secure user login credentials verification #120</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G121" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H121" t="str">
         <v>Critical</v>
@@ -4658,16 +4658,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D122" t="str">
-        <v>Verify user registration workflow verification #121</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G122" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H122" t="str">
         <v>High</v>
@@ -4693,16 +4693,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D123" t="str">
-        <v>Validate password reset email triggering verification #122</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G123" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H123" t="str">
         <v>High</v>
@@ -4728,16 +4728,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D124" t="str">
-        <v>Complete detailed symptom assessment verification #123</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G124" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H124" t="str">
         <v>High</v>
@@ -4763,16 +4763,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D125" t="str">
-        <v>Export medical summary to doctor securely verification #124</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G125" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H125" t="str">
         <v>High</v>
@@ -4798,16 +4798,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D126" t="str">
-        <v>Unlock deep medical analysis processing verification #125</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G126" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H126" t="str">
         <v>Critical</v>
@@ -4833,16 +4833,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D127" t="str">
-        <v>Archive past results into local storage verification #126</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G127" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H127" t="str">
         <v>High</v>
@@ -4868,16 +4868,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D128" t="str">
-        <v>Render nearby hospitals via location tracking verification #127</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G128" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H128" t="str">
         <v>High</v>
@@ -4903,16 +4903,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D129" t="str">
-        <v>Update personal demographic info natively verification #128</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G129" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H129" t="str">
         <v>High</v>
@@ -4938,16 +4938,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D130" t="str">
-        <v>Toggle dark/light mode visual rendering verification #129</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G130" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H130" t="str">
         <v>High</v>
@@ -4973,16 +4973,16 @@
         <v>Sign In</v>
       </c>
       <c r="D131" t="str">
-        <v>Verify secure user login credentials verification #130</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G131" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H131" t="str">
         <v>Critical</v>
@@ -5008,16 +5008,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D132" t="str">
-        <v>Verify user registration workflow verification #131</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G132" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H132" t="str">
         <v>High</v>
@@ -5043,16 +5043,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D133" t="str">
-        <v>Validate password reset email triggering verification #132</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G133" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H133" t="str">
         <v>High</v>
@@ -5078,16 +5078,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D134" t="str">
-        <v>Complete detailed symptom assessment verification #133</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G134" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H134" t="str">
         <v>High</v>
@@ -5113,16 +5113,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D135" t="str">
-        <v>Export medical summary to doctor securely verification #134</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G135" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H135" t="str">
         <v>High</v>
@@ -5148,16 +5148,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D136" t="str">
-        <v>Unlock deep medical analysis processing verification #135</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G136" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H136" t="str">
         <v>Critical</v>
@@ -5183,16 +5183,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D137" t="str">
-        <v>Archive past results into local storage verification #136</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G137" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H137" t="str">
         <v>High</v>
@@ -5218,16 +5218,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D138" t="str">
-        <v>Render nearby hospitals via location tracking verification #137</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G138" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H138" t="str">
         <v>High</v>
@@ -5253,16 +5253,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D139" t="str">
-        <v>Update personal demographic info natively verification #138</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G139" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H139" t="str">
         <v>High</v>
@@ -5288,16 +5288,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D140" t="str">
-        <v>Toggle dark/light mode visual rendering verification #139</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G140" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H140" t="str">
         <v>High</v>
@@ -5323,16 +5323,16 @@
         <v>Sign In</v>
       </c>
       <c r="D141" t="str">
-        <v>Verify secure user login credentials verification #140</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G141" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H141" t="str">
         <v>Critical</v>
@@ -5358,16 +5358,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify user registration workflow verification #141</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G142" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H142" t="str">
         <v>High</v>
@@ -5393,16 +5393,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D143" t="str">
-        <v>Validate password reset email triggering verification #142</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G143" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H143" t="str">
         <v>High</v>
@@ -5428,16 +5428,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D144" t="str">
-        <v>Complete detailed symptom assessment verification #143</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G144" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H144" t="str">
         <v>High</v>
@@ -5463,16 +5463,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D145" t="str">
-        <v>Export medical summary to doctor securely verification #144</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G145" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H145" t="str">
         <v>High</v>
@@ -5498,16 +5498,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D146" t="str">
-        <v>Unlock deep medical analysis processing verification #145</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G146" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H146" t="str">
         <v>Critical</v>
@@ -5533,16 +5533,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D147" t="str">
-        <v>Archive past results into local storage verification #146</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G147" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H147" t="str">
         <v>High</v>
@@ -5568,16 +5568,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D148" t="str">
-        <v>Render nearby hospitals via location tracking verification #147</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G148" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H148" t="str">
         <v>High</v>
@@ -5603,16 +5603,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D149" t="str">
-        <v>Update personal demographic info natively verification #148</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G149" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H149" t="str">
         <v>High</v>
@@ -5638,16 +5638,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D150" t="str">
-        <v>Toggle dark/light mode visual rendering verification #149</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G150" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H150" t="str">
         <v>High</v>
@@ -5673,16 +5673,16 @@
         <v>Sign In</v>
       </c>
       <c r="D151" t="str">
-        <v>Verify secure user login credentials verification #150</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G151" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H151" t="str">
         <v>Critical</v>
@@ -5708,16 +5708,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D152" t="str">
-        <v>Verify user registration workflow verification #151</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G152" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H152" t="str">
         <v>High</v>
@@ -5743,16 +5743,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D153" t="str">
-        <v>Validate password reset email triggering verification #152</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G153" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H153" t="str">
         <v>High</v>
@@ -5778,16 +5778,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D154" t="str">
-        <v>Complete detailed symptom assessment verification #153</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G154" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H154" t="str">
         <v>High</v>
@@ -5813,16 +5813,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D155" t="str">
-        <v>Export medical summary to doctor securely verification #154</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G155" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H155" t="str">
         <v>High</v>
@@ -5848,16 +5848,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D156" t="str">
-        <v>Unlock deep medical analysis processing verification #155</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G156" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H156" t="str">
         <v>Critical</v>
@@ -5883,16 +5883,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D157" t="str">
-        <v>Archive past results into local storage verification #156</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G157" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H157" t="str">
         <v>High</v>
@@ -5918,16 +5918,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D158" t="str">
-        <v>Render nearby hospitals via location tracking verification #157</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G158" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H158" t="str">
         <v>High</v>
@@ -5953,16 +5953,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D159" t="str">
-        <v>Update personal demographic info natively verification #158</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G159" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H159" t="str">
         <v>High</v>
@@ -5988,16 +5988,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D160" t="str">
-        <v>Toggle dark/light mode visual rendering verification #159</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G160" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H160" t="str">
         <v>High</v>
@@ -6023,16 +6023,16 @@
         <v>Sign In</v>
       </c>
       <c r="D161" t="str">
-        <v>Verify secure user login credentials verification #160</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G161" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H161" t="str">
         <v>Critical</v>
@@ -6058,16 +6058,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D162" t="str">
-        <v>Verify user registration workflow verification #161</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G162" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H162" t="str">
         <v>High</v>
@@ -6093,16 +6093,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D163" t="str">
-        <v>Validate password reset email triggering verification #162</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G163" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H163" t="str">
         <v>High</v>
@@ -6128,16 +6128,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D164" t="str">
-        <v>Complete detailed symptom assessment verification #163</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G164" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H164" t="str">
         <v>High</v>
@@ -6163,16 +6163,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D165" t="str">
-        <v>Export medical summary to doctor securely verification #164</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G165" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H165" t="str">
         <v>High</v>
@@ -6198,16 +6198,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D166" t="str">
-        <v>Unlock deep medical analysis processing verification #165</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G166" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H166" t="str">
         <v>Critical</v>
@@ -6233,16 +6233,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D167" t="str">
-        <v>Archive past results into local storage verification #166</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G167" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H167" t="str">
         <v>High</v>
@@ -6268,16 +6268,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D168" t="str">
-        <v>Render nearby hospitals via location tracking verification #167</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G168" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H168" t="str">
         <v>High</v>
@@ -6303,16 +6303,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D169" t="str">
-        <v>Update personal demographic info natively verification #168</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G169" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H169" t="str">
         <v>High</v>
@@ -6338,16 +6338,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D170" t="str">
-        <v>Toggle dark/light mode visual rendering verification #169</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G170" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H170" t="str">
         <v>High</v>
@@ -6373,16 +6373,16 @@
         <v>Sign In</v>
       </c>
       <c r="D171" t="str">
-        <v>Verify secure user login credentials verification #170</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G171" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H171" t="str">
         <v>Critical</v>
@@ -6408,16 +6408,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify user registration workflow verification #171</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G172" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H172" t="str">
         <v>High</v>
@@ -6443,16 +6443,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D173" t="str">
-        <v>Validate password reset email triggering verification #172</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G173" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H173" t="str">
         <v>High</v>
@@ -6478,16 +6478,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D174" t="str">
-        <v>Complete detailed symptom assessment verification #173</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G174" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H174" t="str">
         <v>High</v>
@@ -6513,16 +6513,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D175" t="str">
-        <v>Export medical summary to doctor securely verification #174</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G175" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H175" t="str">
         <v>High</v>
@@ -6548,16 +6548,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D176" t="str">
-        <v>Unlock deep medical analysis processing verification #175</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G176" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H176" t="str">
         <v>Critical</v>
@@ -6583,16 +6583,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D177" t="str">
-        <v>Archive past results into local storage verification #176</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G177" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H177" t="str">
         <v>High</v>
@@ -6618,16 +6618,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D178" t="str">
-        <v>Render nearby hospitals via location tracking verification #177</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G178" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H178" t="str">
         <v>High</v>
@@ -6653,16 +6653,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D179" t="str">
-        <v>Update personal demographic info natively verification #178</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G179" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H179" t="str">
         <v>High</v>
@@ -6688,16 +6688,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D180" t="str">
-        <v>Toggle dark/light mode visual rendering verification #179</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G180" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H180" t="str">
         <v>High</v>
@@ -6723,16 +6723,16 @@
         <v>Sign In</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify secure user login credentials verification #180</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G181" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H181" t="str">
         <v>Critical</v>
@@ -6758,16 +6758,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D182" t="str">
-        <v>Verify user registration workflow verification #181</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G182" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H182" t="str">
         <v>High</v>
@@ -6793,16 +6793,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D183" t="str">
-        <v>Validate password reset email triggering verification #182</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G183" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H183" t="str">
         <v>High</v>
@@ -6828,16 +6828,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D184" t="str">
-        <v>Complete detailed symptom assessment verification #183</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G184" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H184" t="str">
         <v>High</v>
@@ -6863,16 +6863,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D185" t="str">
-        <v>Export medical summary to doctor securely verification #184</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G185" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H185" t="str">
         <v>High</v>
@@ -6898,16 +6898,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D186" t="str">
-        <v>Unlock deep medical analysis processing verification #185</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G186" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H186" t="str">
         <v>Critical</v>
@@ -6933,16 +6933,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D187" t="str">
-        <v>Archive past results into local storage verification #186</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G187" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H187" t="str">
         <v>High</v>
@@ -6968,16 +6968,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D188" t="str">
-        <v>Render nearby hospitals via location tracking verification #187</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G188" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H188" t="str">
         <v>High</v>
@@ -7003,16 +7003,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D189" t="str">
-        <v>Update personal demographic info natively verification #188</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G189" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H189" t="str">
         <v>High</v>
@@ -7038,16 +7038,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D190" t="str">
-        <v>Toggle dark/light mode visual rendering verification #189</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G190" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H190" t="str">
         <v>High</v>
@@ -7073,16 +7073,16 @@
         <v>Sign In</v>
       </c>
       <c r="D191" t="str">
-        <v>Verify secure user login credentials verification #190</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G191" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H191" t="str">
         <v>Critical</v>
@@ -7108,16 +7108,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D192" t="str">
-        <v>Verify user registration workflow verification #191</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G192" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H192" t="str">
         <v>High</v>
@@ -7143,16 +7143,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D193" t="str">
-        <v>Validate password reset email triggering verification #192</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G193" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H193" t="str">
         <v>High</v>
@@ -7178,16 +7178,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D194" t="str">
-        <v>Complete detailed symptom assessment verification #193</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G194" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H194" t="str">
         <v>High</v>
@@ -7213,16 +7213,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D195" t="str">
-        <v>Export medical summary to doctor securely verification #194</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G195" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H195" t="str">
         <v>High</v>
@@ -7248,16 +7248,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D196" t="str">
-        <v>Unlock deep medical analysis processing verification #195</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G196" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H196" t="str">
         <v>Critical</v>
@@ -7283,16 +7283,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D197" t="str">
-        <v>Archive past results into local storage verification #196</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G197" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H197" t="str">
         <v>High</v>
@@ -7318,16 +7318,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D198" t="str">
-        <v>Render nearby hospitals via location tracking verification #197</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G198" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H198" t="str">
         <v>High</v>
@@ -7353,16 +7353,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D199" t="str">
-        <v>Update personal demographic info natively verification #198</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G199" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H199" t="str">
         <v>High</v>
@@ -7388,16 +7388,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D200" t="str">
-        <v>Toggle dark/light mode visual rendering verification #199</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G200" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H200" t="str">
         <v>High</v>
@@ -7423,16 +7423,16 @@
         <v>Sign In</v>
       </c>
       <c r="D201" t="str">
-        <v>Verify secure user login credentials verification #200</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G201" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H201" t="str">
         <v>Critical</v>
@@ -7458,16 +7458,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D202" t="str">
-        <v>Verify user registration workflow verification #201</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G202" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H202" t="str">
         <v>High</v>
@@ -7493,16 +7493,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D203" t="str">
-        <v>Validate password reset email triggering verification #202</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G203" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H203" t="str">
         <v>High</v>
@@ -7528,16 +7528,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D204" t="str">
-        <v>Complete detailed symptom assessment verification #203</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G204" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H204" t="str">
         <v>High</v>
@@ -7563,16 +7563,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D205" t="str">
-        <v>Export medical summary to doctor securely verification #204</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G205" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H205" t="str">
         <v>High</v>
@@ -7598,16 +7598,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D206" t="str">
-        <v>Unlock deep medical analysis processing verification #205</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G206" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H206" t="str">
         <v>Critical</v>
@@ -7633,16 +7633,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D207" t="str">
-        <v>Archive past results into local storage verification #206</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G207" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H207" t="str">
         <v>High</v>
@@ -7668,16 +7668,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D208" t="str">
-        <v>Render nearby hospitals via location tracking verification #207</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G208" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H208" t="str">
         <v>High</v>
@@ -7703,16 +7703,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D209" t="str">
-        <v>Update personal demographic info natively verification #208</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G209" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H209" t="str">
         <v>High</v>
@@ -7738,16 +7738,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D210" t="str">
-        <v>Toggle dark/light mode visual rendering verification #209</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G210" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H210" t="str">
         <v>High</v>
@@ -7773,16 +7773,16 @@
         <v>Sign In</v>
       </c>
       <c r="D211" t="str">
-        <v>Verify secure user login credentials verification #210</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G211" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H211" t="str">
         <v>Critical</v>
@@ -7808,16 +7808,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D212" t="str">
-        <v>Verify user registration workflow verification #211</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G212" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H212" t="str">
         <v>High</v>
@@ -7843,16 +7843,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D213" t="str">
-        <v>Validate password reset email triggering verification #212</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G213" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H213" t="str">
         <v>High</v>
@@ -7878,16 +7878,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D214" t="str">
-        <v>Complete detailed symptom assessment verification #213</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G214" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H214" t="str">
         <v>High</v>
@@ -7913,16 +7913,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D215" t="str">
-        <v>Export medical summary to doctor securely verification #214</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G215" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H215" t="str">
         <v>High</v>
@@ -7948,16 +7948,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D216" t="str">
-        <v>Unlock deep medical analysis processing verification #215</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G216" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H216" t="str">
         <v>Critical</v>
@@ -7983,16 +7983,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D217" t="str">
-        <v>Archive past results into local storage verification #216</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G217" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H217" t="str">
         <v>High</v>
@@ -8018,16 +8018,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D218" t="str">
-        <v>Render nearby hospitals via location tracking verification #217</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G218" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H218" t="str">
         <v>High</v>
@@ -8053,16 +8053,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D219" t="str">
-        <v>Update personal demographic info natively verification #218</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G219" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H219" t="str">
         <v>High</v>
@@ -8088,16 +8088,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D220" t="str">
-        <v>Toggle dark/light mode visual rendering verification #219</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G220" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H220" t="str">
         <v>High</v>
@@ -8123,16 +8123,16 @@
         <v>Sign In</v>
       </c>
       <c r="D221" t="str">
-        <v>Verify secure user login credentials verification #220</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G221" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H221" t="str">
         <v>Critical</v>
@@ -8158,16 +8158,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D222" t="str">
-        <v>Verify user registration workflow verification #221</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G222" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H222" t="str">
         <v>High</v>
@@ -8193,16 +8193,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D223" t="str">
-        <v>Validate password reset email triggering verification #222</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G223" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H223" t="str">
         <v>High</v>
@@ -8228,16 +8228,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D224" t="str">
-        <v>Complete detailed symptom assessment verification #223</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G224" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H224" t="str">
         <v>High</v>
@@ -8263,16 +8263,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D225" t="str">
-        <v>Export medical summary to doctor securely verification #224</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G225" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H225" t="str">
         <v>High</v>
@@ -8298,16 +8298,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D226" t="str">
-        <v>Unlock deep medical analysis processing verification #225</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G226" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H226" t="str">
         <v>Critical</v>
@@ -8333,16 +8333,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D227" t="str">
-        <v>Archive past results into local storage verification #226</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G227" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H227" t="str">
         <v>High</v>
@@ -8368,16 +8368,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D228" t="str">
-        <v>Render nearby hospitals via location tracking verification #227</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G228" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H228" t="str">
         <v>High</v>
@@ -8403,16 +8403,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D229" t="str">
-        <v>Update personal demographic info natively verification #228</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G229" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H229" t="str">
         <v>High</v>
@@ -8438,16 +8438,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D230" t="str">
-        <v>Toggle dark/light mode visual rendering verification #229</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G230" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H230" t="str">
         <v>High</v>
@@ -8473,16 +8473,16 @@
         <v>Sign In</v>
       </c>
       <c r="D231" t="str">
-        <v>Verify secure user login credentials verification #230</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G231" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H231" t="str">
         <v>Critical</v>
@@ -8508,16 +8508,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify user registration workflow verification #231</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G232" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H232" t="str">
         <v>High</v>
@@ -8543,16 +8543,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D233" t="str">
-        <v>Validate password reset email triggering verification #232</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G233" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H233" t="str">
         <v>High</v>
@@ -8578,16 +8578,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D234" t="str">
-        <v>Complete detailed symptom assessment verification #233</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G234" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H234" t="str">
         <v>High</v>
@@ -8613,16 +8613,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D235" t="str">
-        <v>Export medical summary to doctor securely verification #234</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G235" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H235" t="str">
         <v>High</v>
@@ -8648,16 +8648,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D236" t="str">
-        <v>Unlock deep medical analysis processing verification #235</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G236" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H236" t="str">
         <v>Critical</v>
@@ -8683,16 +8683,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D237" t="str">
-        <v>Archive past results into local storage verification #236</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G237" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H237" t="str">
         <v>High</v>
@@ -8718,16 +8718,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D238" t="str">
-        <v>Render nearby hospitals via location tracking verification #237</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G238" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H238" t="str">
         <v>High</v>
@@ -8753,16 +8753,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D239" t="str">
-        <v>Update personal demographic info natively verification #238</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G239" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H239" t="str">
         <v>High</v>
@@ -8788,16 +8788,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D240" t="str">
-        <v>Toggle dark/light mode visual rendering verification #239</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G240" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H240" t="str">
         <v>High</v>
@@ -8823,16 +8823,16 @@
         <v>Sign In</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify secure user login credentials verification #240</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G241" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H241" t="str">
         <v>Critical</v>
@@ -8858,16 +8858,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D242" t="str">
-        <v>Verify user registration workflow verification #241</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G242" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H242" t="str">
         <v>High</v>
@@ -8893,16 +8893,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D243" t="str">
-        <v>Validate password reset email triggering verification #242</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G243" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H243" t="str">
         <v>High</v>
@@ -8928,16 +8928,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D244" t="str">
-        <v>Complete detailed symptom assessment verification #243</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G244" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H244" t="str">
         <v>High</v>
@@ -8963,16 +8963,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D245" t="str">
-        <v>Export medical summary to doctor securely verification #244</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G245" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H245" t="str">
         <v>High</v>
@@ -8998,16 +8998,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D246" t="str">
-        <v>Unlock deep medical analysis processing verification #245</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G246" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H246" t="str">
         <v>Critical</v>
@@ -9033,16 +9033,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D247" t="str">
-        <v>Archive past results into local storage verification #246</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G247" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H247" t="str">
         <v>High</v>
@@ -9068,16 +9068,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D248" t="str">
-        <v>Render nearby hospitals via location tracking verification #247</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G248" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H248" t="str">
         <v>High</v>
@@ -9103,16 +9103,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D249" t="str">
-        <v>Update personal demographic info natively verification #248</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G249" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H249" t="str">
         <v>High</v>
@@ -9138,16 +9138,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D250" t="str">
-        <v>Toggle dark/light mode visual rendering verification #249</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G250" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H250" t="str">
         <v>High</v>
@@ -9173,16 +9173,16 @@
         <v>Sign In</v>
       </c>
       <c r="D251" t="str">
-        <v>Verify secure user login credentials verification #250</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G251" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H251" t="str">
         <v>Critical</v>
@@ -9208,16 +9208,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D252" t="str">
-        <v>Verify user registration workflow verification #251</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G252" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H252" t="str">
         <v>High</v>
@@ -9243,16 +9243,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D253" t="str">
-        <v>Validate password reset email triggering verification #252</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G253" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H253" t="str">
         <v>High</v>
@@ -9278,16 +9278,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D254" t="str">
-        <v>Complete detailed symptom assessment verification #253</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G254" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H254" t="str">
         <v>High</v>
@@ -9313,16 +9313,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D255" t="str">
-        <v>Export medical summary to doctor securely verification #254</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G255" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H255" t="str">
         <v>High</v>
@@ -9348,16 +9348,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D256" t="str">
-        <v>Unlock deep medical analysis processing verification #255</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G256" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H256" t="str">
         <v>Critical</v>
@@ -9383,16 +9383,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D257" t="str">
-        <v>Archive past results into local storage verification #256</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G257" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H257" t="str">
         <v>High</v>
@@ -9418,16 +9418,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D258" t="str">
-        <v>Render nearby hospitals via location tracking verification #257</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G258" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H258" t="str">
         <v>High</v>
@@ -9453,16 +9453,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D259" t="str">
-        <v>Update personal demographic info natively verification #258</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G259" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H259" t="str">
         <v>High</v>
@@ -9488,16 +9488,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D260" t="str">
-        <v>Toggle dark/light mode visual rendering verification #259</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G260" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H260" t="str">
         <v>High</v>
@@ -9523,16 +9523,16 @@
         <v>Sign In</v>
       </c>
       <c r="D261" t="str">
-        <v>Verify secure user login credentials verification #260</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G261" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H261" t="str">
         <v>Critical</v>
@@ -9558,16 +9558,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D262" t="str">
-        <v>Verify user registration workflow verification #261</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G262" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H262" t="str">
         <v>High</v>
@@ -9593,16 +9593,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D263" t="str">
-        <v>Validate password reset email triggering verification #262</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G263" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H263" t="str">
         <v>High</v>
@@ -9628,16 +9628,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D264" t="str">
-        <v>Complete detailed symptom assessment verification #263</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G264" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H264" t="str">
         <v>High</v>
@@ -9663,16 +9663,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D265" t="str">
-        <v>Export medical summary to doctor securely verification #264</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G265" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H265" t="str">
         <v>High</v>
@@ -9698,16 +9698,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D266" t="str">
-        <v>Unlock deep medical analysis processing verification #265</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G266" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H266" t="str">
         <v>Critical</v>
@@ -9733,16 +9733,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D267" t="str">
-        <v>Archive past results into local storage verification #266</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G267" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H267" t="str">
         <v>High</v>
@@ -9768,16 +9768,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D268" t="str">
-        <v>Render nearby hospitals via location tracking verification #267</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G268" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H268" t="str">
         <v>High</v>
@@ -9803,16 +9803,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D269" t="str">
-        <v>Update personal demographic info natively verification #268</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G269" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H269" t="str">
         <v>High</v>
@@ -9838,16 +9838,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D270" t="str">
-        <v>Toggle dark/light mode visual rendering verification #269</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G270" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H270" t="str">
         <v>High</v>
@@ -9873,16 +9873,16 @@
         <v>Sign In</v>
       </c>
       <c r="D271" t="str">
-        <v>Verify secure user login credentials verification #270</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G271" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H271" t="str">
         <v>Critical</v>
@@ -9908,16 +9908,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D272" t="str">
-        <v>Verify user registration workflow verification #271</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G272" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H272" t="str">
         <v>High</v>
@@ -9943,16 +9943,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D273" t="str">
-        <v>Validate password reset email triggering verification #272</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G273" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H273" t="str">
         <v>High</v>
@@ -9978,16 +9978,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D274" t="str">
-        <v>Complete detailed symptom assessment verification #273</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G274" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H274" t="str">
         <v>High</v>
@@ -10013,16 +10013,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D275" t="str">
-        <v>Export medical summary to doctor securely verification #274</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G275" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H275" t="str">
         <v>High</v>
@@ -10048,16 +10048,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D276" t="str">
-        <v>Unlock deep medical analysis processing verification #275</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G276" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H276" t="str">
         <v>Critical</v>
@@ -10083,16 +10083,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D277" t="str">
-        <v>Archive past results into local storage verification #276</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G277" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H277" t="str">
         <v>High</v>
@@ -10118,16 +10118,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D278" t="str">
-        <v>Render nearby hospitals via location tracking verification #277</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G278" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H278" t="str">
         <v>High</v>
@@ -10153,16 +10153,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D279" t="str">
-        <v>Update personal demographic info natively verification #278</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G279" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H279" t="str">
         <v>High</v>
@@ -10188,16 +10188,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D280" t="str">
-        <v>Toggle dark/light mode visual rendering verification #279</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G280" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H280" t="str">
         <v>High</v>
@@ -10223,16 +10223,16 @@
         <v>Sign In</v>
       </c>
       <c r="D281" t="str">
-        <v>Verify secure user login credentials verification #280</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G281" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H281" t="str">
         <v>Critical</v>
@@ -10258,16 +10258,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D282" t="str">
-        <v>Verify user registration workflow verification #281</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G282" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H282" t="str">
         <v>High</v>
@@ -10293,16 +10293,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D283" t="str">
-        <v>Validate password reset email triggering verification #282</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G283" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H283" t="str">
         <v>High</v>
@@ -10328,16 +10328,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D284" t="str">
-        <v>Complete detailed symptom assessment verification #283</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G284" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H284" t="str">
         <v>High</v>
@@ -10363,16 +10363,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D285" t="str">
-        <v>Export medical summary to doctor securely verification #284</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G285" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H285" t="str">
         <v>High</v>
@@ -10398,16 +10398,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D286" t="str">
-        <v>Unlock deep medical analysis processing verification #285</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G286" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H286" t="str">
         <v>Critical</v>
@@ -10433,16 +10433,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D287" t="str">
-        <v>Archive past results into local storage verification #286</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G287" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H287" t="str">
         <v>High</v>
@@ -10468,16 +10468,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D288" t="str">
-        <v>Render nearby hospitals via location tracking verification #287</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G288" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H288" t="str">
         <v>High</v>
@@ -10503,16 +10503,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D289" t="str">
-        <v>Update personal demographic info natively verification #288</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G289" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H289" t="str">
         <v>High</v>
@@ -10538,16 +10538,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D290" t="str">
-        <v>Toggle dark/light mode visual rendering verification #289</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G290" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H290" t="str">
         <v>High</v>
@@ -10573,16 +10573,16 @@
         <v>Sign In</v>
       </c>
       <c r="D291" t="str">
-        <v>Verify secure user login credentials verification #290</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G291" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H291" t="str">
         <v>Critical</v>
@@ -10608,16 +10608,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify user registration workflow verification #291</v>
+        <v>Verify user registration workflow [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Authentication and perform Sign Up action</v>
+        <v>Execute Sign Up action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G292" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H292" t="str">
         <v>High</v>
@@ -10643,16 +10643,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D293" t="str">
-        <v>Validate password reset email triggering verification #292</v>
+        <v>Validate password reset email triggering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Authentication and perform Forgot Password action</v>
+        <v>Execute Forgot Password action while simulating security guard (special char injection)</v>
       </c>
       <c r="G293" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H293" t="str">
         <v>High</v>
@@ -10678,16 +10678,16 @@
         <v>Symptom Check</v>
       </c>
       <c r="D294" t="str">
-        <v>Complete detailed symptom assessment verification #293</v>
+        <v>Complete detailed symptom assessment [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Diagnostics and perform Symptom Check action</v>
+        <v>Execute Symptom Check action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G294" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H294" t="str">
         <v>High</v>
@@ -10713,16 +10713,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D295" t="str">
-        <v>Export medical summary to doctor securely verification #294</v>
+        <v>Export medical summary to doctor securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Diagnostics and perform Diagnostic Report action</v>
+        <v>Execute Diagnostic Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G295" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H295" t="str">
         <v>High</v>
@@ -10748,16 +10748,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D296" t="str">
-        <v>Unlock deep medical analysis processing verification #295</v>
+        <v>Unlock deep medical analysis processing [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Diagnostics and perform Deep Analysis action</v>
+        <v>Execute Deep Analysis action while simulating normal path (standard execution)</v>
       </c>
       <c r="G296" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H296" t="str">
         <v>Critical</v>
@@ -10783,16 +10783,16 @@
         <v>Archive Result</v>
       </c>
       <c r="D297" t="str">
-        <v>Archive past results into local storage verification #296</v>
+        <v>Archive past results into local storage [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Diagnostics and perform Archive Result action</v>
+        <v>Execute Archive Result action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G297" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H297" t="str">
         <v>High</v>
@@ -10818,16 +10818,16 @@
         <v>Find Hospitals</v>
       </c>
       <c r="D298" t="str">
-        <v>Render nearby hospitals via location tracking verification #297</v>
+        <v>Render nearby hospitals via location tracking [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Geolocation and perform Find Hospitals action</v>
+        <v>Execute Find Hospitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G298" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H298" t="str">
         <v>High</v>
@@ -10853,16 +10853,16 @@
         <v>Edit Profile</v>
       </c>
       <c r="D299" t="str">
-        <v>Update personal demographic info natively verification #298</v>
+        <v>Update personal demographic info natively [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Settings and perform Edit Profile action</v>
+        <v>Execute Edit Profile action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G299" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H299" t="str">
         <v>High</v>
@@ -10888,16 +10888,16 @@
         <v>Display Theme</v>
       </c>
       <c r="D300" t="str">
-        <v>Toggle dark/light mode visual rendering verification #299</v>
+        <v>Toggle dark/light mode visual rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Settings and perform Display Theme action</v>
+        <v>Execute Display Theme action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G300" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H300" t="str">
         <v>High</v>
@@ -10923,16 +10923,16 @@
         <v>Sign In</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify secure user login credentials verification #300</v>
+        <v>Verify secure user login credentials [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Web/React</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Authentication and perform Sign In action</v>
+        <v>Execute Sign In action while simulating normal path (standard execution)</v>
       </c>
       <c r="G301" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H301" t="str">
         <v>Critical</v>

--- a/e2e_tests_suite/Report_01_Selenium.xlsx
+++ b/e2e_tests_suite/Report_01_Selenium.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K301"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -458,16 +458,16 @@
         <v>Sign In</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify Email input validation rendering and execution in Web UI</v>
+        <v>Verify Email input validation under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E2" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Email input validation' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Email input validation'</v>
       </c>
       <c r="G2" t="str">
-        <v>UI updates seamlessly, 'Email input validation' executes correctly without console errors</v>
+        <v>Element 'Email input validation' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H2" t="str">
         <v>Medium</v>
@@ -493,16 +493,16 @@
         <v>Sign In</v>
       </c>
       <c r="D3" t="str">
-        <v>Verify Password visibility toggle rendering and execution in Web UI</v>
+        <v>Verify Password visibility toggle under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E3" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Password visibility toggle' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Password visibility toggle'</v>
       </c>
       <c r="G3" t="str">
-        <v>UI updates seamlessly, 'Password visibility toggle' executes correctly without console errors</v>
+        <v>Element 'Password visibility toggle' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H3" t="str">
         <v>High</v>
@@ -528,16 +528,16 @@
         <v>Sign In</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify Remember me checkbox rendering and execution in Web UI</v>
+        <v>Verify Remember me checkbox under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E4" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Remember me checkbox' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Remember me checkbox'</v>
       </c>
       <c r="G4" t="str">
-        <v>UI updates seamlessly, 'Remember me checkbox' executes correctly without console errors</v>
+        <v>Element 'Remember me checkbox' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H4" t="str">
         <v>Medium</v>
@@ -563,16 +563,16 @@
         <v>Sign In</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify Sign In button state rendering and execution in Web UI</v>
+        <v>Verify Sign In button state under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E5" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Sign In button state' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Sign In button state'</v>
       </c>
       <c r="G5" t="str">
-        <v>UI updates seamlessly, 'Sign In button state' executes correctly without console errors</v>
+        <v>Element 'Sign In button state' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H5" t="str">
         <v>Critical</v>
@@ -598,16 +598,16 @@
         <v>Sign In</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify Invalid credentials alert rendering and execution in Web UI</v>
+        <v>Verify Invalid credentials alert under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E6" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Invalid credentials alert' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Invalid credentials alert'</v>
       </c>
       <c r="G6" t="str">
-        <v>UI updates seamlessly, 'Invalid credentials alert' executes correctly without console errors</v>
+        <v>Element 'Invalid credentials alert' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H6" t="str">
         <v>Medium</v>
@@ -633,16 +633,16 @@
         <v>Sign In</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify Session persistence check rendering and execution in Web UI</v>
+        <v>Verify Session persistence check under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E7" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Session persistence check' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Session persistence check'</v>
       </c>
       <c r="G7" t="str">
-        <v>UI updates seamlessly, 'Session persistence check' executes correctly without console errors</v>
+        <v>Element 'Session persistence check' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H7" t="str">
         <v>High</v>
@@ -668,16 +668,16 @@
         <v>Sign In</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify OAuth Google Sign-In rendering and execution in Web UI</v>
+        <v>Verify OAuth Google Sign-In under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E8" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'OAuth Google Sign-In' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'OAuth Google Sign-In'</v>
       </c>
       <c r="G8" t="str">
-        <v>UI updates seamlessly, 'OAuth Google Sign-In' executes correctly without console errors</v>
+        <v>Element 'OAuth Google Sign-In' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H8" t="str">
         <v>Medium</v>
@@ -703,16 +703,16 @@
         <v>Sign In</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify OAuth Apple Sign-In rendering and execution in Web UI</v>
+        <v>Verify OAuth Apple Sign-In under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E9" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'OAuth Apple Sign-In' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'OAuth Apple Sign-In'</v>
       </c>
       <c r="G9" t="str">
-        <v>UI updates seamlessly, 'OAuth Apple Sign-In' executes correctly without console errors</v>
+        <v>Element 'OAuth Apple Sign-In' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H9" t="str">
         <v>Critical</v>
@@ -738,16 +738,16 @@
         <v>Sign In</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify SSO Redirect flow rendering and execution in Web UI</v>
+        <v>Verify SSO Redirect flow under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E10" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'SSO Redirect flow' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'SSO Redirect flow'</v>
       </c>
       <c r="G10" t="str">
-        <v>UI updates seamlessly, 'SSO Redirect flow' executes correctly without console errors</v>
+        <v>Element 'SSO Redirect flow' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H10" t="str">
         <v>Medium</v>
@@ -773,16 +773,16 @@
         <v>Sign In</v>
       </c>
       <c r="D11" t="str">
-        <v>Verify Logout session destruction rendering and execution in Web UI</v>
+        <v>Verify Logout session destruction under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E11" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Authentication &gt; Sign In, trigger 'Logout session destruction' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign In: Verify DOM element rendering and click handler response for 'Logout session destruction'</v>
       </c>
       <c r="G11" t="str">
-        <v>UI updates seamlessly, 'Logout session destruction' executes correctly without console errors</v>
+        <v>Element 'Logout session destruction' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H11" t="str">
         <v>High</v>
@@ -808,16 +808,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify Full Name field validation rendering and execution in Web UI</v>
+        <v>Verify Full Name field validation under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E12" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Full Name field validation' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Full Name field validation'</v>
       </c>
       <c r="G12" t="str">
-        <v>UI updates seamlessly, 'Full Name field validation' executes correctly without console errors</v>
+        <v>Element 'Full Name field validation' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H12" t="str">
         <v>Medium</v>
@@ -843,16 +843,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify Email syntax checker rendering and execution in Web UI</v>
+        <v>Verify Email syntax checker under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E13" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Email syntax checker' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Email syntax checker'</v>
       </c>
       <c r="G13" t="str">
-        <v>UI updates seamlessly, 'Email syntax checker' executes correctly without console errors</v>
+        <v>Element 'Email syntax checker' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H13" t="str">
         <v>Critical</v>
@@ -878,16 +878,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D14" t="str">
-        <v>Verify Password strength meter rendering and execution in Web UI</v>
+        <v>Verify Password strength meter under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E14" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Password strength meter' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Password strength meter'</v>
       </c>
       <c r="G14" t="str">
-        <v>UI updates seamlessly, 'Password strength meter' executes correctly without console errors</v>
+        <v>Element 'Password strength meter' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H14" t="str">
         <v>Medium</v>
@@ -913,16 +913,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D15" t="str">
-        <v>Verify Confirm password matching rendering and execution in Web UI</v>
+        <v>Verify Confirm password matching under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E15" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Confirm password matching' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Confirm password matching'</v>
       </c>
       <c r="G15" t="str">
-        <v>UI updates seamlessly, 'Confirm password matching' executes correctly without console errors</v>
+        <v>Element 'Confirm password matching' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H15" t="str">
         <v>High</v>
@@ -948,16 +948,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify Terms consent checkbox rendering and execution in Web UI</v>
+        <v>Verify Terms consent checkbox under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E16" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Terms consent checkbox' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Terms consent checkbox'</v>
       </c>
       <c r="G16" t="str">
-        <v>UI updates seamlessly, 'Terms consent checkbox' executes correctly without console errors</v>
+        <v>Element 'Terms consent checkbox' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H16" t="str">
         <v>Medium</v>
@@ -983,16 +983,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify Biometric age picker rendering and execution in Web UI</v>
+        <v>Verify Biometric age picker under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E17" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Biometric age picker' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Biometric age picker'</v>
       </c>
       <c r="G17" t="str">
-        <v>UI updates seamlessly, 'Biometric age picker' executes correctly without console errors</v>
+        <v>Element 'Biometric age picker' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H17" t="str">
         <v>Critical</v>
@@ -1018,16 +1018,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D18" t="str">
-        <v>Verify Gender selection radio rendering and execution in Web UI</v>
+        <v>Verify Gender selection radio under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E18" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Gender selection radio' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Gender selection radio'</v>
       </c>
       <c r="G18" t="str">
-        <v>UI updates seamlessly, 'Gender selection radio' executes correctly without console errors</v>
+        <v>Element 'Gender selection radio' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H18" t="str">
         <v>Medium</v>
@@ -1053,16 +1053,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D19" t="str">
-        <v>Verify Registration submit button rendering and execution in Web UI</v>
+        <v>Verify Registration submit button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E19" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Registration submit button' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Registration submit button'</v>
       </c>
       <c r="G19" t="str">
-        <v>UI updates seamlessly, 'Registration submit button' executes correctly without console errors</v>
+        <v>Element 'Registration submit button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H19" t="str">
         <v>High</v>
@@ -1088,16 +1088,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify Duplicate email error toast rendering and execution in Web UI</v>
+        <v>Verify Duplicate email error toast under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E20" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Duplicate email error toast' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Duplicate email error toast'</v>
       </c>
       <c r="G20" t="str">
-        <v>UI updates seamlessly, 'Duplicate email error toast' executes correctly without console errors</v>
+        <v>Element 'Duplicate email error toast' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H20" t="str">
         <v>Medium</v>
@@ -1123,16 +1123,16 @@
         <v>Sign Up</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify Welcome modal trigger rendering and execution in Web UI</v>
+        <v>Verify Welcome modal trigger under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E21" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Authentication &gt; Sign Up, trigger 'Welcome modal trigger' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Sign Up: Verify DOM element rendering and click handler response for 'Welcome modal trigger'</v>
       </c>
       <c r="G21" t="str">
-        <v>UI updates seamlessly, 'Welcome modal trigger' executes correctly without console errors</v>
+        <v>Element 'Welcome modal trigger' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H21" t="str">
         <v>Critical</v>
@@ -1158,16 +1158,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify Email recovery prompt rendering and execution in Web UI</v>
+        <v>Verify Email recovery prompt under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E22" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Email recovery prompt' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Email recovery prompt'</v>
       </c>
       <c r="G22" t="str">
-        <v>UI updates seamlessly, 'Email recovery prompt' executes correctly without console errors</v>
+        <v>Element 'Email recovery prompt' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H22" t="str">
         <v>Medium</v>
@@ -1193,16 +1193,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D23" t="str">
-        <v>Verify Reset link trigger button rendering and execution in Web UI</v>
+        <v>Verify Reset link trigger button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E23" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Reset link trigger button' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Reset link trigger button'</v>
       </c>
       <c r="G23" t="str">
-        <v>UI updates seamlessly, 'Reset link trigger button' executes correctly without console errors</v>
+        <v>Element 'Reset link trigger button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H23" t="str">
         <v>High</v>
@@ -1228,16 +1228,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify Back to Sign In link rendering and execution in Web UI</v>
+        <v>Verify Back to Sign In link under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E24" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Back to Sign In link' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Back to Sign In link'</v>
       </c>
       <c r="G24" t="str">
-        <v>UI updates seamlessly, 'Back to Sign In link' executes correctly without console errors</v>
+        <v>Element 'Back to Sign In link' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H24" t="str">
         <v>Medium</v>
@@ -1263,16 +1263,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify Invalid email warning rendering and execution in Web UI</v>
+        <v>Verify Invalid email warning under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E25" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Invalid email warning' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Invalid email warning'</v>
       </c>
       <c r="G25" t="str">
-        <v>UI updates seamlessly, 'Invalid email warning' executes correctly without console errors</v>
+        <v>Element 'Invalid email warning' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H25" t="str">
         <v>Critical</v>
@@ -1298,16 +1298,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify Success banner display rendering and execution in Web UI</v>
+        <v>Verify Success banner display under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E26" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Success banner display' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Success banner display'</v>
       </c>
       <c r="G26" t="str">
-        <v>UI updates seamlessly, 'Success banner display' executes correctly without console errors</v>
+        <v>Element 'Success banner display' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H26" t="str">
         <v>Medium</v>
@@ -1333,16 +1333,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D27" t="str">
-        <v>Verify Rate limit on reset requests rendering and execution in Web UI</v>
+        <v>Verify Rate limit on reset requests under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E27" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Rate limit on reset requests' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Rate limit on reset requests'</v>
       </c>
       <c r="G27" t="str">
-        <v>UI updates seamlessly, 'Rate limit on reset requests' executes correctly without console errors</v>
+        <v>Element 'Rate limit on reset requests' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H27" t="str">
         <v>High</v>
@@ -1368,16 +1368,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify Token link expiration handling rendering and execution in Web UI</v>
+        <v>Verify Token link expiration handling under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E28" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Token link expiration handling' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Token link expiration handling'</v>
       </c>
       <c r="G28" t="str">
-        <v>UI updates seamlessly, 'Token link expiration handling' executes correctly without console errors</v>
+        <v>Element 'Token link expiration handling' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H28" t="str">
         <v>Medium</v>
@@ -1403,16 +1403,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D29" t="str">
-        <v>Verify New password input rendering and execution in Web UI</v>
+        <v>Verify New password input under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E29" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'New password input' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'New password input'</v>
       </c>
       <c r="G29" t="str">
-        <v>UI updates seamlessly, 'New password input' executes correctly without console errors</v>
+        <v>Element 'New password input' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H29" t="str">
         <v>Critical</v>
@@ -1438,16 +1438,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D30" t="str">
-        <v>Verify Confirm new password rendering and execution in Web UI</v>
+        <v>Verify Confirm new password under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E30" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Confirm new password' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Confirm new password'</v>
       </c>
       <c r="G30" t="str">
-        <v>UI updates seamlessly, 'Confirm new password' executes correctly without console errors</v>
+        <v>Element 'Confirm new password' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H30" t="str">
         <v>Medium</v>
@@ -1473,16 +1473,16 @@
         <v>Forgot Password</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify Password reset completion redirect rendering and execution in Web UI</v>
+        <v>Verify Password reset completion redirect under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E31" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Authentication &gt; Forgot Password, trigger 'Password reset completion redirect' control, and observe DOM response</v>
+        <v>Navigate to Authentication &gt; Forgot Password: Verify DOM element rendering and click handler response for 'Password reset completion redirect'</v>
       </c>
       <c r="G31" t="str">
-        <v>UI updates seamlessly, 'Password reset completion redirect' executes correctly without console errors</v>
+        <v>Element 'Password reset completion redirect' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H31" t="str">
         <v>High</v>
@@ -1508,16 +1508,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify Symptom search input autocomplete rendering and execution in Web UI</v>
+        <v>Verify Symptom search input autocomplete under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E32" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Symptom search input autocomplete' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Symptom search input autocomplete'</v>
       </c>
       <c r="G32" t="str">
-        <v>UI updates seamlessly, 'Symptom search input autocomplete' executes correctly without console errors</v>
+        <v>Element 'Symptom search input autocomplete' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H32" t="str">
         <v>Medium</v>
@@ -1543,16 +1543,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify Primary symptom tag selection rendering and execution in Web UI</v>
+        <v>Verify Primary symptom tag selection under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E33" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Primary symptom tag selection' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Primary symptom tag selection'</v>
       </c>
       <c r="G33" t="str">
-        <v>UI updates seamlessly, 'Primary symptom tag selection' executes correctly without console errors</v>
+        <v>Element 'Primary symptom tag selection' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H33" t="str">
         <v>Critical</v>
@@ -1578,16 +1578,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify Severity slider adjustment rendering and execution in Web UI</v>
+        <v>Verify Severity slider adjustment under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E34" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Severity slider adjustment' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Severity slider adjustment'</v>
       </c>
       <c r="G34" t="str">
-        <v>UI updates seamlessly, 'Severity slider adjustment' executes correctly without console errors</v>
+        <v>Element 'Severity slider adjustment' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H34" t="str">
         <v>Medium</v>
@@ -1613,16 +1613,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D35" t="str">
-        <v>Verify Duration selection dropdown rendering and execution in Web UI</v>
+        <v>Verify Duration selection dropdown under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E35" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Duration selection dropdown' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Duration selection dropdown'</v>
       </c>
       <c r="G35" t="str">
-        <v>UI updates seamlessly, 'Duration selection dropdown' executes correctly without console errors</v>
+        <v>Element 'Duration selection dropdown' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H35" t="str">
         <v>High</v>
@@ -1648,16 +1648,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify Body region target selector rendering and execution in Web UI</v>
+        <v>Verify Body region target selector under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E36" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Body region target selector' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Body region target selector'</v>
       </c>
       <c r="G36" t="str">
-        <v>UI updates seamlessly, 'Body region target selector' executes correctly without console errors</v>
+        <v>Element 'Body region target selector' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H36" t="str">
         <v>Medium</v>
@@ -1683,16 +1683,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify Additional notes text area rendering and execution in Web UI</v>
+        <v>Verify Additional notes text area under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E37" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Additional notes text area' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Additional notes text area'</v>
       </c>
       <c r="G37" t="str">
-        <v>UI updates seamlessly, 'Additional notes text area' executes correctly without console errors</v>
+        <v>Element 'Additional notes text area' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H37" t="str">
         <v>Critical</v>
@@ -1718,16 +1718,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D38" t="str">
-        <v>Verify Analyze Symptoms action button rendering and execution in Web UI</v>
+        <v>Verify Analyze Symptoms action button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E38" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Analyze Symptoms action button' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Analyze Symptoms action button'</v>
       </c>
       <c r="G38" t="str">
-        <v>UI updates seamlessly, 'Analyze Symptoms action button' executes correctly without console errors</v>
+        <v>Element 'Analyze Symptoms action button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H38" t="str">
         <v>Medium</v>
@@ -1753,16 +1753,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D39" t="str">
-        <v>Verify Clear selected symptoms button rendering and execution in Web UI</v>
+        <v>Verify Clear selected symptoms button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E39" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Clear selected symptoms button' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Clear selected symptoms button'</v>
       </c>
       <c r="G39" t="str">
-        <v>UI updates seamlessly, 'Clear selected symptoms button' executes correctly without console errors</v>
+        <v>Element 'Clear selected symptoms button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H39" t="str">
         <v>High</v>
@@ -1788,16 +1788,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify Symptom history list render rendering and execution in Web UI</v>
+        <v>Verify Symptom history list render under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E40" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Symptom history list render' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Symptom history list render'</v>
       </c>
       <c r="G40" t="str">
-        <v>UI updates seamlessly, 'Symptom history list render' executes correctly without console errors</v>
+        <v>Element 'Symptom history list render' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H40" t="str">
         <v>Medium</v>
@@ -1823,16 +1823,16 @@
         <v>Symptom Checker</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify Recent assessment card view rendering and execution in Web UI</v>
+        <v>Verify Recent assessment card view under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E41" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Diagnostics &gt; Symptom Checker, trigger 'Recent assessment card view' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Verify DOM element rendering and click handler response for 'Recent assessment card view'</v>
       </c>
       <c r="G41" t="str">
-        <v>UI updates seamlessly, 'Recent assessment card view' executes correctly without console errors</v>
+        <v>Element 'Recent assessment card view' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H41" t="str">
         <v>Critical</v>
@@ -1858,16 +1858,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify Multi-step questionnaire step 1 rendering and execution in Web UI</v>
+        <v>Verify Multi-step questionnaire step 1 under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E42" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Multi-step questionnaire step 1' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Multi-step questionnaire step 1'</v>
       </c>
       <c r="G42" t="str">
-        <v>UI updates seamlessly, 'Multi-step questionnaire step 1' executes correctly without console errors</v>
+        <v>Element 'Multi-step questionnaire step 1' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H42" t="str">
         <v>Medium</v>
@@ -1893,16 +1893,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D43" t="str">
-        <v>Verify Multi-step questionnaire step 2 rendering and execution in Web UI</v>
+        <v>Verify Multi-step questionnaire step 2 under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E43" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Multi-step questionnaire step 2' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Multi-step questionnaire step 2'</v>
       </c>
       <c r="G43" t="str">
-        <v>UI updates seamlessly, 'Multi-step questionnaire step 2' executes correctly without console errors</v>
+        <v>Element 'Multi-step questionnaire step 2' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H43" t="str">
         <v>High</v>
@@ -1928,16 +1928,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D44" t="str">
-        <v>Verify Multi-step questionnaire step 3 rendering and execution in Web UI</v>
+        <v>Verify Multi-step questionnaire step 3 under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E44" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Multi-step questionnaire step 3' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Multi-step questionnaire step 3'</v>
       </c>
       <c r="G44" t="str">
-        <v>UI updates seamlessly, 'Multi-step questionnaire step 3' executes correctly without console errors</v>
+        <v>Element 'Multi-step questionnaire step 3' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H44" t="str">
         <v>Medium</v>
@@ -1963,16 +1963,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D45" t="str">
-        <v>Verify Risk score percentage display rendering and execution in Web UI</v>
+        <v>Verify Risk score percentage display under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E45" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Risk score percentage display' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Risk score percentage display'</v>
       </c>
       <c r="G45" t="str">
-        <v>UI updates seamlessly, 'Risk score percentage display' executes correctly without console errors</v>
+        <v>Element 'Risk score percentage display' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H45" t="str">
         <v>Critical</v>
@@ -1998,16 +1998,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify Condition likelihood ranking rendering and execution in Web UI</v>
+        <v>Verify Condition likelihood ranking under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E46" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Condition likelihood ranking' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Condition likelihood ranking'</v>
       </c>
       <c r="G46" t="str">
-        <v>UI updates seamlessly, 'Condition likelihood ranking' executes correctly without console errors</v>
+        <v>Element 'Condition likelihood ranking' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H46" t="str">
         <v>Medium</v>
@@ -2033,16 +2033,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D47" t="str">
-        <v>Verify Emergency warning banner rendering and execution in Web UI</v>
+        <v>Verify Emergency warning banner under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E47" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Emergency warning banner' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Emergency warning banner'</v>
       </c>
       <c r="G47" t="str">
-        <v>UI updates seamlessly, 'Emergency warning banner' executes correctly without console errors</v>
+        <v>Element 'Emergency warning banner' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H47" t="str">
         <v>High</v>
@@ -2068,16 +2068,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D48" t="str">
-        <v>Verify Doctor recommendation card rendering and execution in Web UI</v>
+        <v>Verify Doctor recommendation card under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E48" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Doctor recommendation card' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Doctor recommendation card'</v>
       </c>
       <c r="G48" t="str">
-        <v>UI updates seamlessly, 'Doctor recommendation card' executes correctly without console errors</v>
+        <v>Element 'Doctor recommendation card' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H48" t="str">
         <v>Medium</v>
@@ -2103,16 +2103,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify Print assessment summary rendering and execution in Web UI</v>
+        <v>Verify Print assessment summary under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E49" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Print assessment summary' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Print assessment summary'</v>
       </c>
       <c r="G49" t="str">
-        <v>UI updates seamlessly, 'Print assessment summary' executes correctly without console errors</v>
+        <v>Element 'Print assessment summary' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H49" t="str">
         <v>Critical</v>
@@ -2138,16 +2138,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D50" t="str">
-        <v>Verify Share assessment modal rendering and execution in Web UI</v>
+        <v>Verify Share assessment modal under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E50" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Share assessment modal' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Share assessment modal'</v>
       </c>
       <c r="G50" t="str">
-        <v>UI updates seamlessly, 'Share assessment modal' executes correctly without console errors</v>
+        <v>Element 'Share assessment modal' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H50" t="str">
         <v>Medium</v>
@@ -2173,16 +2173,16 @@
         <v>Detailed Assessment</v>
       </c>
       <c r="D51" t="str">
-        <v>Verify Save assessment to profile rendering and execution in Web UI</v>
+        <v>Verify Save assessment to profile under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E51" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Diagnostics &gt; Detailed Assessment, trigger 'Save assessment to profile' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Verify DOM element rendering and click handler response for 'Save assessment to profile'</v>
       </c>
       <c r="G51" t="str">
-        <v>UI updates seamlessly, 'Save assessment to profile' executes correctly without console errors</v>
+        <v>Element 'Save assessment to profile' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H51" t="str">
         <v>High</v>
@@ -2208,16 +2208,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify PDF report generator button rendering and execution in Web UI</v>
+        <v>Verify PDF report generator button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E52" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'PDF report generator button' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'PDF report generator button'</v>
       </c>
       <c r="G52" t="str">
-        <v>UI updates seamlessly, 'PDF report generator button' executes correctly without console errors</v>
+        <v>Element 'PDF report generator button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H52" t="str">
         <v>Medium</v>
@@ -2243,16 +2243,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D53" t="str">
-        <v>Verify Doctor PDF export format rendering and execution in Web UI</v>
+        <v>Verify Doctor PDF export format under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E53" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Doctor PDF export format' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Doctor PDF export format'</v>
       </c>
       <c r="G53" t="str">
-        <v>UI updates seamlessly, 'Doctor PDF export format' executes correctly without console errors</v>
+        <v>Element 'Doctor PDF export format' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H53" t="str">
         <v>Critical</v>
@@ -2278,16 +2278,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D54" t="str">
-        <v>Verify Vitals summary chart render rendering and execution in Web UI</v>
+        <v>Verify Vitals summary chart render under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E54" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Vitals summary chart render' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Vitals summary chart render'</v>
       </c>
       <c r="G54" t="str">
-        <v>UI updates seamlessly, 'Vitals summary chart render' executes correctly without console errors</v>
+        <v>Element 'Vitals summary chart render' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H54" t="str">
         <v>Medium</v>
@@ -2313,16 +2313,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D55" t="str">
-        <v>Verify Symptom timeline visualization rendering and execution in Web UI</v>
+        <v>Verify Symptom timeline visualization under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E55" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Symptom timeline visualization' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Symptom timeline visualization'</v>
       </c>
       <c r="G55" t="str">
-        <v>UI updates seamlessly, 'Symptom timeline visualization' executes correctly without console errors</v>
+        <v>Element 'Symptom timeline visualization' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H55" t="str">
         <v>High</v>
@@ -2348,16 +2348,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify Clinical notes section rendering and execution in Web UI</v>
+        <v>Verify Clinical notes section under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E56" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Clinical notes section' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Clinical notes section'</v>
       </c>
       <c r="G56" t="str">
-        <v>UI updates seamlessly, 'Clinical notes section' executes correctly without console errors</v>
+        <v>Element 'Clinical notes section' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H56" t="str">
         <v>Medium</v>
@@ -2383,16 +2383,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify Prescription record attachment rendering and execution in Web UI</v>
+        <v>Verify Prescription record attachment under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E57" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Prescription record attachment' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Prescription record attachment'</v>
       </c>
       <c r="G57" t="str">
-        <v>UI updates seamlessly, 'Prescription record attachment' executes correctly without console errors</v>
+        <v>Element 'Prescription record attachment' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H57" t="str">
         <v>Critical</v>
@@ -2418,16 +2418,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify Digital signature validation rendering and execution in Web UI</v>
+        <v>Verify Digital signature validation under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E58" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Digital signature validation' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Digital signature validation'</v>
       </c>
       <c r="G58" t="str">
-        <v>UI updates seamlessly, 'Digital signature validation' executes correctly without console errors</v>
+        <v>Element 'Digital signature validation' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H58" t="str">
         <v>Medium</v>
@@ -2453,16 +2453,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D59" t="str">
-        <v>Verify Download report action rendering and execution in Web UI</v>
+        <v>Verify Download report action under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E59" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Download report action' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Download report action'</v>
       </c>
       <c r="G59" t="str">
-        <v>UI updates seamlessly, 'Download report action' executes correctly without console errors</v>
+        <v>Element 'Download report action' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H59" t="str">
         <v>High</v>
@@ -2488,16 +2488,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D60" t="str">
-        <v>Verify Email report to doctor form rendering and execution in Web UI</v>
+        <v>Verify Email report to doctor form under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E60" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Email report to doctor form' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Email report to doctor form'</v>
       </c>
       <c r="G60" t="str">
-        <v>UI updates seamlessly, 'Email report to doctor form' executes correctly without console errors</v>
+        <v>Element 'Email report to doctor form' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H60" t="str">
         <v>Medium</v>
@@ -2523,16 +2523,16 @@
         <v>Diagnostic Report</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify Print friendly view toggle rendering and execution in Web UI</v>
+        <v>Verify Print friendly view toggle under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E61" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Diagnostics &gt; Diagnostic Report, trigger 'Print friendly view toggle' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Verify DOM element rendering and click handler response for 'Print friendly view toggle'</v>
       </c>
       <c r="G61" t="str">
-        <v>UI updates seamlessly, 'Print friendly view toggle' executes correctly without console errors</v>
+        <v>Element 'Print friendly view toggle' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H61" t="str">
         <v>Critical</v>
@@ -2558,16 +2558,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify Unlock Deep Analysis modal rendering and execution in Web UI</v>
+        <v>Verify Unlock Deep Analysis modal under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E62" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Unlock Deep Analysis modal' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Unlock Deep Analysis modal'</v>
       </c>
       <c r="G62" t="str">
-        <v>UI updates seamlessly, 'Unlock Deep Analysis modal' executes correctly without console errors</v>
+        <v>Element 'Unlock Deep Analysis modal' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H62" t="str">
         <v>Medium</v>
@@ -2593,16 +2593,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D63" t="str">
-        <v>Verify AI model selection dropdown rendering and execution in Web UI</v>
+        <v>Verify AI model selection dropdown under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E63" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'AI model selection dropdown' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'AI model selection dropdown'</v>
       </c>
       <c r="G63" t="str">
-        <v>UI updates seamlessly, 'AI model selection dropdown' executes correctly without console errors</v>
+        <v>Element 'AI model selection dropdown' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H63" t="str">
         <v>High</v>
@@ -2628,16 +2628,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify Confidence interval score display rendering and execution in Web UI</v>
+        <v>Verify Confidence interval score display under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E64" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Confidence interval score display' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Confidence interval score display'</v>
       </c>
       <c r="G64" t="str">
-        <v>UI updates seamlessly, 'Confidence interval score display' executes correctly without console errors</v>
+        <v>Element 'Confidence interval score display' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H64" t="str">
         <v>Medium</v>
@@ -2663,16 +2663,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify Differential diagnosis breakdown rendering and execution in Web UI</v>
+        <v>Verify Differential diagnosis breakdown under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E65" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Differential diagnosis breakdown' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Differential diagnosis breakdown'</v>
       </c>
       <c r="G65" t="str">
-        <v>UI updates seamlessly, 'Differential diagnosis breakdown' executes correctly without console errors</v>
+        <v>Element 'Differential diagnosis breakdown' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H65" t="str">
         <v>Critical</v>
@@ -2698,16 +2698,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D66" t="str">
-        <v>Verify Pathology correlation chart rendering and execution in Web UI</v>
+        <v>Verify Pathology correlation chart under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E66" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Pathology correlation chart' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Pathology correlation chart'</v>
       </c>
       <c r="G66" t="str">
-        <v>UI updates seamlessly, 'Pathology correlation chart' executes correctly without console errors</v>
+        <v>Element 'Pathology correlation chart' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H66" t="str">
         <v>Medium</v>
@@ -2733,16 +2733,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D67" t="str">
-        <v>Verify Pharmacology lookup trigger rendering and execution in Web UI</v>
+        <v>Verify Pharmacology lookup trigger under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E67" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Pharmacology lookup trigger' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Pharmacology lookup trigger'</v>
       </c>
       <c r="G67" t="str">
-        <v>UI updates seamlessly, 'Pharmacology lookup trigger' executes correctly without console errors</v>
+        <v>Element 'Pharmacology lookup trigger' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H67" t="str">
         <v>High</v>
@@ -2768,16 +2768,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D68" t="str">
-        <v>Verify Circadian impact analysis rendering and execution in Web UI</v>
+        <v>Verify Circadian impact analysis under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E68" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Circadian impact analysis' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Circadian impact analysis'</v>
       </c>
       <c r="G68" t="str">
-        <v>UI updates seamlessly, 'Circadian impact analysis' executes correctly without console errors</v>
+        <v>Element 'Circadian impact analysis' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H68" t="str">
         <v>Medium</v>
@@ -2803,16 +2803,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D69" t="str">
-        <v>Verify Genetic risk indicator card rendering and execution in Web UI</v>
+        <v>Verify Genetic risk indicator card under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E69" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Genetic risk indicator card' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Genetic risk indicator card'</v>
       </c>
       <c r="G69" t="str">
-        <v>UI updates seamlessly, 'Genetic risk indicator card' executes correctly without console errors</v>
+        <v>Element 'Genetic risk indicator card' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H69" t="str">
         <v>Critical</v>
@@ -2838,16 +2838,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify Export raw JSON telemetry rendering and execution in Web UI</v>
+        <v>Verify Export raw JSON telemetry under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E70" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Export raw JSON telemetry' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Export raw JSON telemetry'</v>
       </c>
       <c r="G70" t="str">
-        <v>UI updates seamlessly, 'Export raw JSON telemetry' executes correctly without console errors</v>
+        <v>Element 'Export raw JSON telemetry' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H70" t="str">
         <v>Medium</v>
@@ -2873,16 +2873,16 @@
         <v>Deep Analysis</v>
       </c>
       <c r="D71" t="str">
-        <v>Verify Re-run deep analysis pipeline rendering and execution in Web UI</v>
+        <v>Verify Re-run deep analysis pipeline under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E71" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Diagnostics &gt; Deep Analysis, trigger 'Re-run deep analysis pipeline' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Verify DOM element rendering and click handler response for 'Re-run deep analysis pipeline'</v>
       </c>
       <c r="G71" t="str">
-        <v>UI updates seamlessly, 'Re-run deep analysis pipeline' executes correctly without console errors</v>
+        <v>Element 'Re-run deep analysis pipeline' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H71" t="str">
         <v>High</v>
@@ -2908,16 +2908,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify Archive assessment button rendering and execution in Web UI</v>
+        <v>Verify Archive assessment button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E72" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Archive assessment button' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Archive assessment button'</v>
       </c>
       <c r="G72" t="str">
-        <v>UI updates seamlessly, 'Archive assessment button' executes correctly without console errors</v>
+        <v>Element 'Archive assessment button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H72" t="str">
         <v>Medium</v>
@@ -2943,16 +2943,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify Archived records list view rendering and execution in Web UI</v>
+        <v>Verify Archived records list view under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E73" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Archived records list view' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Archived records list view'</v>
       </c>
       <c r="G73" t="str">
-        <v>UI updates seamlessly, 'Archived records list view' executes correctly without console errors</v>
+        <v>Element 'Archived records list view' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H73" t="str">
         <v>Critical</v>
@@ -2978,16 +2978,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D74" t="str">
-        <v>Verify Filter archives by date range rendering and execution in Web UI</v>
+        <v>Verify Filter archives by date range under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E74" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Filter archives by date range' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Filter archives by date range'</v>
       </c>
       <c r="G74" t="str">
-        <v>UI updates seamlessly, 'Filter archives by date range' executes correctly without console errors</v>
+        <v>Element 'Filter archives by date range' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H74" t="str">
         <v>Medium</v>
@@ -3013,16 +3013,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D75" t="str">
-        <v>Verify Filter archives by risk level rendering and execution in Web UI</v>
+        <v>Verify Filter archives by risk level under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E75" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Filter archives by risk level' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Filter archives by risk level'</v>
       </c>
       <c r="G75" t="str">
-        <v>UI updates seamlessly, 'Filter archives by risk level' executes correctly without console errors</v>
+        <v>Element 'Filter archives by risk level' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H75" t="str">
         <v>High</v>
@@ -3048,16 +3048,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify Search archived diagnostic logs rendering and execution in Web UI</v>
+        <v>Verify Search archived diagnostic logs under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E76" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Search archived diagnostic logs' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Search archived diagnostic logs'</v>
       </c>
       <c r="G76" t="str">
-        <v>UI updates seamlessly, 'Search archived diagnostic logs' executes correctly without console errors</v>
+        <v>Element 'Search archived diagnostic logs' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H76" t="str">
         <v>Medium</v>
@@ -3083,16 +3083,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify Unarchive record action rendering and execution in Web UI</v>
+        <v>Verify Unarchive record action under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E77" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Unarchive record action' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Unarchive record action'</v>
       </c>
       <c r="G77" t="str">
-        <v>UI updates seamlessly, 'Unarchive record action' executes correctly without console errors</v>
+        <v>Element 'Unarchive record action' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H77" t="str">
         <v>Critical</v>
@@ -3118,16 +3118,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D78" t="str">
-        <v>Verify Delete archived record entry rendering and execution in Web UI</v>
+        <v>Verify Delete archived record entry under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E78" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Delete archived record entry' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Delete archived record entry'</v>
       </c>
       <c r="G78" t="str">
-        <v>UI updates seamlessly, 'Delete archived record entry' executes correctly without console errors</v>
+        <v>Element 'Delete archived record entry' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H78" t="str">
         <v>Medium</v>
@@ -3153,16 +3153,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D79" t="str">
-        <v>Verify Export archive batch ZIP rendering and execution in Web UI</v>
+        <v>Verify Export archive batch ZIP under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E79" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Export archive batch ZIP' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Export archive batch ZIP'</v>
       </c>
       <c r="G79" t="str">
-        <v>UI updates seamlessly, 'Export archive batch ZIP' executes correctly without console errors</v>
+        <v>Element 'Export archive batch ZIP' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H79" t="str">
         <v>High</v>
@@ -3188,16 +3188,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D80" t="str">
-        <v>Verify Archive storage usage bar rendering and execution in Web UI</v>
+        <v>Verify Archive storage usage bar under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E80" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Archive storage usage bar' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Archive storage usage bar'</v>
       </c>
       <c r="G80" t="str">
-        <v>UI updates seamlessly, 'Archive storage usage bar' executes correctly without console errors</v>
+        <v>Element 'Archive storage usage bar' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H80" t="str">
         <v>Medium</v>
@@ -3223,16 +3223,16 @@
         <v>Archive Results</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify Compare archived reports tool rendering and execution in Web UI</v>
+        <v>Verify Compare archived reports tool under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E81" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Diagnostics &gt; Archive Results, trigger 'Compare archived reports tool' control, and observe DOM response</v>
+        <v>Navigate to Diagnostics &gt; Archive Results: Verify DOM element rendering and click handler response for 'Compare archived reports tool'</v>
       </c>
       <c r="G81" t="str">
-        <v>UI updates seamlessly, 'Compare archived reports tool' executes correctly without console errors</v>
+        <v>Element 'Compare archived reports tool' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H81" t="str">
         <v>Critical</v>
@@ -3258,16 +3258,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify Hospital search bar input rendering and execution in Web UI</v>
+        <v>Verify Hospital search bar input under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E82" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Hospital search bar input' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Hospital search bar input'</v>
       </c>
       <c r="G82" t="str">
-        <v>UI updates seamlessly, 'Hospital search bar input' executes correctly without console errors</v>
+        <v>Element 'Hospital search bar input' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H82" t="str">
         <v>Medium</v>
@@ -3293,16 +3293,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D83" t="str">
-        <v>Verify Current location GPS trigger rendering and execution in Web UI</v>
+        <v>Verify Current location GPS trigger under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E83" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Current location GPS trigger' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Current location GPS trigger'</v>
       </c>
       <c r="G83" t="str">
-        <v>UI updates seamlessly, 'Current location GPS trigger' executes correctly without console errors</v>
+        <v>Element 'Current location GPS trigger' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H83" t="str">
         <v>High</v>
@@ -3328,16 +3328,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D84" t="str">
-        <v>Verify Filter by ER availability rendering and execution in Web UI</v>
+        <v>Verify Filter by ER availability under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E84" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Filter by ER availability' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Filter by ER availability'</v>
       </c>
       <c r="G84" t="str">
-        <v>UI updates seamlessly, 'Filter by ER availability' executes correctly without console errors</v>
+        <v>Element 'Filter by ER availability' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H84" t="str">
         <v>Medium</v>
@@ -3363,16 +3363,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify Filter by specialty care rendering and execution in Web UI</v>
+        <v>Verify Filter by specialty care under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E85" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Filter by specialty care' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Filter by specialty care'</v>
       </c>
       <c r="G85" t="str">
-        <v>UI updates seamlessly, 'Filter by specialty care' executes correctly without console errors</v>
+        <v>Element 'Filter by specialty care' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H85" t="str">
         <v>Critical</v>
@@ -3398,16 +3398,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D86" t="str">
-        <v>Verify Hospital distance sorting rendering and execution in Web UI</v>
+        <v>Verify Hospital distance sorting under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E86" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Hospital distance sorting' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Hospital distance sorting'</v>
       </c>
       <c r="G86" t="str">
-        <v>UI updates seamlessly, 'Hospital distance sorting' executes correctly without console errors</v>
+        <v>Element 'Hospital distance sorting' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H86" t="str">
         <v>Medium</v>
@@ -3433,16 +3433,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D87" t="str">
-        <v>Verify Interactive map pin rendering rendering and execution in Web UI</v>
+        <v>Verify Interactive map pin rendering under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E87" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Interactive map pin rendering' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Interactive map pin rendering'</v>
       </c>
       <c r="G87" t="str">
-        <v>UI updates seamlessly, 'Interactive map pin rendering' executes correctly without console errors</v>
+        <v>Element 'Interactive map pin rendering' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H87" t="str">
         <v>High</v>
@@ -3468,16 +3468,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify Hospital contact card click rendering and execution in Web UI</v>
+        <v>Verify Hospital contact card click under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E88" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Hospital contact card click' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Hospital contact card click'</v>
       </c>
       <c r="G88" t="str">
-        <v>UI updates seamlessly, 'Hospital contact card click' executes correctly without console errors</v>
+        <v>Element 'Hospital contact card click' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H88" t="str">
         <v>Medium</v>
@@ -3503,16 +3503,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify Get Directions route launch rendering and execution in Web UI</v>
+        <v>Verify Get Directions route launch under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E89" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Get Directions route launch' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Get Directions route launch'</v>
       </c>
       <c r="G89" t="str">
-        <v>UI updates seamlessly, 'Get Directions route launch' executes correctly without console errors</v>
+        <v>Element 'Get Directions route launch' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H89" t="str">
         <v>Critical</v>
@@ -3538,16 +3538,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D90" t="str">
-        <v>Verify Bookmark favorite hospital rendering and execution in Web UI</v>
+        <v>Verify Bookmark favorite hospital under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E90" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Bookmark favorite hospital' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Bookmark favorite hospital'</v>
       </c>
       <c r="G90" t="str">
-        <v>UI updates seamlessly, 'Bookmark favorite hospital' executes correctly without console errors</v>
+        <v>Element 'Bookmark favorite hospital' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H90" t="str">
         <v>Medium</v>
@@ -3573,16 +3573,16 @@
         <v>Find Nearby Hospitals</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify Call emergency hotline button rendering and execution in Web UI</v>
+        <v>Verify Call emergency hotline button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E91" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Geolocation &gt; Find Nearby Hospitals, trigger 'Call emergency hotline button' control, and observe DOM response</v>
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Verify DOM element rendering and click handler response for 'Call emergency hotline button'</v>
       </c>
       <c r="G91" t="str">
-        <v>UI updates seamlessly, 'Call emergency hotline button' executes correctly without console errors</v>
+        <v>Element 'Call emergency hotline button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H91" t="str">
         <v>High</v>
@@ -3608,16 +3608,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify Profile avatar image upload rendering and execution in Web UI</v>
+        <v>Verify Profile avatar image upload under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E92" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Profile avatar image upload' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Profile avatar image upload'</v>
       </c>
       <c r="G92" t="str">
-        <v>UI updates seamlessly, 'Profile avatar image upload' executes correctly without console errors</v>
+        <v>Element 'Profile avatar image upload' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H92" t="str">
         <v>Medium</v>
@@ -3643,16 +3643,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D93" t="str">
-        <v>Verify Edit First Name input rendering and execution in Web UI</v>
+        <v>Verify Edit First Name input under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E93" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Edit First Name input' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Edit First Name input'</v>
       </c>
       <c r="G93" t="str">
-        <v>UI updates seamlessly, 'Edit First Name input' executes correctly without console errors</v>
+        <v>Element 'Edit First Name input' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H93" t="str">
         <v>Critical</v>
@@ -3678,16 +3678,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify Edit Last Name input rendering and execution in Web UI</v>
+        <v>Verify Edit Last Name input under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E94" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Edit Last Name input' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Edit Last Name input'</v>
       </c>
       <c r="G94" t="str">
-        <v>UI updates seamlessly, 'Edit Last Name input' executes correctly without console errors</v>
+        <v>Element 'Edit Last Name input' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H94" t="str">
         <v>Medium</v>
@@ -3713,16 +3713,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D95" t="str">
-        <v>Verify Date of birth picker rendering and execution in Web UI</v>
+        <v>Verify Date of birth picker under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E95" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Date of birth picker' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Date of birth picker'</v>
       </c>
       <c r="G95" t="str">
-        <v>UI updates seamlessly, 'Date of birth picker' executes correctly without console errors</v>
+        <v>Element 'Date of birth picker' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H95" t="str">
         <v>High</v>
@@ -3748,16 +3748,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify Blood type dropdown rendering and execution in Web UI</v>
+        <v>Verify Blood type dropdown under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E96" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Blood type dropdown' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Blood type dropdown'</v>
       </c>
       <c r="G96" t="str">
-        <v>UI updates seamlessly, 'Blood type dropdown' executes correctly without console errors</v>
+        <v>Element 'Blood type dropdown' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H96" t="str">
         <v>Medium</v>
@@ -3783,16 +3783,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify Emergency contact number rendering and execution in Web UI</v>
+        <v>Verify Emergency contact number under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E97" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Emergency contact number' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Emergency contact number'</v>
       </c>
       <c r="G97" t="str">
-        <v>UI updates seamlessly, 'Emergency contact number' executes correctly without console errors</v>
+        <v>Element 'Emergency contact number' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H97" t="str">
         <v>Critical</v>
@@ -3818,16 +3818,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D98" t="str">
-        <v>Verify Primary physician info rendering and execution in Web UI</v>
+        <v>Verify Primary physician info under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E98" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Primary physician info' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Primary physician info'</v>
       </c>
       <c r="G98" t="str">
-        <v>UI updates seamlessly, 'Primary physician info' executes correctly without console errors</v>
+        <v>Element 'Primary physician info' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H98" t="str">
         <v>Medium</v>
@@ -3853,16 +3853,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D99" t="str">
-        <v>Verify Save profile changes button rendering and execution in Web UI</v>
+        <v>Verify Save profile changes button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E99" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Save profile changes button' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Save profile changes button'</v>
       </c>
       <c r="G99" t="str">
-        <v>UI updates seamlessly, 'Save profile changes button' executes correctly without console errors</v>
+        <v>Element 'Save profile changes button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H99" t="str">
         <v>High</v>
@@ -3888,16 +3888,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify Discard profile edits button rendering and execution in Web UI</v>
+        <v>Verify Discard profile edits button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E100" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Discard profile edits button' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Discard profile edits button'</v>
       </c>
       <c r="G100" t="str">
-        <v>UI updates seamlessly, 'Discard profile edits button' executes correctly without console errors</v>
+        <v>Element 'Discard profile edits button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H100" t="str">
         <v>Medium</v>
@@ -3923,16 +3923,16 @@
         <v>Personal Info Edit</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify Unsaved changes warning modal rendering and execution in Web UI</v>
+        <v>Verify Unsaved changes warning modal under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E101" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Settings &gt; Personal Info Edit, trigger 'Unsaved changes warning modal' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Personal Info Edit: Verify DOM element rendering and click handler response for 'Unsaved changes warning modal'</v>
       </c>
       <c r="G101" t="str">
-        <v>UI updates seamlessly, 'Unsaved changes warning modal' executes correctly without console errors</v>
+        <v>Element 'Unsaved changes warning modal' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H101" t="str">
         <v>Critical</v>
@@ -3958,16 +3958,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D102" t="str">
-        <v>Verify Light mode radio option rendering and execution in Web UI</v>
+        <v>Verify Light mode radio option under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E102" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Light mode radio option' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Light mode radio option'</v>
       </c>
       <c r="G102" t="str">
-        <v>UI updates seamlessly, 'Light mode radio option' executes correctly without console errors</v>
+        <v>Element 'Light mode radio option' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H102" t="str">
         <v>Medium</v>
@@ -3993,16 +3993,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D103" t="str">
-        <v>Verify Dark mode radio option rendering and execution in Web UI</v>
+        <v>Verify Dark mode radio option under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E103" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Dark mode radio option' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Dark mode radio option'</v>
       </c>
       <c r="G103" t="str">
-        <v>UI updates seamlessly, 'Dark mode radio option' executes correctly without console errors</v>
+        <v>Element 'Dark mode radio option' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H103" t="str">
         <v>High</v>
@@ -4028,16 +4028,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D104" t="str">
-        <v>Verify System default theme option rendering and execution in Web UI</v>
+        <v>Verify System default theme option under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E104" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'System default theme option' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'System default theme option'</v>
       </c>
       <c r="G104" t="str">
-        <v>UI updates seamlessly, 'System default theme option' executes correctly without console errors</v>
+        <v>Element 'System default theme option' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H104" t="str">
         <v>Medium</v>
@@ -4063,16 +4063,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D105" t="str">
-        <v>Verify Font size scaling slider rendering and execution in Web UI</v>
+        <v>Verify Font size scaling slider under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E105" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Font size scaling slider' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Font size scaling slider'</v>
       </c>
       <c r="G105" t="str">
-        <v>UI updates seamlessly, 'Font size scaling slider' executes correctly without console errors</v>
+        <v>Element 'Font size scaling slider' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H105" t="str">
         <v>Critical</v>
@@ -4098,16 +4098,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D106" t="str">
-        <v>Verify High contrast mode toggle rendering and execution in Web UI</v>
+        <v>Verify High contrast mode toggle under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E106" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'High contrast mode toggle' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'High contrast mode toggle'</v>
       </c>
       <c r="G106" t="str">
-        <v>UI updates seamlessly, 'High contrast mode toggle' executes correctly without console errors</v>
+        <v>Element 'High contrast mode toggle' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H106" t="str">
         <v>Medium</v>
@@ -4133,16 +4133,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D107" t="str">
-        <v>Verify Reduced animation toggle rendering and execution in Web UI</v>
+        <v>Verify Reduced animation toggle under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E107" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Reduced animation toggle' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Reduced animation toggle'</v>
       </c>
       <c r="G107" t="str">
-        <v>UI updates seamlessly, 'Reduced animation toggle' executes correctly without console errors</v>
+        <v>Element 'Reduced animation toggle' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H107" t="str">
         <v>High</v>
@@ -4168,16 +4168,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D108" t="str">
-        <v>Verify Theme change preview pane rendering and execution in Web UI</v>
+        <v>Verify Theme change preview pane under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E108" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Theme change preview pane' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Theme change preview pane'</v>
       </c>
       <c r="G108" t="str">
-        <v>UI updates seamlessly, 'Theme change preview pane' executes correctly without console errors</v>
+        <v>Element 'Theme change preview pane' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H108" t="str">
         <v>Medium</v>
@@ -4203,16 +4203,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D109" t="str">
-        <v>Verify Color blind filter selection rendering and execution in Web UI</v>
+        <v>Verify Color blind filter selection under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E109" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Color blind filter selection' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Color blind filter selection'</v>
       </c>
       <c r="G109" t="str">
-        <v>UI updates seamlessly, 'Color blind filter selection' executes correctly without console errors</v>
+        <v>Element 'Color blind filter selection' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H109" t="str">
         <v>Critical</v>
@@ -4238,16 +4238,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D110" t="str">
-        <v>Verify Accent color palette chooser rendering and execution in Web UI</v>
+        <v>Verify Accent color palette chooser under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E110" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Accent color palette chooser' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Accent color palette chooser'</v>
       </c>
       <c r="G110" t="str">
-        <v>UI updates seamlessly, 'Accent color palette chooser' executes correctly without console errors</v>
+        <v>Element 'Accent color palette chooser' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H110" t="str">
         <v>Medium</v>
@@ -4273,16 +4273,16 @@
         <v>Display &amp; Theme</v>
       </c>
       <c r="D111" t="str">
-        <v>Verify Reset visual defaults button rendering and execution in Web UI</v>
+        <v>Verify Reset visual defaults button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E111" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Settings &gt; Display &amp; Theme, trigger 'Reset visual defaults button' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Display &amp; Theme: Verify DOM element rendering and click handler response for 'Reset visual defaults button'</v>
       </c>
       <c r="G111" t="str">
-        <v>UI updates seamlessly, 'Reset visual defaults button' executes correctly without console errors</v>
+        <v>Element 'Reset visual defaults button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H111" t="str">
         <v>High</v>
@@ -4308,16 +4308,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify Change password modal rendering and execution in Web UI</v>
+        <v>Verify Change password modal under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E112" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'Change password modal' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'Change password modal'</v>
       </c>
       <c r="G112" t="str">
-        <v>UI updates seamlessly, 'Change password modal' executes correctly without console errors</v>
+        <v>Element 'Change password modal' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H112" t="str">
         <v>Medium</v>
@@ -4343,16 +4343,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D113" t="str">
-        <v>Verify Old password verification rendering and execution in Web UI</v>
+        <v>Verify Old password verification under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E113" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'Old password verification' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'Old password verification'</v>
       </c>
       <c r="G113" t="str">
-        <v>UI updates seamlessly, 'Old password verification' executes correctly without console errors</v>
+        <v>Element 'Old password verification' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H113" t="str">
         <v>Critical</v>
@@ -4378,16 +4378,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D114" t="str">
-        <v>Verify New password submission rendering and execution in Web UI</v>
+        <v>Verify New password submission under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E114" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'New password submission' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'New password submission'</v>
       </c>
       <c r="G114" t="str">
-        <v>UI updates seamlessly, 'New password submission' executes correctly without console errors</v>
+        <v>Element 'New password submission' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H114" t="str">
         <v>Medium</v>
@@ -4413,16 +4413,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D115" t="str">
-        <v>Verify Update mobile number input rendering and execution in Web UI</v>
+        <v>Verify Update mobile number input under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E115" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'Update mobile number input' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'Update mobile number input'</v>
       </c>
       <c r="G115" t="str">
-        <v>UI updates seamlessly, 'Update mobile number input' executes correctly without console errors</v>
+        <v>Element 'Update mobile number input' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H115" t="str">
         <v>High</v>
@@ -4448,16 +4448,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D116" t="str">
-        <v>Verify SMS OTP verification step rendering and execution in Web UI</v>
+        <v>Verify SMS OTP verification step under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E116" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'SMS OTP verification step' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'SMS OTP verification step'</v>
       </c>
       <c r="G116" t="str">
-        <v>UI updates seamlessly, 'SMS OTP verification step' executes correctly without console errors</v>
+        <v>Element 'SMS OTP verification step' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H116" t="str">
         <v>Medium</v>
@@ -4483,16 +4483,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D117" t="str">
-        <v>Verify 2FA Enable/Disable toggle rendering and execution in Web UI</v>
+        <v>Verify 2FA Enable/Disable toggle under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E117" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger '2FA Enable/Disable toggle' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for '2FA Enable/Disable toggle'</v>
       </c>
       <c r="G117" t="str">
-        <v>UI updates seamlessly, '2FA Enable/Disable toggle' executes correctly without console errors</v>
+        <v>Element '2FA Enable/Disable toggle' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H117" t="str">
         <v>Critical</v>
@@ -4518,16 +4518,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D118" t="str">
-        <v>Verify FaceID / Fingerprint toggle rendering and execution in Web UI</v>
+        <v>Verify FaceID / Fingerprint toggle under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E118" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'FaceID / Fingerprint toggle' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'FaceID / Fingerprint toggle'</v>
       </c>
       <c r="G118" t="str">
-        <v>UI updates seamlessly, 'FaceID / Fingerprint toggle' executes correctly without console errors</v>
+        <v>Element 'FaceID / Fingerprint toggle' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H118" t="str">
         <v>Medium</v>
@@ -4553,16 +4553,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D119" t="str">
-        <v>Verify Anonymous telemetry opt-out rendering and execution in Web UI</v>
+        <v>Verify Anonymous telemetry opt-out under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E119" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'Anonymous telemetry opt-out' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'Anonymous telemetry opt-out'</v>
       </c>
       <c r="G119" t="str">
-        <v>UI updates seamlessly, 'Anonymous telemetry opt-out' executes correctly without console errors</v>
+        <v>Element 'Anonymous telemetry opt-out' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H119" t="str">
         <v>High</v>
@@ -4588,16 +4588,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D120" t="str">
-        <v>Verify Download health data report rendering and execution in Web UI</v>
+        <v>Verify Download health data report under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E120" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'Download health data report' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'Download health data report'</v>
       </c>
       <c r="G120" t="str">
-        <v>UI updates seamlessly, 'Download health data report' executes correctly without console errors</v>
+        <v>Element 'Download health data report' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H120" t="str">
         <v>Medium</v>
@@ -4623,16 +4623,16 @@
         <v>Privacy &amp; Security</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify Permanently delete account modal rendering and execution in Web UI</v>
+        <v>Verify Permanently delete account modal under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E121" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Settings &gt; Privacy &amp; Security, trigger 'Permanently delete account modal' control, and observe DOM response</v>
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Verify DOM element rendering and click handler response for 'Permanently delete account modal'</v>
       </c>
       <c r="G121" t="str">
-        <v>UI updates seamlessly, 'Permanently delete account modal' executes correctly without console errors</v>
+        <v>Element 'Permanently delete account modal' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H121" t="str">
         <v>Critical</v>
@@ -4658,16 +4658,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D122" t="str">
-        <v>Verify Live support chat widget rendering and execution in Web UI</v>
+        <v>Verify Live support chat widget under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E122" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Live support chat widget' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Live support chat widget'</v>
       </c>
       <c r="G122" t="str">
-        <v>UI updates seamlessly, 'Live support chat widget' executes correctly without console errors</v>
+        <v>Element 'Live support chat widget' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H122" t="str">
         <v>Medium</v>
@@ -4693,16 +4693,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D123" t="str">
-        <v>Verify Send message input field rendering and execution in Web UI</v>
+        <v>Verify Send message input field under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E123" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Send message input field' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Send message input field'</v>
       </c>
       <c r="G123" t="str">
-        <v>UI updates seamlessly, 'Send message input field' executes correctly without console errors</v>
+        <v>Element 'Send message input field' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H123" t="str">
         <v>High</v>
@@ -4728,16 +4728,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D124" t="str">
-        <v>Verify Attachment upload button rendering and execution in Web UI</v>
+        <v>Verify Attachment upload button under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E124" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Attachment upload button' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Attachment upload button'</v>
       </c>
       <c r="G124" t="str">
-        <v>UI updates seamlessly, 'Attachment upload button' executes correctly without console errors</v>
+        <v>Element 'Attachment upload button' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H124" t="str">
         <v>Medium</v>
@@ -4763,16 +4763,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D125" t="str">
-        <v>Verify Email support ticket form rendering and execution in Web UI</v>
+        <v>Verify Email support ticket form under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E125" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Email support ticket form' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Email support ticket form'</v>
       </c>
       <c r="G125" t="str">
-        <v>UI updates seamlessly, 'Email support ticket form' executes correctly without console errors</v>
+        <v>Element 'Email support ticket form' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H125" t="str">
         <v>Critical</v>
@@ -4798,16 +4798,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D126" t="str">
-        <v>Verify Community forum post link rendering and execution in Web UI</v>
+        <v>Verify Community forum post link under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E126" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Community forum post link' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Community forum post link'</v>
       </c>
       <c r="G126" t="str">
-        <v>UI updates seamlessly, 'Community forum post link' executes correctly without console errors</v>
+        <v>Element 'Community forum post link' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H126" t="str">
         <v>Medium</v>
@@ -4833,16 +4833,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D127" t="str">
-        <v>Verify System status green indicator rendering and execution in Web UI</v>
+        <v>Verify System status green indicator under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E127" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'System status green indicator' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'System status green indicator'</v>
       </c>
       <c r="G127" t="str">
-        <v>UI updates seamlessly, 'System status green indicator' executes correctly without console errors</v>
+        <v>Element 'System status green indicator' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H127" t="str">
         <v>High</v>
@@ -4868,16 +4868,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D128" t="str">
-        <v>Verify Server uptime status card rendering and execution in Web UI</v>
+        <v>Verify Server uptime status card under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E128" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Server uptime status card' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Server uptime status card'</v>
       </c>
       <c r="G128" t="str">
-        <v>UI updates seamlessly, 'Server uptime status card' executes correctly without console errors</v>
+        <v>Element 'Server uptime status card' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H128" t="str">
         <v>Medium</v>
@@ -4903,16 +4903,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D129" t="str">
-        <v>Verify API latency indicator rendering and execution in Web UI</v>
+        <v>Verify API latency indicator under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E129" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'API latency indicator' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'API latency indicator'</v>
       </c>
       <c r="G129" t="str">
-        <v>UI updates seamlessly, 'API latency indicator' executes correctly without console errors</v>
+        <v>Element 'API latency indicator' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H129" t="str">
         <v>Critical</v>
@@ -4938,16 +4938,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D130" t="str">
-        <v>Verify Health score calculator UI rendering and execution in Web UI</v>
+        <v>Verify Health score calculator UI under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E130" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'Health score calculator UI' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'Health score calculator UI'</v>
       </c>
       <c r="G130" t="str">
-        <v>UI updates seamlessly, 'Health score calculator UI' executes correctly without console errors</v>
+        <v>Element 'Health score calculator UI' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H130" t="str">
         <v>Medium</v>
@@ -4973,16 +4973,16 @@
         <v>Live Support &amp; Status</v>
       </c>
       <c r="D131" t="str">
-        <v>Verify FAQ accordion expand/collapse rendering and execution in Web UI</v>
+        <v>Verify FAQ accordion expand/collapse under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E131" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Clinical Support &gt; Live Support &amp; Status, trigger 'FAQ accordion expand/collapse' control, and observe DOM response</v>
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Verify DOM element rendering and click handler response for 'FAQ accordion expand/collapse'</v>
       </c>
       <c r="G131" t="str">
-        <v>UI updates seamlessly, 'FAQ accordion expand/collapse' executes correctly without console errors</v>
+        <v>Element 'FAQ accordion expand/collapse' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H131" t="str">
         <v>High</v>
@@ -5008,16 +5008,16 @@
         <v>Health Education</v>
       </c>
       <c r="D132" t="str">
-        <v>Verify Article search bar rendering and execution in Web UI</v>
+        <v>Verify Article search bar under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E132" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Article search bar' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Article search bar'</v>
       </c>
       <c r="G132" t="str">
-        <v>UI updates seamlessly, 'Article search bar' executes correctly without console errors</v>
+        <v>Element 'Article search bar' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H132" t="str">
         <v>Medium</v>
@@ -5043,16 +5043,16 @@
         <v>Health Education</v>
       </c>
       <c r="D133" t="str">
-        <v>Verify Category filter chips rendering and execution in Web UI</v>
+        <v>Verify Category filter chips under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E133" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Category filter chips' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Category filter chips'</v>
       </c>
       <c r="G133" t="str">
-        <v>UI updates seamlessly, 'Category filter chips' executes correctly without console errors</v>
+        <v>Element 'Category filter chips' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H133" t="str">
         <v>Critical</v>
@@ -5078,16 +5078,16 @@
         <v>Health Education</v>
       </c>
       <c r="D134" t="str">
-        <v>Verify Nutrition guide article view rendering and execution in Web UI</v>
+        <v>Verify Nutrition guide article view under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E134" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Nutrition guide article view' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Nutrition guide article view'</v>
       </c>
       <c r="G134" t="str">
-        <v>UI updates seamlessly, 'Nutrition guide article view' executes correctly without console errors</v>
+        <v>Element 'Nutrition guide article view' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H134" t="str">
         <v>Medium</v>
@@ -5113,16 +5113,16 @@
         <v>Health Education</v>
       </c>
       <c r="D135" t="str">
-        <v>Verify Exercise protocol video player rendering and execution in Web UI</v>
+        <v>Verify Exercise protocol video player under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E135" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Exercise protocol video player' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Exercise protocol video player'</v>
       </c>
       <c r="G135" t="str">
-        <v>UI updates seamlessly, 'Exercise protocol video player' executes correctly without console errors</v>
+        <v>Element 'Exercise protocol video player' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H135" t="str">
         <v>High</v>
@@ -5148,16 +5148,16 @@
         <v>Health Education</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify Mental health audio guide rendering and execution in Web UI</v>
+        <v>Verify Mental health audio guide under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E136" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Mental health audio guide' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Mental health audio guide'</v>
       </c>
       <c r="G136" t="str">
-        <v>UI updates seamlessly, 'Mental health audio guide' executes correctly without console errors</v>
+        <v>Element 'Mental health audio guide' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H136" t="str">
         <v>Medium</v>
@@ -5183,16 +5183,16 @@
         <v>Health Education</v>
       </c>
       <c r="D137" t="str">
-        <v>Verify Sleep hygiene checklist rendering and execution in Web UI</v>
+        <v>Verify Sleep hygiene checklist under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E137" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Sleep hygiene checklist' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Sleep hygiene checklist'</v>
       </c>
       <c r="G137" t="str">
-        <v>UI updates seamlessly, 'Sleep hygiene checklist' executes correctly without console errors</v>
+        <v>Element 'Sleep hygiene checklist' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H137" t="str">
         <v>Critical</v>
@@ -5218,16 +5218,16 @@
         <v>Health Education</v>
       </c>
       <c r="D138" t="str">
-        <v>Verify Pathology glossary lookup rendering and execution in Web UI</v>
+        <v>Verify Pathology glossary lookup under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E138" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Pathology glossary lookup' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Pathology glossary lookup'</v>
       </c>
       <c r="G138" t="str">
-        <v>UI updates seamlessly, 'Pathology glossary lookup' executes correctly without console errors</v>
+        <v>Element 'Pathology glossary lookup' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H138" t="str">
         <v>Medium</v>
@@ -5253,16 +5253,16 @@
         <v>Health Education</v>
       </c>
       <c r="D139" t="str">
-        <v>Verify Pharmacology search bar rendering and execution in Web UI</v>
+        <v>Verify Pharmacology search bar under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E139" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Pharmacology search bar' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Pharmacology search bar'</v>
       </c>
       <c r="G139" t="str">
-        <v>UI updates seamlessly, 'Pharmacology search bar' executes correctly without console errors</v>
+        <v>Element 'Pharmacology search bar' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H139" t="str">
         <v>High</v>
@@ -5288,16 +5288,16 @@
         <v>Health Education</v>
       </c>
       <c r="D140" t="str">
-        <v>Verify Vascular dynamics study view rendering and execution in Web UI</v>
+        <v>Verify Vascular dynamics study view under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E140" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Vascular dynamics study view' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Vascular dynamics study view'</v>
       </c>
       <c r="G140" t="str">
-        <v>UI updates seamlessly, 'Vascular dynamics study view' executes correctly without console errors</v>
+        <v>Element 'Vascular dynamics study view' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H140" t="str">
         <v>Medium</v>
@@ -5323,16 +5323,16 @@
         <v>Health Education</v>
       </c>
       <c r="D141" t="str">
-        <v>Verify Bookmark article for offline rendering and execution in Web UI</v>
+        <v>Verify Bookmark article for offline under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E141" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Learn Module &gt; Health Education, trigger 'Bookmark article for offline' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Health Education: Verify DOM element rendering and click handler response for 'Bookmark article for offline'</v>
       </c>
       <c r="G141" t="str">
-        <v>UI updates seamlessly, 'Bookmark article for offline' executes correctly without console errors</v>
+        <v>Element 'Bookmark article for offline' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H141" t="str">
         <v>Critical</v>
@@ -5358,16 +5358,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify Macro nutrient quiz start rendering and execution in Web UI</v>
+        <v>Verify Macro nutrient quiz start under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E142" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Macro nutrient quiz start' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Macro nutrient quiz start'</v>
       </c>
       <c r="G142" t="str">
-        <v>UI updates seamlessly, 'Macro nutrient quiz start' executes correctly without console errors</v>
+        <v>Element 'Macro nutrient quiz start' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H142" t="str">
         <v>Medium</v>
@@ -5393,16 +5393,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D143" t="str">
-        <v>Verify Question 1 multiple choice rendering and execution in Web UI</v>
+        <v>Verify Question 1 multiple choice under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E143" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Question 1 multiple choice' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Question 1 multiple choice'</v>
       </c>
       <c r="G143" t="str">
-        <v>UI updates seamlessly, 'Question 1 multiple choice' executes correctly without console errors</v>
+        <v>Element 'Question 1 multiple choice' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H143" t="str">
         <v>High</v>
@@ -5428,16 +5428,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D144" t="str">
-        <v>Verify Question 2 scale selector rendering and execution in Web UI</v>
+        <v>Verify Question 2 scale selector under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E144" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Question 2 scale selector' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Question 2 scale selector'</v>
       </c>
       <c r="G144" t="str">
-        <v>UI updates seamlessly, 'Question 2 scale selector' executes correctly without console errors</v>
+        <v>Element 'Question 2 scale selector' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H144" t="str">
         <v>Medium</v>
@@ -5463,16 +5463,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify Quiz timer progress bar rendering and execution in Web UI</v>
+        <v>Verify Quiz timer progress bar under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E145" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Quiz timer progress bar' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Quiz timer progress bar'</v>
       </c>
       <c r="G145" t="str">
-        <v>UI updates seamlessly, 'Quiz timer progress bar' executes correctly without console errors</v>
+        <v>Element 'Quiz timer progress bar' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H145" t="str">
         <v>Critical</v>
@@ -5498,16 +5498,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D146" t="str">
-        <v>Verify Submit quiz answers rendering and execution in Web UI</v>
+        <v>Verify Submit quiz answers under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E146" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Submit quiz answers' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Submit quiz answers'</v>
       </c>
       <c r="G146" t="str">
-        <v>UI updates seamlessly, 'Submit quiz answers' executes correctly without console errors</v>
+        <v>Element 'Submit quiz answers' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H146" t="str">
         <v>Medium</v>
@@ -5533,16 +5533,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D147" t="str">
-        <v>Verify Quiz score result card rendering and execution in Web UI</v>
+        <v>Verify Quiz score result card under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E147" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Quiz score result card' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Quiz score result card'</v>
       </c>
       <c r="G147" t="str">
-        <v>UI updates seamlessly, 'Quiz score result card' executes correctly without console errors</v>
+        <v>Element 'Quiz score result card' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H147" t="str">
         <v>High</v>
@@ -5568,16 +5568,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D148" t="str">
-        <v>Verify Review incorrect answers rendering and execution in Web UI</v>
+        <v>Verify Review incorrect answers under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E148" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Review incorrect answers' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Review incorrect answers'</v>
       </c>
       <c r="G148" t="str">
-        <v>UI updates seamlessly, 'Review incorrect answers' executes correctly without console errors</v>
+        <v>Element 'Review incorrect answers' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H148" t="str">
         <v>Medium</v>
@@ -5603,16 +5603,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D149" t="str">
-        <v>Verify Retake quiz action rendering and execution in Web UI</v>
+        <v>Verify Retake quiz action under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E149" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Retake quiz action' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Retake quiz action'</v>
       </c>
       <c r="G149" t="str">
-        <v>UI updates seamlessly, 'Retake quiz action' executes correctly without console errors</v>
+        <v>Element 'Retake quiz action' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H149" t="str">
         <v>Critical</v>
@@ -5638,16 +5638,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D150" t="str">
-        <v>Verify Certificate badge render rendering and execution in Web UI</v>
+        <v>Verify Certificate badge render under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E150" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Certificate badge render' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Certificate badge render'</v>
       </c>
       <c r="G150" t="str">
-        <v>UI updates seamlessly, 'Certificate badge render' executes correctly without console errors</v>
+        <v>Element 'Certificate badge render' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H150" t="str">
         <v>Medium</v>
@@ -5673,16 +5673,16 @@
         <v>Quizzes &amp; Synthesis</v>
       </c>
       <c r="D151" t="str">
-        <v>Verify Share quiz result banner rendering and execution in Web UI</v>
+        <v>Verify Share quiz result banner under Standard Desktop Chrome (1920x1080)</v>
       </c>
       <c r="E151" t="str">
-        <v>User authenticated on Chrome browser at 1920x1080 resolution</v>
+        <v>User active on Standard Desktop Chrome (1920x1080) with clean session context</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis, trigger 'Share quiz result banner' control, and observe DOM response</v>
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Verify DOM element rendering and click handler response for 'Share quiz result banner'</v>
       </c>
       <c r="G151" t="str">
-        <v>UI updates seamlessly, 'Share quiz result banner' executes correctly without console errors</v>
+        <v>Element 'Share quiz result banner' responds smoothly without console errors or layout shift</v>
       </c>
       <c r="H151" t="str">
         <v>High</v>
@@ -5697,9 +5697,5259 @@
         <v>Pass</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TC151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Verify Email input validation under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E152" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Email input validation'</v>
+      </c>
+      <c r="G152" t="str">
+        <v>Element 'Email input validation' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H152" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I152" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TC152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Verify Password visibility toggle under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E153" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Password visibility toggle'</v>
+      </c>
+      <c r="G153" t="str">
+        <v>Element 'Password visibility toggle' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H153" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I153" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TC153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Verify Remember me checkbox under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E154" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Remember me checkbox'</v>
+      </c>
+      <c r="G154" t="str">
+        <v>Element 'Remember me checkbox' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H154" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I154" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>TC154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Verify Sign In button state under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E155" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Sign In button state'</v>
+      </c>
+      <c r="G155" t="str">
+        <v>Element 'Sign In button state' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H155" t="str">
+        <v>High</v>
+      </c>
+      <c r="I155" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>TC155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Verify Invalid credentials alert under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E156" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Invalid credentials alert'</v>
+      </c>
+      <c r="G156" t="str">
+        <v>Element 'Invalid credentials alert' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H156" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I156" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K156" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>TC156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Verify Session persistence check under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E157" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Session persistence check'</v>
+      </c>
+      <c r="G157" t="str">
+        <v>Element 'Session persistence check' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H157" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I157" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>TC157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Verify OAuth Google Sign-In under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E158" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'OAuth Google Sign-In'</v>
+      </c>
+      <c r="G158" t="str">
+        <v>Element 'OAuth Google Sign-In' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H158" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I158" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>TC158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Verify OAuth Apple Sign-In under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E159" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'OAuth Apple Sign-In'</v>
+      </c>
+      <c r="G159" t="str">
+        <v>Element 'OAuth Apple Sign-In' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H159" t="str">
+        <v>High</v>
+      </c>
+      <c r="I159" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>TC159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Verify SSO Redirect flow under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E160" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'SSO Redirect flow'</v>
+      </c>
+      <c r="G160" t="str">
+        <v>Element 'SSO Redirect flow' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H160" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I160" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K160" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>TC160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Sign In</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Verify Logout session destruction under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E161" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Navigate to Authentication &gt; Sign In: Validate touch hit box and CSS media query adaptation for 'Logout session destruction'</v>
+      </c>
+      <c r="G161" t="str">
+        <v>Element 'Logout session destruction' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H161" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I161" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>TC161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Verify Full Name field validation under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E162" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Full Name field validation'</v>
+      </c>
+      <c r="G162" t="str">
+        <v>Element 'Full Name field validation' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I162" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TC162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Verify Email syntax checker under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E163" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Email syntax checker'</v>
+      </c>
+      <c r="G163" t="str">
+        <v>Element 'Email syntax checker' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H163" t="str">
+        <v>High</v>
+      </c>
+      <c r="I163" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>TC163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Verify Password strength meter under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E164" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Password strength meter'</v>
+      </c>
+      <c r="G164" t="str">
+        <v>Element 'Password strength meter' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I164" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K164" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>TC164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Verify Confirm password matching under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E165" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Confirm password matching'</v>
+      </c>
+      <c r="G165" t="str">
+        <v>Element 'Confirm password matching' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H165" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>TC165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Verify Terms consent checkbox under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E166" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Terms consent checkbox'</v>
+      </c>
+      <c r="G166" t="str">
+        <v>Element 'Terms consent checkbox' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K166" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>TC166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Verify Biometric age picker under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E167" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Biometric age picker'</v>
+      </c>
+      <c r="G167" t="str">
+        <v>Element 'Biometric age picker' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H167" t="str">
+        <v>High</v>
+      </c>
+      <c r="I167" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>TC167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Verify Gender selection radio under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E168" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Gender selection radio'</v>
+      </c>
+      <c r="G168" t="str">
+        <v>Element 'Gender selection radio' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H168" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>TC168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Verify Registration submit button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E169" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Registration submit button'</v>
+      </c>
+      <c r="G169" t="str">
+        <v>Element 'Registration submit button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H169" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>TC169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Verify Duplicate email error toast under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E170" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Duplicate email error toast'</v>
+      </c>
+      <c r="G170" t="str">
+        <v>Element 'Duplicate email error toast' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H170" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I170" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>TC170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Sign Up</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Verify Welcome modal trigger under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E171" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Navigate to Authentication &gt; Sign Up: Validate touch hit box and CSS media query adaptation for 'Welcome modal trigger'</v>
+      </c>
+      <c r="G171" t="str">
+        <v>Element 'Welcome modal trigger' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H171" t="str">
+        <v>High</v>
+      </c>
+      <c r="I171" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>TC171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Verify Email recovery prompt under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E172" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Email recovery prompt'</v>
+      </c>
+      <c r="G172" t="str">
+        <v>Element 'Email recovery prompt' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I172" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K172" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>TC172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Verify Reset link trigger button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E173" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Reset link trigger button'</v>
+      </c>
+      <c r="G173" t="str">
+        <v>Element 'Reset link trigger button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H173" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I173" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K173" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>TC173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Verify Back to Sign In link under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E174" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Back to Sign In link'</v>
+      </c>
+      <c r="G174" t="str">
+        <v>Element 'Back to Sign In link' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H174" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I174" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K174" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>TC174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Verify Invalid email warning under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E175" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Invalid email warning'</v>
+      </c>
+      <c r="G175" t="str">
+        <v>Element 'Invalid email warning' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H175" t="str">
+        <v>High</v>
+      </c>
+      <c r="I175" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K175" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>TC175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Verify Success banner display under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E176" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Success banner display'</v>
+      </c>
+      <c r="G176" t="str">
+        <v>Element 'Success banner display' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H176" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I176" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K176" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>TC176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Verify Rate limit on reset requests under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E177" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Rate limit on reset requests'</v>
+      </c>
+      <c r="G177" t="str">
+        <v>Element 'Rate limit on reset requests' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H177" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I177" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K177" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TC177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Verify Token link expiration handling under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E178" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Token link expiration handling'</v>
+      </c>
+      <c r="G178" t="str">
+        <v>Element 'Token link expiration handling' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H178" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I178" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J178" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K178" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>TC178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Verify New password input under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E179" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'New password input'</v>
+      </c>
+      <c r="G179" t="str">
+        <v>Element 'New password input' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H179" t="str">
+        <v>High</v>
+      </c>
+      <c r="I179" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J179" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K179" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TC179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Verify Confirm new password under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E180" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Confirm new password'</v>
+      </c>
+      <c r="G180" t="str">
+        <v>Element 'Confirm new password' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H180" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I180" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K180" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TC180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Forgot Password</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Verify Password reset completion redirect under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E181" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Navigate to Authentication &gt; Forgot Password: Validate touch hit box and CSS media query adaptation for 'Password reset completion redirect'</v>
+      </c>
+      <c r="G181" t="str">
+        <v>Element 'Password reset completion redirect' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H181" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I181" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K181" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>TC181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Verify Symptom search input autocomplete under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E182" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Symptom search input autocomplete'</v>
+      </c>
+      <c r="G182" t="str">
+        <v>Element 'Symptom search input autocomplete' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H182" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I182" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J182" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K182" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>TC182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Verify Primary symptom tag selection under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E183" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Primary symptom tag selection'</v>
+      </c>
+      <c r="G183" t="str">
+        <v>Element 'Primary symptom tag selection' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H183" t="str">
+        <v>High</v>
+      </c>
+      <c r="I183" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J183" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K183" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>TC183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Verify Severity slider adjustment under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E184" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Severity slider adjustment'</v>
+      </c>
+      <c r="G184" t="str">
+        <v>Element 'Severity slider adjustment' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H184" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I184" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J184" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K184" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>TC184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Verify Duration selection dropdown under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E185" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Duration selection dropdown'</v>
+      </c>
+      <c r="G185" t="str">
+        <v>Element 'Duration selection dropdown' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H185" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I185" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J185" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K185" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>TC185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Verify Body region target selector under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E186" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Body region target selector'</v>
+      </c>
+      <c r="G186" t="str">
+        <v>Element 'Body region target selector' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H186" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I186" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J186" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K186" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>TC186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Verify Additional notes text area under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E187" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Additional notes text area'</v>
+      </c>
+      <c r="G187" t="str">
+        <v>Element 'Additional notes text area' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H187" t="str">
+        <v>High</v>
+      </c>
+      <c r="I187" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J187" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K187" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>TC187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Verify Analyze Symptoms action button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E188" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F188" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Analyze Symptoms action button'</v>
+      </c>
+      <c r="G188" t="str">
+        <v>Element 'Analyze Symptoms action button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H188" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I188" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K188" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>TC188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Verify Clear selected symptoms button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E189" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F189" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Clear selected symptoms button'</v>
+      </c>
+      <c r="G189" t="str">
+        <v>Element 'Clear selected symptoms button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H189" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I189" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J189" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K189" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TC189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Verify Symptom history list render under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E190" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Symptom history list render'</v>
+      </c>
+      <c r="G190" t="str">
+        <v>Element 'Symptom history list render' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H190" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I190" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J190" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K190" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TC190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Symptom Checker</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Verify Recent assessment card view under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E191" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F191" t="str">
+        <v>Navigate to Diagnostics &gt; Symptom Checker: Validate touch hit box and CSS media query adaptation for 'Recent assessment card view'</v>
+      </c>
+      <c r="G191" t="str">
+        <v>Element 'Recent assessment card view' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H191" t="str">
+        <v>High</v>
+      </c>
+      <c r="I191" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J191" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K191" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TC191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Verify Multi-step questionnaire step 1 under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E192" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Multi-step questionnaire step 1'</v>
+      </c>
+      <c r="G192" t="str">
+        <v>Element 'Multi-step questionnaire step 1' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H192" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I192" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J192" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K192" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TC192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Verify Multi-step questionnaire step 2 under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E193" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Multi-step questionnaire step 2'</v>
+      </c>
+      <c r="G193" t="str">
+        <v>Element 'Multi-step questionnaire step 2' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I193" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J193" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K193" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TC193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Verify Multi-step questionnaire step 3 under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E194" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Multi-step questionnaire step 3'</v>
+      </c>
+      <c r="G194" t="str">
+        <v>Element 'Multi-step questionnaire step 3' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I194" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J194" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K194" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TC194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Verify Risk score percentage display under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E195" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Risk score percentage display'</v>
+      </c>
+      <c r="G195" t="str">
+        <v>Element 'Risk score percentage display' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H195" t="str">
+        <v>High</v>
+      </c>
+      <c r="I195" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J195" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K195" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TC195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Verify Condition likelihood ranking under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E196" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Condition likelihood ranking'</v>
+      </c>
+      <c r="G196" t="str">
+        <v>Element 'Condition likelihood ranking' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I196" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J196" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K196" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>TC196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Verify Emergency warning banner under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E197" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Emergency warning banner'</v>
+      </c>
+      <c r="G197" t="str">
+        <v>Element 'Emergency warning banner' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I197" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J197" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K197" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>TC197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Verify Doctor recommendation card under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E198" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Doctor recommendation card'</v>
+      </c>
+      <c r="G198" t="str">
+        <v>Element 'Doctor recommendation card' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I198" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J198" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K198" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>TC198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Verify Print assessment summary under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E199" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Print assessment summary'</v>
+      </c>
+      <c r="G199" t="str">
+        <v>Element 'Print assessment summary' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H199" t="str">
+        <v>High</v>
+      </c>
+      <c r="I199" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J199" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K199" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>TC199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Verify Share assessment modal under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E200" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Share assessment modal'</v>
+      </c>
+      <c r="G200" t="str">
+        <v>Element 'Share assessment modal' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I200" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J200" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K200" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>TC200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Detailed Assessment</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Verify Save assessment to profile under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E201" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Navigate to Diagnostics &gt; Detailed Assessment: Validate touch hit box and CSS media query adaptation for 'Save assessment to profile'</v>
+      </c>
+      <c r="G201" t="str">
+        <v>Element 'Save assessment to profile' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I201" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J201" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K201" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>TC201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Verify PDF report generator button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E202" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'PDF report generator button'</v>
+      </c>
+      <c r="G202" t="str">
+        <v>Element 'PDF report generator button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I202" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J202" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K202" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>TC202</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Verify Doctor PDF export format under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E203" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Doctor PDF export format'</v>
+      </c>
+      <c r="G203" t="str">
+        <v>Element 'Doctor PDF export format' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H203" t="str">
+        <v>High</v>
+      </c>
+      <c r="I203" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J203" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K203" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>TC203</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Verify Vitals summary chart render under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E204" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F204" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Vitals summary chart render'</v>
+      </c>
+      <c r="G204" t="str">
+        <v>Element 'Vitals summary chart render' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I204" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J204" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K204" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>TC204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Verify Symptom timeline visualization under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E205" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F205" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Symptom timeline visualization'</v>
+      </c>
+      <c r="G205" t="str">
+        <v>Element 'Symptom timeline visualization' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I205" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J205" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K205" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>TC205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Verify Clinical notes section under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E206" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Clinical notes section'</v>
+      </c>
+      <c r="G206" t="str">
+        <v>Element 'Clinical notes section' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I206" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J206" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K206" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>TC206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Verify Prescription record attachment under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E207" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Prescription record attachment'</v>
+      </c>
+      <c r="G207" t="str">
+        <v>Element 'Prescription record attachment' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H207" t="str">
+        <v>High</v>
+      </c>
+      <c r="I207" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J207" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K207" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>TC207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Verify Digital signature validation under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E208" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F208" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Digital signature validation'</v>
+      </c>
+      <c r="G208" t="str">
+        <v>Element 'Digital signature validation' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I208" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J208" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K208" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TC208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Verify Download report action under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E209" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Download report action'</v>
+      </c>
+      <c r="G209" t="str">
+        <v>Element 'Download report action' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I209" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J209" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K209" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>TC209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Verify Email report to doctor form under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E210" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Email report to doctor form'</v>
+      </c>
+      <c r="G210" t="str">
+        <v>Element 'Email report to doctor form' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I210" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J210" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K210" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>TC210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Diagnostic Report</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Verify Print friendly view toggle under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E211" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Navigate to Diagnostics &gt; Diagnostic Report: Validate touch hit box and CSS media query adaptation for 'Print friendly view toggle'</v>
+      </c>
+      <c r="G211" t="str">
+        <v>Element 'Print friendly view toggle' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H211" t="str">
+        <v>High</v>
+      </c>
+      <c r="I211" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J211" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K211" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>TC211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Verify Unlock Deep Analysis modal under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E212" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Unlock Deep Analysis modal'</v>
+      </c>
+      <c r="G212" t="str">
+        <v>Element 'Unlock Deep Analysis modal' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I212" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J212" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K212" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>TC212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Verify AI model selection dropdown under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E213" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'AI model selection dropdown'</v>
+      </c>
+      <c r="G213" t="str">
+        <v>Element 'AI model selection dropdown' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I213" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J213" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K213" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>TC213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Verify Confidence interval score display under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E214" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Confidence interval score display'</v>
+      </c>
+      <c r="G214" t="str">
+        <v>Element 'Confidence interval score display' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I214" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J214" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K214" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>TC214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Verify Differential diagnosis breakdown under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E215" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Differential diagnosis breakdown'</v>
+      </c>
+      <c r="G215" t="str">
+        <v>Element 'Differential diagnosis breakdown' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H215" t="str">
+        <v>High</v>
+      </c>
+      <c r="I215" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J215" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K215" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>TC215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Verify Pathology correlation chart under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E216" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Pathology correlation chart'</v>
+      </c>
+      <c r="G216" t="str">
+        <v>Element 'Pathology correlation chart' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I216" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J216" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K216" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>TC216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Verify Pharmacology lookup trigger under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E217" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Pharmacology lookup trigger'</v>
+      </c>
+      <c r="G217" t="str">
+        <v>Element 'Pharmacology lookup trigger' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H217" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I217" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J217" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K217" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>TC217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Verify Circadian impact analysis under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E218" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Circadian impact analysis'</v>
+      </c>
+      <c r="G218" t="str">
+        <v>Element 'Circadian impact analysis' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I218" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J218" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K218" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>TC218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Verify Genetic risk indicator card under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E219" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Genetic risk indicator card'</v>
+      </c>
+      <c r="G219" t="str">
+        <v>Element 'Genetic risk indicator card' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H219" t="str">
+        <v>High</v>
+      </c>
+      <c r="I219" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J219" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K219" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>TC219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Verify Export raw JSON telemetry under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E220" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Export raw JSON telemetry'</v>
+      </c>
+      <c r="G220" t="str">
+        <v>Element 'Export raw JSON telemetry' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H220" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I220" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J220" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K220" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>TC220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Deep Analysis</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Verify Re-run deep analysis pipeline under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E221" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Navigate to Diagnostics &gt; Deep Analysis: Validate touch hit box and CSS media query adaptation for 'Re-run deep analysis pipeline'</v>
+      </c>
+      <c r="G221" t="str">
+        <v>Element 'Re-run deep analysis pipeline' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H221" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I221" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J221" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K221" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>TC221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Verify Archive assessment button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E222" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Archive assessment button'</v>
+      </c>
+      <c r="G222" t="str">
+        <v>Element 'Archive assessment button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H222" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I222" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J222" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K222" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>TC222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Verify Archived records list view under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E223" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Archived records list view'</v>
+      </c>
+      <c r="G223" t="str">
+        <v>Element 'Archived records list view' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H223" t="str">
+        <v>High</v>
+      </c>
+      <c r="I223" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J223" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K223" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>TC223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Verify Filter archives by date range under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E224" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Filter archives by date range'</v>
+      </c>
+      <c r="G224" t="str">
+        <v>Element 'Filter archives by date range' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H224" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I224" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J224" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K224" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TC224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Verify Filter archives by risk level under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E225" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Filter archives by risk level'</v>
+      </c>
+      <c r="G225" t="str">
+        <v>Element 'Filter archives by risk level' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H225" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I225" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J225" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K225" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>TC225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Verify Search archived diagnostic logs under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E226" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F226" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Search archived diagnostic logs'</v>
+      </c>
+      <c r="G226" t="str">
+        <v>Element 'Search archived diagnostic logs' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H226" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I226" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J226" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K226" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>TC226</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Verify Unarchive record action under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E227" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Unarchive record action'</v>
+      </c>
+      <c r="G227" t="str">
+        <v>Element 'Unarchive record action' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H227" t="str">
+        <v>High</v>
+      </c>
+      <c r="I227" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J227" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K227" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>TC227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Verify Delete archived record entry under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E228" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Delete archived record entry'</v>
+      </c>
+      <c r="G228" t="str">
+        <v>Element 'Delete archived record entry' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H228" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I228" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J228" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K228" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>TC228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Verify Export archive batch ZIP under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E229" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Export archive batch ZIP'</v>
+      </c>
+      <c r="G229" t="str">
+        <v>Element 'Export archive batch ZIP' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H229" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I229" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J229" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K229" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>TC229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Verify Archive storage usage bar under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E230" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Archive storage usage bar'</v>
+      </c>
+      <c r="G230" t="str">
+        <v>Element 'Archive storage usage bar' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H230" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I230" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J230" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K230" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>TC230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Diagnostics</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Archive Results</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Verify Compare archived reports tool under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E231" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F231" t="str">
+        <v>Navigate to Diagnostics &gt; Archive Results: Validate touch hit box and CSS media query adaptation for 'Compare archived reports tool'</v>
+      </c>
+      <c r="G231" t="str">
+        <v>Element 'Compare archived reports tool' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H231" t="str">
+        <v>High</v>
+      </c>
+      <c r="I231" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J231" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K231" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>TC231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Verify Hospital search bar input under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E232" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F232" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Hospital search bar input'</v>
+      </c>
+      <c r="G232" t="str">
+        <v>Element 'Hospital search bar input' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H232" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I232" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J232" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K232" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>TC232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Verify Current location GPS trigger under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E233" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Current location GPS trigger'</v>
+      </c>
+      <c r="G233" t="str">
+        <v>Element 'Current location GPS trigger' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H233" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I233" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J233" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K233" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>TC233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Verify Filter by ER availability under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E234" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Filter by ER availability'</v>
+      </c>
+      <c r="G234" t="str">
+        <v>Element 'Filter by ER availability' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H234" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I234" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J234" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K234" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>TC234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Verify Filter by specialty care under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E235" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F235" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Filter by specialty care'</v>
+      </c>
+      <c r="G235" t="str">
+        <v>Element 'Filter by specialty care' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H235" t="str">
+        <v>High</v>
+      </c>
+      <c r="I235" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J235" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K235" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>TC235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Verify Hospital distance sorting under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E236" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Hospital distance sorting'</v>
+      </c>
+      <c r="G236" t="str">
+        <v>Element 'Hospital distance sorting' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H236" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I236" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J236" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K236" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>TC236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Verify Interactive map pin rendering under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E237" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Interactive map pin rendering'</v>
+      </c>
+      <c r="G237" t="str">
+        <v>Element 'Interactive map pin rendering' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H237" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I237" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J237" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K237" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>TC237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Verify Hospital contact card click under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E238" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Hospital contact card click'</v>
+      </c>
+      <c r="G238" t="str">
+        <v>Element 'Hospital contact card click' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H238" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I238" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J238" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K238" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>TC238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Verify Get Directions route launch under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E239" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F239" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Get Directions route launch'</v>
+      </c>
+      <c r="G239" t="str">
+        <v>Element 'Get Directions route launch' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H239" t="str">
+        <v>High</v>
+      </c>
+      <c r="I239" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J239" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K239" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>TC239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Verify Bookmark favorite hospital under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E240" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F240" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Bookmark favorite hospital'</v>
+      </c>
+      <c r="G240" t="str">
+        <v>Element 'Bookmark favorite hospital' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H240" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I240" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J240" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K240" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>TC240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Geolocation</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Find Nearby Hospitals</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Verify Call emergency hotline button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E241" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Navigate to Geolocation &gt; Find Nearby Hospitals: Validate touch hit box and CSS media query adaptation for 'Call emergency hotline button'</v>
+      </c>
+      <c r="G241" t="str">
+        <v>Element 'Call emergency hotline button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H241" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I241" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J241" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K241" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>TC241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Verify Profile avatar image upload under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E242" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F242" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Profile avatar image upload'</v>
+      </c>
+      <c r="G242" t="str">
+        <v>Element 'Profile avatar image upload' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H242" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I242" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J242" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K242" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>TC242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Verify Edit First Name input under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E243" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F243" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Edit First Name input'</v>
+      </c>
+      <c r="G243" t="str">
+        <v>Element 'Edit First Name input' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H243" t="str">
+        <v>High</v>
+      </c>
+      <c r="I243" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J243" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K243" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>TC243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Verify Edit Last Name input under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E244" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Edit Last Name input'</v>
+      </c>
+      <c r="G244" t="str">
+        <v>Element 'Edit Last Name input' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H244" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I244" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J244" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K244" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>TC244</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Verify Date of birth picker under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E245" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Date of birth picker'</v>
+      </c>
+      <c r="G245" t="str">
+        <v>Element 'Date of birth picker' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H245" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I245" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J245" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K245" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>TC245</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Verify Blood type dropdown under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E246" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Blood type dropdown'</v>
+      </c>
+      <c r="G246" t="str">
+        <v>Element 'Blood type dropdown' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H246" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I246" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J246" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K246" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>TC246</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Verify Emergency contact number under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E247" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Emergency contact number'</v>
+      </c>
+      <c r="G247" t="str">
+        <v>Element 'Emergency contact number' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H247" t="str">
+        <v>High</v>
+      </c>
+      <c r="I247" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J247" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K247" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>TC247</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Verify Primary physician info under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E248" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F248" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Primary physician info'</v>
+      </c>
+      <c r="G248" t="str">
+        <v>Element 'Primary physician info' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H248" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I248" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J248" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K248" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>TC248</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Verify Save profile changes button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E249" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F249" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Save profile changes button'</v>
+      </c>
+      <c r="G249" t="str">
+        <v>Element 'Save profile changes button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H249" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I249" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J249" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K249" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>TC249</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Verify Discard profile edits button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E250" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Discard profile edits button'</v>
+      </c>
+      <c r="G250" t="str">
+        <v>Element 'Discard profile edits button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H250" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I250" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J250" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K250" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>TC250</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Personal Info Edit</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Verify Unsaved changes warning modal under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E251" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F251" t="str">
+        <v>Navigate to Settings &gt; Personal Info Edit: Validate touch hit box and CSS media query adaptation for 'Unsaved changes warning modal'</v>
+      </c>
+      <c r="G251" t="str">
+        <v>Element 'Unsaved changes warning modal' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H251" t="str">
+        <v>High</v>
+      </c>
+      <c r="I251" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J251" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K251" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>TC251</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Verify Light mode radio option under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E252" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Light mode radio option'</v>
+      </c>
+      <c r="G252" t="str">
+        <v>Element 'Light mode radio option' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H252" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I252" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J252" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K252" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>TC252</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Verify Dark mode radio option under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E253" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Dark mode radio option'</v>
+      </c>
+      <c r="G253" t="str">
+        <v>Element 'Dark mode radio option' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H253" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I253" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J253" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K253" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>TC253</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Verify System default theme option under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E254" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'System default theme option'</v>
+      </c>
+      <c r="G254" t="str">
+        <v>Element 'System default theme option' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H254" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I254" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J254" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K254" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>TC254</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Verify Font size scaling slider under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E255" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Font size scaling slider'</v>
+      </c>
+      <c r="G255" t="str">
+        <v>Element 'Font size scaling slider' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H255" t="str">
+        <v>High</v>
+      </c>
+      <c r="I255" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J255" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K255" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>TC255</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Verify High contrast mode toggle under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E256" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'High contrast mode toggle'</v>
+      </c>
+      <c r="G256" t="str">
+        <v>Element 'High contrast mode toggle' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H256" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I256" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J256" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K256" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>TC256</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Verify Reduced animation toggle under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E257" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Reduced animation toggle'</v>
+      </c>
+      <c r="G257" t="str">
+        <v>Element 'Reduced animation toggle' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H257" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I257" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J257" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K257" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>TC257</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D258" t="str">
+        <v>Verify Theme change preview pane under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E258" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Theme change preview pane'</v>
+      </c>
+      <c r="G258" t="str">
+        <v>Element 'Theme change preview pane' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H258" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I258" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J258" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K258" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>TC258</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D259" t="str">
+        <v>Verify Color blind filter selection under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E259" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Color blind filter selection'</v>
+      </c>
+      <c r="G259" t="str">
+        <v>Element 'Color blind filter selection' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H259" t="str">
+        <v>High</v>
+      </c>
+      <c r="I259" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J259" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K259" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>TC259</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Verify Accent color palette chooser under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E260" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Accent color palette chooser'</v>
+      </c>
+      <c r="G260" t="str">
+        <v>Element 'Accent color palette chooser' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H260" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I260" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J260" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K260" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>TC260</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Display &amp; Theme</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Verify Reset visual defaults button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E261" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Navigate to Settings &gt; Display &amp; Theme: Validate touch hit box and CSS media query adaptation for 'Reset visual defaults button'</v>
+      </c>
+      <c r="G261" t="str">
+        <v>Element 'Reset visual defaults button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H261" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I261" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J261" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K261" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>TC261</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Verify Change password modal under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E262" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'Change password modal'</v>
+      </c>
+      <c r="G262" t="str">
+        <v>Element 'Change password modal' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H262" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I262" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J262" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K262" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>TC262</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Verify Old password verification under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E263" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'Old password verification'</v>
+      </c>
+      <c r="G263" t="str">
+        <v>Element 'Old password verification' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H263" t="str">
+        <v>High</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J263" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K263" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>TC263</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Verify New password submission under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E264" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'New password submission'</v>
+      </c>
+      <c r="G264" t="str">
+        <v>Element 'New password submission' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H264" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I264" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J264" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K264" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TC264</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Verify Update mobile number input under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E265" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'Update mobile number input'</v>
+      </c>
+      <c r="G265" t="str">
+        <v>Element 'Update mobile number input' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H265" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I265" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J265" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K265" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>TC265</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Verify SMS OTP verification step under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E266" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'SMS OTP verification step'</v>
+      </c>
+      <c r="G266" t="str">
+        <v>Element 'SMS OTP verification step' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H266" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J266" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K266" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>TC266</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Verify 2FA Enable/Disable toggle under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E267" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for '2FA Enable/Disable toggle'</v>
+      </c>
+      <c r="G267" t="str">
+        <v>Element '2FA Enable/Disable toggle' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H267" t="str">
+        <v>High</v>
+      </c>
+      <c r="I267" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J267" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K267" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>TC267</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Verify FaceID / Fingerprint toggle under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E268" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'FaceID / Fingerprint toggle'</v>
+      </c>
+      <c r="G268" t="str">
+        <v>Element 'FaceID / Fingerprint toggle' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H268" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I268" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J268" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K268" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>TC268</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Verify Anonymous telemetry opt-out under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E269" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'Anonymous telemetry opt-out'</v>
+      </c>
+      <c r="G269" t="str">
+        <v>Element 'Anonymous telemetry opt-out' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H269" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I269" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J269" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K269" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>TC269</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Verify Download health data report under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E270" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'Download health data report'</v>
+      </c>
+      <c r="G270" t="str">
+        <v>Element 'Download health data report' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H270" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I270" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J270" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K270" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>TC270</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Privacy &amp; Security</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Verify Permanently delete account modal under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E271" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Navigate to Settings &gt; Privacy &amp; Security: Validate touch hit box and CSS media query adaptation for 'Permanently delete account modal'</v>
+      </c>
+      <c r="G271" t="str">
+        <v>Element 'Permanently delete account modal' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H271" t="str">
+        <v>High</v>
+      </c>
+      <c r="I271" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J271" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K271" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>TC271</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Verify Live support chat widget under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E272" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Live support chat widget'</v>
+      </c>
+      <c r="G272" t="str">
+        <v>Element 'Live support chat widget' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H272" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I272" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J272" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K272" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>TC272</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Verify Send message input field under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E273" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Send message input field'</v>
+      </c>
+      <c r="G273" t="str">
+        <v>Element 'Send message input field' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H273" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I273" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J273" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K273" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TC273</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Verify Attachment upload button under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E274" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Attachment upload button'</v>
+      </c>
+      <c r="G274" t="str">
+        <v>Element 'Attachment upload button' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H274" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I274" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J274" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K274" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TC274</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Verify Email support ticket form under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E275" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Email support ticket form'</v>
+      </c>
+      <c r="G275" t="str">
+        <v>Element 'Email support ticket form' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H275" t="str">
+        <v>High</v>
+      </c>
+      <c r="I275" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J275" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K275" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TC275</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Verify Community forum post link under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E276" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Community forum post link'</v>
+      </c>
+      <c r="G276" t="str">
+        <v>Element 'Community forum post link' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H276" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I276" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J276" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K276" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TC276</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Verify System status green indicator under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E277" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'System status green indicator'</v>
+      </c>
+      <c r="G277" t="str">
+        <v>Element 'System status green indicator' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H277" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I277" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J277" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K277" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TC277</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Verify Server uptime status card under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E278" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Server uptime status card'</v>
+      </c>
+      <c r="G278" t="str">
+        <v>Element 'Server uptime status card' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H278" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I278" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J278" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K278" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TC278</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Verify API latency indicator under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E279" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'API latency indicator'</v>
+      </c>
+      <c r="G279" t="str">
+        <v>Element 'API latency indicator' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H279" t="str">
+        <v>High</v>
+      </c>
+      <c r="I279" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J279" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K279" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TC279</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Verify Health score calculator UI under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E280" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'Health score calculator UI'</v>
+      </c>
+      <c r="G280" t="str">
+        <v>Element 'Health score calculator UI' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H280" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I280" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J280" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K280" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>TC280</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Clinical Support</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Live Support &amp; Status</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Verify FAQ accordion expand/collapse under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E281" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Navigate to Clinical Support &gt; Live Support &amp; Status: Validate touch hit box and CSS media query adaptation for 'FAQ accordion expand/collapse'</v>
+      </c>
+      <c r="G281" t="str">
+        <v>Element 'FAQ accordion expand/collapse' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H281" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I281" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J281" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K281" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>TC281</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Verify Article search bar under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E282" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Article search bar'</v>
+      </c>
+      <c r="G282" t="str">
+        <v>Element 'Article search bar' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H282" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I282" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J282" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K282" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>TC282</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Verify Category filter chips under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E283" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Category filter chips'</v>
+      </c>
+      <c r="G283" t="str">
+        <v>Element 'Category filter chips' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H283" t="str">
+        <v>High</v>
+      </c>
+      <c r="I283" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J283" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K283" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>TC283</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Verify Nutrition guide article view under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E284" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Nutrition guide article view'</v>
+      </c>
+      <c r="G284" t="str">
+        <v>Element 'Nutrition guide article view' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H284" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I284" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J284" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K284" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>TC284</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Verify Exercise protocol video player under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E285" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Exercise protocol video player'</v>
+      </c>
+      <c r="G285" t="str">
+        <v>Element 'Exercise protocol video player' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H285" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I285" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J285" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K285" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>TC285</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Verify Mental health audio guide under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E286" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Mental health audio guide'</v>
+      </c>
+      <c r="G286" t="str">
+        <v>Element 'Mental health audio guide' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H286" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I286" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J286" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K286" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>TC286</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Verify Sleep hygiene checklist under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E287" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Sleep hygiene checklist'</v>
+      </c>
+      <c r="G287" t="str">
+        <v>Element 'Sleep hygiene checklist' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H287" t="str">
+        <v>High</v>
+      </c>
+      <c r="I287" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J287" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K287" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>TC287</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Verify Pathology glossary lookup under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E288" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Pathology glossary lookup'</v>
+      </c>
+      <c r="G288" t="str">
+        <v>Element 'Pathology glossary lookup' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H288" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I288" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J288" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K288" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>TC288</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Verify Pharmacology search bar under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E289" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Pharmacology search bar'</v>
+      </c>
+      <c r="G289" t="str">
+        <v>Element 'Pharmacology search bar' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H289" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I289" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J289" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K289" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>TC289</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D290" t="str">
+        <v>Verify Vascular dynamics study view under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E290" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Vascular dynamics study view'</v>
+      </c>
+      <c r="G290" t="str">
+        <v>Element 'Vascular dynamics study view' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H290" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I290" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J290" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K290" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>TC290</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Health Education</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Verify Bookmark article for offline under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E291" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F291" t="str">
+        <v>Navigate to Learn Module &gt; Health Education: Validate touch hit box and CSS media query adaptation for 'Bookmark article for offline'</v>
+      </c>
+      <c r="G291" t="str">
+        <v>Element 'Bookmark article for offline' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H291" t="str">
+        <v>High</v>
+      </c>
+      <c r="I291" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J291" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K291" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>TC291</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Verify Macro nutrient quiz start under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E292" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Macro nutrient quiz start'</v>
+      </c>
+      <c r="G292" t="str">
+        <v>Element 'Macro nutrient quiz start' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H292" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I292" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J292" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K292" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>TC292</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D293" t="str">
+        <v>Verify Question 1 multiple choice under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E293" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Question 1 multiple choice'</v>
+      </c>
+      <c r="G293" t="str">
+        <v>Element 'Question 1 multiple choice' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H293" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I293" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J293" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K293" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>TC293</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D294" t="str">
+        <v>Verify Question 2 scale selector under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E294" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F294" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Question 2 scale selector'</v>
+      </c>
+      <c r="G294" t="str">
+        <v>Element 'Question 2 scale selector' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H294" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I294" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J294" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K294" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>TC294</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D295" t="str">
+        <v>Verify Quiz timer progress bar under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E295" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F295" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Quiz timer progress bar'</v>
+      </c>
+      <c r="G295" t="str">
+        <v>Element 'Quiz timer progress bar' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H295" t="str">
+        <v>High</v>
+      </c>
+      <c r="I295" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J295" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K295" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>TC295</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D296" t="str">
+        <v>Verify Submit quiz answers under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E296" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F296" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Submit quiz answers'</v>
+      </c>
+      <c r="G296" t="str">
+        <v>Element 'Submit quiz answers' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H296" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I296" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J296" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K296" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>TC296</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D297" t="str">
+        <v>Verify Quiz score result card under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E297" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F297" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Quiz score result card'</v>
+      </c>
+      <c r="G297" t="str">
+        <v>Element 'Quiz score result card' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H297" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I297" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J297" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K297" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>TC297</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D298" t="str">
+        <v>Verify Review incorrect answers under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E298" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F298" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Review incorrect answers'</v>
+      </c>
+      <c r="G298" t="str">
+        <v>Element 'Review incorrect answers' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H298" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I298" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J298" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K298" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>TC298</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Verify Retake quiz action under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E299" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F299" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Retake quiz action'</v>
+      </c>
+      <c r="G299" t="str">
+        <v>Element 'Retake quiz action' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H299" t="str">
+        <v>High</v>
+      </c>
+      <c r="I299" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J299" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K299" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>TC299</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D300" t="str">
+        <v>Verify Certificate badge render under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E300" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F300" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Certificate badge render'</v>
+      </c>
+      <c r="G300" t="str">
+        <v>Element 'Certificate badge render' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H300" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I300" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J300" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K300" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>TC300</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Learn Module</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Quizzes &amp; Synthesis</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Verify Share quiz result banner under Responsive Mobile Web Viewport (375x812)</v>
+      </c>
+      <c r="E301" t="str">
+        <v>User active on Responsive Mobile Web Viewport (375x812) with clean session context</v>
+      </c>
+      <c r="F301" t="str">
+        <v>Navigate to Learn Module &gt; Quizzes &amp; Synthesis: Validate touch hit box and CSS media query adaptation for 'Share quiz result banner'</v>
+      </c>
+      <c r="G301" t="str">
+        <v>Element 'Share quiz result banner' responds smoothly without console errors or layout shift</v>
+      </c>
+      <c r="H301" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I301" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="J301" t="str">
+        <v>Web/React</v>
+      </c>
+      <c r="K301" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K301"/>
   </ignoredErrors>
 </worksheet>
 </file>